--- a/public/downloads/drift_radar.xlsx
+++ b/public/downloads/drift_radar.xlsx
@@ -8,11 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All prompts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drifting" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Own-only silence" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full silence" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source mix" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All prompts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drifting" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Own-only silence" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full silence" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source mix" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +34,9 @@
     <font>
       <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -64,10 +68,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -623,6 +636,216 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Drift Radar workbook – read this first</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Visibility &amp; Wilson columns</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>All visibility_*, wilson_lo_*, wilson_hi_*, mean_visibility, range_visibility, and competitor_* columns are 0–1 ratios. Multiply by 100 for percent display, or apply Excel format »0%« to the columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>divergence_score</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>0.7 × range(visibility) + 0.3 × clamp(CV, 0, 2) / 2. Bounded in [0, 1]. ≥ 0.30 is the »drifting« shortlist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>wilson_lo_&lt;engine&gt; · wilson_hi_&lt;engine&gt;</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Wilson 95 % confidence interval [lower, upper] for the visibility point estimate, computed over the sampled chat count (typically N = 3 for a 3-day window). Wide intervals are honest, not noise – Peec samples once per engine per day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>silence_type</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>own_only = brand absent on every engine, at least one competitor cited; full = no tracked brand mentioned on any engine. Empty = active (drifting or aligned).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>competitor_&lt;brand&gt;</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Wide-format max-visibility per competitor (one column per tracked competitor). For pivot work, consider the long-format helper drift_radar.csv or drift_radar.json.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>competitor_&lt;brand&gt;_&lt;engine&gt;</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Per-engine competitor visibility for fine-grained pivots. 0 = absent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>top_competitors</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Pre-formatted comma-separated string of the top 5 cited competitors with peak visibility – ready for paste into a deck or report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>gap_urls_top3</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Pipe-separated URLs that engines cited next to competitors but not next to the brand. The earned-placement target list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Sheet map</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Headline KPIs and per-engine averages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>All prompts</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Master row-per-prompt with full Wilson CI + competitor matrix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Drifting</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Filter: divergence_score ≥ 0.30.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Own-only silence</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Filter: silence_type = own_only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Full silence</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Filter: silence_type = full.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Source mix</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Per-prompt domain-class share of all retrieved citations.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -681,262 +904,262 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>prompt_id</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>prompt_text</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>topic</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>divergence_score</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>cv_visibility</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>range_visibility</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>mean_visibility</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>own_silence</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>silence_type</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>visibility_chatgpt</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>mentions_chatgpt</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="5" t="inlineStr">
         <is>
           <t>wilson_lo_chatgpt</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="5" t="inlineStr">
         <is>
           <t>wilson_hi_chatgpt</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>visibility_gemini</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="5" t="inlineStr">
         <is>
           <t>mentions_gemini</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>wilson_lo_gemini</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="R1" s="5" t="inlineStr">
         <is>
           <t>wilson_hi_gemini</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="S1" s="5" t="inlineStr">
         <is>
           <t>visibility_ai_overview</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="T1" s="5" t="inlineStr">
         <is>
           <t>mentions_ai_overview</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="U1" s="5" t="inlineStr">
         <is>
           <t>wilson_lo_ai_overview</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="V1" s="5" t="inlineStr">
         <is>
           <t>wilson_hi_ai_overview</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="W1" s="5" t="inlineStr">
         <is>
           <t>competitor_max_havens</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="X1" s="5" t="inlineStr">
         <is>
           <t>competitor_max_pavo</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="Y1" s="5" t="inlineStr">
         <is>
           <t>competitor_max_marstall</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="Z1" s="5" t="inlineStr">
         <is>
           <t>competitor_max_eggersmann</t>
         </is>
       </c>
-      <c r="AA1" s="2" t="inlineStr">
+      <c r="AA1" s="5" t="inlineStr">
         <is>
           <t>competitor_max_höveler</t>
         </is>
       </c>
-      <c r="AB1" s="2" t="inlineStr">
+      <c r="AB1" s="5" t="inlineStr">
         <is>
           <t>competitor_max_nösenberger</t>
         </is>
       </c>
-      <c r="AC1" s="2" t="inlineStr">
+      <c r="AC1" s="5" t="inlineStr">
         <is>
           <t>competitor_max_st__hippolyt</t>
         </is>
       </c>
-      <c r="AD1" s="2" t="inlineStr">
+      <c r="AD1" s="5" t="inlineStr">
         <is>
           <t>competitor_havens_chatgpt</t>
         </is>
       </c>
-      <c r="AE1" s="2" t="inlineStr">
+      <c r="AE1" s="5" t="inlineStr">
         <is>
           <t>competitor_havens_gemini</t>
         </is>
       </c>
-      <c r="AF1" s="2" t="inlineStr">
+      <c r="AF1" s="5" t="inlineStr">
         <is>
           <t>competitor_havens_ai_overview</t>
         </is>
       </c>
-      <c r="AG1" s="2" t="inlineStr">
+      <c r="AG1" s="5" t="inlineStr">
         <is>
           <t>competitor_pavo_chatgpt</t>
         </is>
       </c>
-      <c r="AH1" s="2" t="inlineStr">
+      <c r="AH1" s="5" t="inlineStr">
         <is>
           <t>competitor_pavo_gemini</t>
         </is>
       </c>
-      <c r="AI1" s="2" t="inlineStr">
+      <c r="AI1" s="5" t="inlineStr">
         <is>
           <t>competitor_pavo_ai_overview</t>
         </is>
       </c>
-      <c r="AJ1" s="2" t="inlineStr">
+      <c r="AJ1" s="5" t="inlineStr">
         <is>
           <t>competitor_marstall_chatgpt</t>
         </is>
       </c>
-      <c r="AK1" s="2" t="inlineStr">
+      <c r="AK1" s="5" t="inlineStr">
         <is>
           <t>competitor_marstall_gemini</t>
         </is>
       </c>
-      <c r="AL1" s="2" t="inlineStr">
+      <c r="AL1" s="5" t="inlineStr">
         <is>
           <t>competitor_marstall_ai_overview</t>
         </is>
       </c>
-      <c r="AM1" s="2" t="inlineStr">
+      <c r="AM1" s="5" t="inlineStr">
         <is>
           <t>competitor_eggersmann_chatgpt</t>
         </is>
       </c>
-      <c r="AN1" s="2" t="inlineStr">
+      <c r="AN1" s="5" t="inlineStr">
         <is>
           <t>competitor_eggersmann_gemini</t>
         </is>
       </c>
-      <c r="AO1" s="2" t="inlineStr">
+      <c r="AO1" s="5" t="inlineStr">
         <is>
           <t>competitor_eggersmann_ai_overview</t>
         </is>
       </c>
-      <c r="AP1" s="2" t="inlineStr">
+      <c r="AP1" s="5" t="inlineStr">
         <is>
           <t>competitor_höveler_chatgpt</t>
         </is>
       </c>
-      <c r="AQ1" s="2" t="inlineStr">
+      <c r="AQ1" s="5" t="inlineStr">
         <is>
           <t>competitor_höveler_gemini</t>
         </is>
       </c>
-      <c r="AR1" s="2" t="inlineStr">
+      <c r="AR1" s="5" t="inlineStr">
         <is>
           <t>competitor_höveler_ai_overview</t>
         </is>
       </c>
-      <c r="AS1" s="2" t="inlineStr">
+      <c r="AS1" s="5" t="inlineStr">
         <is>
           <t>competitor_nösenberger_chatgpt</t>
         </is>
       </c>
-      <c r="AT1" s="2" t="inlineStr">
+      <c r="AT1" s="5" t="inlineStr">
         <is>
           <t>competitor_nösenberger_gemini</t>
         </is>
       </c>
-      <c r="AU1" s="2" t="inlineStr">
+      <c r="AU1" s="5" t="inlineStr">
         <is>
           <t>competitor_nösenberger_ai_overview</t>
         </is>
       </c>
-      <c r="AV1" s="2" t="inlineStr">
+      <c r="AV1" s="5" t="inlineStr">
         <is>
           <t>competitor_st__hippolyt_chatgpt</t>
         </is>
       </c>
-      <c r="AW1" s="2" t="inlineStr">
+      <c r="AW1" s="5" t="inlineStr">
         <is>
           <t>competitor_st__hippolyt_gemini</t>
         </is>
       </c>
-      <c r="AX1" s="2" t="inlineStr">
+      <c r="AX1" s="5" t="inlineStr">
         <is>
           <t>competitor_st__hippolyt_ai_overview</t>
         </is>
       </c>
-      <c r="AY1" s="2" t="inlineStr">
+      <c r="AY1" s="5" t="inlineStr">
         <is>
           <t>top_competitors</t>
         </is>
       </c>
-      <c r="AZ1" s="2" t="inlineStr">
+      <c r="AZ1" s="5" t="inlineStr">
         <is>
           <t>gap_urls_top3</t>
         </is>
@@ -1098,11 +1321,7 @@
         <v>0</v>
       </c>
       <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>https://facebook.com/MarstallPferdefutter/videos/-empfindlicher-magen-nerv%C3%B6ses-pferd-unser-gastro-m%C3%BCsli-bietet-die-perfekte-f%C3%BCtte/938385081784838 | https://amazon.de/-/en/Stomach-Kit-1-5-Irritation-Grain-Free/dp/B09BZM2HL8 | https://amazon.de/-/en/Gastric-Supplement-Irritation-Bufferes-Pellets/dp/B07X4WZ72K</t>
-        </is>
-      </c>
+      <c r="AZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1418,11 +1637,7 @@
         <v>0</v>
       </c>
       <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>https://hipposport.de/Pferdefutter-Ergaenzungsfutter-Sehnen-Gelenke</t>
-        </is>
-      </c>
+      <c r="AZ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1738,11 +1953,7 @@
         <v>0.33</v>
       </c>
       <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>https://pavo-futter.de/beratung/futterung-von-nervosen-dunnen-pferden | https://hipposport.de/Pferdefutter-Ergaenzungsfutter-Nervositaet | https://st-hippolyt.de/wissen/wissenwertes/fuetterungstipps-fuer-starke-nerven-beim-pferd</t>
-        </is>
-      </c>
+      <c r="AZ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1900,11 +2111,7 @@
         <v>0</v>
       </c>
       <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>https://pferde-heilkunde.com/2025/08/06/zusatzfutter-gelenke-pferd-test</t>
-        </is>
-      </c>
+      <c r="AZ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2062,11 +2269,7 @@
         <v>0</v>
       </c>
       <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>https://pferdefuttershop.de/Spezialfutter/Zur-Unterstuetzung/Hufrehe | https://reiter-pferde.de/den-muskelaufbau-foerdern | https://tierarzt24.de/pferd-ergaenzungsfutter-gelenke</t>
-        </is>
-      </c>
+      <c r="AZ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2382,11 +2585,7 @@
         <v>0</v>
       </c>
       <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>https://stallbedarf24.de/st.hippolyt-ricelein-pellets</t>
-        </is>
-      </c>
+      <c r="AZ10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2548,11 +2747,7 @@
         <v>0</v>
       </c>
       <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>https://pavo-futter.de/beratung/die-10-wichtigsten-inhaltsstoffe-im-erganzungsfutter-fur-pferde | https://cavallo.de/medizin/welches-mineralfutter-fuer-welches-pferd | https://pferdefutter.de/de/zusatzfutter-supplemente</t>
-        </is>
-      </c>
+      <c r="AZ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2880,11 +3075,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>https://pferdefuttershop.de/Pferdefutter/Misch-Ergaenzungsfutter/Pellets | https://hipposport.de/Pferdefutter-Ergaenzungsfutter-Sehnen-Gelenke</t>
-        </is>
-      </c>
+      <c r="AZ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3050,11 +3241,7 @@
           <t>Marstall (100%), St. Hippolyt (100%), Pavo (67%), Eggersmann (33%), Höveler (33%)</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>https://pferdefutter.de | https://pferdefuttershop.de/Marken | https://pavo-futter.de</t>
-        </is>
-      </c>
+      <c r="AZ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3382,11 +3569,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>https://pavo-futter.de/glucosamine-wenn-gelenke-und-sehnen-bei-pferden-probleme-machen</t>
-        </is>
-      </c>
+      <c r="AZ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3552,11 +3735,7 @@
           <t>St. Hippolyt (67%), Havens (33%), Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>https://havenspferdefutter.at | https://lawau.at/en/products/agrobs-alpengrun-musli-getreidefrei-15kg | https://amazon.de/mypferdefutter-Gr%C3%BCnhafer-Cobs-ohne-Zus%C3%A4tze/dp/B09XLD4D34</t>
-        </is>
-      </c>
+      <c r="AZ17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3722,11 +3901,7 @@
           <t>St. Hippolyt (67%), Pavo (33%)</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>https://hipposport.de/Pferdefutter-Ergaenzungsfutter-Huf | https://ipet.ch/apotheke/pferde/hufpflege | https://reitsport.ch/pferdefutter/ergaenzungsfutter/haare-hufe-haut</t>
-        </is>
-      </c>
+      <c r="AZ18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3888,11 +4063,7 @@
         <v>0</v>
       </c>
       <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>https://hipposport.de/Pferdefutter-Ergaenzungsfutter-Huf | https://pavo-futter.de/beratung/die-10-wichtigsten-inhaltsstoffe-im-erganzungsfutter-fur-pferde | https://hipposport.de/Pferdefutter-Mineralfutter</t>
-        </is>
-      </c>
+      <c r="AZ19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4224,11 +4395,7 @@
           <t>Marstall (67%), Eggersmann (67%), Höveler (67%), St. Hippolyt (67%)</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>https://idealo.de/preisvergleich/ProductCategory/25956.html | https://kaaloon.de/futtermittel-fuer-pferde | https://idealo.de/preisvergleich/ProductCategory/25956F106980893.html</t>
-        </is>
-      </c>
+      <c r="AZ21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4394,11 +4561,7 @@
           <t>Höveler (100%), Eggersmann (33%)</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>https://stallbedarf24.de/st.hippolyt-ricelein-pellets</t>
-        </is>
-      </c>
+      <c r="AZ22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4560,11 +4723,7 @@
         <v>0</v>
       </c>
       <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>https://pavo-futter.de/beratung/wie-erganzungsfutter-die-pferdegesundheit-unterstutzen-kann | https://pferdekumpel.de/ernaehrung/zusatzfutter-fuer-die-hufe-von-pferden | https://ehorses.de/magazin/produkttest/unsere-tester-berichten-pavo-biotinforte-fuer-starke-hufe-gesundes-fell</t>
-        </is>
-      </c>
+      <c r="AZ23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4896,11 +5055,7 @@
           <t>Marstall (100%), Höveler (67%), St. Hippolyt (33%)</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>https://marstall.de/gastro/20kg | https://stroeh.de/shop/Pferdefutter/Misch-Ergaenzungsfuttermittel/Mash/DERBY-Gastro-Mash-12-5-kg-Sack | https://huebner-landmarkt.de/tierbedarf/pferdefutter</t>
-        </is>
-      </c>
+      <c r="AZ25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5718,11 +5873,7 @@
           <t>Marstall (100%), St. Hippolyt (100%), Pavo (67%), Höveler (67%), Nösenberger (33%)</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>https://reitsport.ch/pferdefutter/kraftfutter-raufutter/melassefrei | https://equusvitalis.ch/de-CH/futtermittel/getreidefrei | https://landi.swiss/de-CH/cooperative/landi-zola/content/pferdefutter-und-pferdekompetenz</t>
-        </is>
-      </c>
+      <c r="AZ30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5888,11 +6039,7 @@
           <t>Pavo (100%), St. Hippolyt (100%), Marstall (33%), Eggersmann (33%)</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>https://equidrome.com/pferd/pferdefutter-zusatzfutter/zusatzfutter | https://equusvitalis.de/zusatzfutter</t>
-        </is>
-      </c>
+      <c r="AZ31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6220,11 +6367,7 @@
         <v>0</v>
       </c>
       <c r="AY33" t="inlineStr"/>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>https://equitana.com/essen/de-de/blog/gesundheit/fuetterung-fuer-freizeitpferde.html | https://hipposport.de/Pferdefutter-Ergaenzungsfutter-Huf | https://pferdefuttershop.de/Spezialfutter/Zur-Unterstuetzung</t>
-        </is>
-      </c>
+      <c r="AZ33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6386,11 +6529,7 @@
         <v>0</v>
       </c>
       <c r="AY34" t="inlineStr"/>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>https://pavo-futter.de/beratung/die-10-wichtigsten-inhaltsstoffe-im-erganzungsfutter-fur-pferde | https://aut.pavo.net/beratung/rohstoffe-im-pferdefutter | https://pferdefuttershop.de/Pferdefutter/Eigenschaften/Proteinreich</t>
-        </is>
-      </c>
+      <c r="AZ34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6552,11 +6691,7 @@
         <v>0</v>
       </c>
       <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>https://equiva.com/ratgeber/pferdefuetterung/mineralfutter-und-ergaenzungsfutter</t>
-        </is>
-      </c>
+      <c r="AZ35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6722,11 +6857,7 @@
           <t>Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>https://pavo-futter.de/pferdefutter/allround/pavo-vital</t>
-        </is>
-      </c>
+      <c r="AZ36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6888,11 +7019,7 @@
         <v>0</v>
       </c>
       <c r="AY37" t="inlineStr"/>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>https://pferdefuttershop.de/Pferdefutter/Eigenschaften/Getreidefrei/Pellets | https://pferdefuttershop.de/Pferdefutter/Misch-Ergaenzungsfutter/Pellets | https://pferdhundkatz.com/fuer-pferde/st.-hippolyt</t>
-        </is>
-      </c>
+      <c r="AZ37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -7058,11 +7185,7 @@
           <t>Pavo (33%), Eggersmann (33%), Höveler (33%)</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>https://pavo-futter.de/beratung/die-10-wichtigsten-inhaltsstoffe-im-erganzungsfutter-fur-pferde | https://madbarn.com/feed-types/vitamin | https://dochorse.de/erganzungsfutter/pferde/mineralfutter.html</t>
-        </is>
-      </c>
+      <c r="AZ38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7394,11 +7517,7 @@
           <t>Pavo (67%), Marstall (67%), Höveler (67%), St. Hippolyt (67%)</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>https://amazon.de/Pferdefutter-50-100-EUR-Pferdebedarf/s?c=ts&amp;keywords=Pferdefutter&amp;rh=n%3A470840031%2Cp_36%3A450921031&amp;ts_id=470840031 | https://idealo.de/preisvergleich/ProductCategory/25956.html | https://pferdefuttershop.de/Pferdefutter/Eigenschaften/Bi.-Pferdefutter</t>
-        </is>
-      </c>
+      <c r="AZ40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7564,11 +7683,7 @@
           <t>Eggersmann (33%)</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>https://pavo-futter.de/beratung/energie-im-futter-fuer-freizeitpferde | https://pferdefuttershop.de/Pferdefutter/Getreide-Einzelfutter | https://pferdefuttershop.de/Spezialfutter/Zur-Unterstuetzung/Gelenke-Knochen-Sehnen</t>
-        </is>
-      </c>
+      <c r="AZ41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7896,11 +8011,7 @@
           <t>Marstall (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>https://equifarm.de/Marstall-Vito-Das-Getreidefreie-Muesli-Pferdefutter-20-Kg | https://reiter-guide.de/ratgeber/pferdefutter/zusatzfutter/pferdefutter-ohne-zucker | https://prima-tierfutter.de/ratgeber/futter/pferdefutter/pferdefutter-ohne-zucker-und-getreide</t>
-        </is>
-      </c>
+      <c r="AZ43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -8066,11 +8177,7 @@
           <t>Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>https://madbarn.com/feed-types/gut-supplement | https://pferdefuttershop.de/Spezialfutter/Zur-Unterstuetzung/Durchfall-Koliken-Kotwasser | https://noeltgen.de/lexa-gastro-akut-ergaenzungsfutter-fuer-magenempfindliche-pferde.html</t>
-        </is>
-      </c>
+      <c r="AZ44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -8398,11 +8505,7 @@
           <t>Pavo (100%), St. Hippolyt (100%), Marstall (67%)</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>https://equusvitalis.ch/de-CH/pavo/nervcontrol | https://reitsport.ch/pferdefutter/ergaenzungsfutter/stress-nervositaet | https://cavale-schweiz.ch/product?magnoflexal2=</t>
-        </is>
-      </c>
+      <c r="AZ46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -8568,11 +8671,7 @@
           <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Eggersmann (33%)</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>https://equiva.com/ratgeber/pferdefuetterung/mineralfutter-und-ergaenzungsfutter | https://pferdefuttershop.de/Pferdefutter/Mineralien-Supplemente/Elektrolyte | https://pavo-futter.de/beratung/die-10-wichtigsten-inhaltsstoffe-im-erganzungsfutter-fur-pferde</t>
-        </is>
-      </c>
+      <c r="AZ47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -8734,11 +8833,7 @@
         <v>0</v>
       </c>
       <c r="AY48" t="inlineStr"/>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>https://pferdefuttershop.de/Spezialfutter/Zur-Unterstuetzung/Magen-Darm | https://muehldorfer-pferdefutter.de/pferdefutter/magen</t>
-        </is>
-      </c>
+      <c r="AZ48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -9066,11 +9161,7 @@
           <t>Marstall (100%), Pavo (67%), St. Hippolyt (67%), Höveler (33%)</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>https://pferdy.de/bio-pferdefutter</t>
-        </is>
-      </c>
+      <c r="AZ50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -9236,18 +9327,14 @@
           <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Eggersmann (33%)</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>https://stallbedarf24.de/pferd/pferdefutter/zuckerfrei-zuckerreduziert | https://equifarm.de/Marstall-Force-Das-Mineralfutter-ohne-Getreide-Pferdefutter | https://pferdefuttershop.de/Pferdefutter/Eigenschaften/Low-Carb-zuckerreduziert</t>
-        </is>
-      </c>
+      <c r="AZ51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9269,52 +9356,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>prompt_id</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>prompt_text</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>topic</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>divergence_score</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>silence_type</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>visibility_chatgpt</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>visibility_gemini</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>visibility_ai_overview</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>top_competitors</t>
         </is>
@@ -9631,7 +9718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9653,52 +9740,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>prompt_id</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>prompt_text</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>topic</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>divergence_score</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>silence_type</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>visibility_chatgpt</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>visibility_gemini</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>visibility_ai_overview</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>top_competitors</t>
         </is>
@@ -10759,7 +10846,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10781,52 +10868,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>prompt_id</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>prompt_text</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>topic</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>divergence_score</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>silence_type</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>visibility_chatgpt</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>visibility_gemini</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>visibility_ai_overview</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>top_competitors</t>
         </is>
@@ -11445,7 +11532,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11468,57 +11555,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>prompt_id</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>prompt_text</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>total_retrieved</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>share_own</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>share_competitor</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>share_editorial</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>share_ugc</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>share_reference</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>share_institutional</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>share_corporate</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>share_other</t>
         </is>

--- a/public/downloads/drift_radar.xlsx
+++ b/public/downloads/drift_radar.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Wide-format max-visibility per competitor (one column per tracked competitor). For pivot work, consider the long-format helper drift_radar.csv or drift_radar.json.</t>
+          <t>Wide-format max-visibility per competitor (one column per tracked competitor). For pivot work, see the long-format companion file drift_radar_competitors_long.csv – one row per (prompt × competitor × engine).</t>
         </is>
       </c>
     </row>
@@ -9330,6 +9330,18 @@
       <c r="AZ51" t="inlineStr"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E2:E51">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.3"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="00F4F4F2"/>
+        <color rgb="00F4D9A8"/>
+        <color rgb="00CC7A00"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9714,6 +9726,18 @@
       <c r="J10" t="inlineStr"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E2:E10">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.3"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="00F4F4F2"/>
+        <color rgb="00F4D9A8"/>
+        <color rgb="00CC7A00"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10842,6 +10866,18 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E2:E26">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.3"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="00F4F4F2"/>
+        <color rgb="00F4D9A8"/>
+        <color rgb="00CC7A00"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11528,6 +11564,18 @@
       <c r="J17" t="inlineStr"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E2:E17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="0.3"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="00F4F4F2"/>
+        <color rgb="00F4D9A8"/>
+        <color rgb="00CC7A00"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/public/downloads/drift_radar.xlsx
+++ b/public/downloads/drift_radar.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All prompts" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drifting" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Own-only silence" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full silence" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source mix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Read me" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="All prompts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Drifting" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Own-only silence" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Full silence" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Source mix" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/public/downloads/drift_radar.xlsx
+++ b/public/downloads/drift_radar.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-20 → 2026-04-22</t>
+          <t>2026-04-24 → 2026-04-26</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41 / 50  (82 %)</t>
+          <t>42 / 50  (84 %)</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -561,7 +561,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4.0 %</t>
+          <t>3.3 %</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.7 %</t>
+          <t>2.0 %</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8.0 %</t>
+          <t>3.3 %</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3.3 %</t>
+          <t>4.7 %</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12.1×</t>
+          <t>2.3×</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1228,7 +1228,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U2" t="n">
         <v>0.4385</v>
@@ -1237,25 +1237,25 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -1264,25 +1264,25 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
@@ -1326,74 +1326,74 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.912</v>
+        <v>0.841</v>
       </c>
       <c r="F3" t="n">
-        <v>1.414</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.333</v>
+        <v>0.443</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="N3" t="n">
+        <v>0.7923</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
         <v>0.5615</v>
       </c>
-      <c r="O3" t="n">
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="P3" t="n">
+      <c r="T3" t="n">
         <v>3</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="U3" t="n">
         <v>0.4385</v>
       </c>
-      <c r="R3" t="n">
+      <c r="V3" t="n">
         <v>1</v>
       </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
@@ -1401,10 +1401,10 @@
         <v>0.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -1428,25 +1428,25 @@
         <v>0.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1470,10 +1470,10 @@
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
@@ -1484,157 +1484,157 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.681</v>
+        <v>0.592</v>
       </c>
       <c r="F4" t="n">
-        <v>1.414</v>
+        <v>0.821</v>
       </c>
       <c r="G4" t="n">
         <v>0.67</v>
       </c>
       <c r="H4" t="n">
-        <v>0.223</v>
+        <v>0.333</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.2077</v>
       </c>
       <c r="N4" t="n">
+        <v>0.9385</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
         <v>0.5615</v>
       </c>
-      <c r="O4" t="n">
+      <c r="S4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.0615</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.7923</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
         <v>0.67</v>
       </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.2077</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.9385</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.5615</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
       <c r="AW4" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr"/>
@@ -1642,33 +1642,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0.681</v>
+        <v>0.443</v>
       </c>
       <c r="F5" t="n">
         <v>1.414</v>
       </c>
       <c r="G5" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="H5" t="n">
-        <v>0.223</v>
+        <v>0.11</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -1687,16 +1687,16 @@
         <v>0.5615</v>
       </c>
       <c r="O5" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2077</v>
+        <v>0.0615</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9385</v>
+        <v>0.7923</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1714,10 +1714,10 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1741,10 +1741,10 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1753,7 +1753,7 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -1800,33 +1800,33 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.681</v>
+        <v>0.443</v>
       </c>
       <c r="F6" t="n">
         <v>1.414</v>
       </c>
       <c r="G6" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="H6" t="n">
-        <v>0.223</v>
+        <v>0.11</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -1845,28 +1845,28 @@
         <v>0.5615</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="S6" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2077</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9385</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1875,19 +1875,19 @@
         <v>0.67</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1899,34 +1899,34 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
         <v>0.67</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ6" t="n">
         <v>0</v>
@@ -1947,10 +1947,10 @@
         <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr"/>
@@ -1958,12 +1958,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1972,19 +1972,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0.681</v>
+        <v>0.443</v>
       </c>
       <c r="F7" t="n">
         <v>1.414</v>
       </c>
       <c r="G7" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="H7" t="n">
-        <v>0.223</v>
+        <v>0.11</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -2003,16 +2003,16 @@
         <v>0.5615</v>
       </c>
       <c r="O7" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2077</v>
+        <v>0.0615</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9385</v>
+        <v>0.7923</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0.33</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -2060,13 +2060,13 @@
         <v>0.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -2102,10 +2102,10 @@
         <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
@@ -2116,17 +2116,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -2164,7 +2164,7 @@
         <v>0.33</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
         <v>0.0615</v>
@@ -2182,13 +2182,13 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -2215,10 +2215,10 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2260,10 +2260,10 @@
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
@@ -2274,12 +2274,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2346,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y9" t="n">
         <v>0.33</v>
@@ -2376,7 +2376,7 @@
         <v>0.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
@@ -2432,61 +2432,65 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.707</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="I10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
       <c r="K10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7923</v>
+        <v>0.5615</v>
       </c>
       <c r="O10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7923</v>
+        <v>0.5615</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2504,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -2531,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -2590,17 +2594,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2623,7 +2627,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -2660,13 +2664,13 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -2693,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -2746,27 +2750,31 @@
       <c r="AX11" t="n">
         <v>0</v>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Pavo (33%)</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -2825,19 +2833,19 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X12" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y12" t="n">
         <v>0.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -2846,7 +2854,7 @@
         <v>0.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2855,25 +2863,25 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
@@ -2882,7 +2890,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ12" t="n">
         <v>0</v>
@@ -2900,7 +2908,7 @@
         <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW12" t="n">
         <v>0.33</v>
@@ -2910,7 +2918,7 @@
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (67%), Havens (33%), Marstall (33%), Eggersmann (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr"/>
@@ -2918,21 +2926,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -2951,7 +2959,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -2994,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -3009,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -3021,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -3066,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
@@ -3074,18 +3082,22 @@
       <c r="AX13" t="n">
         <v>0</v>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Pavo (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3094,7 +3106,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -3159,19 +3171,19 @@
         <v>0.67</v>
       </c>
       <c r="Y14" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -3183,28 +3195,28 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3213,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3228,17 +3240,17 @@
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Marstall (100%), St. Hippolyt (100%), Pavo (67%), Eggersmann (33%), Höveler (33%)</t>
+          <t>Pavo (67%), Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr"/>
@@ -3246,21 +3258,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -3316,28 +3328,28 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.6576</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="n">
         <v>0.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -3349,22 +3361,22 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
@@ -3379,7 +3391,7 @@
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3397,14 +3409,14 @@
         <v>0.33</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (100%), St. Hippolyt (100%), Pavo (100%), Höveler (67%), Eggersmann (33%)</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr"/>
@@ -3412,17 +3424,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -3445,7 +3457,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -3488,7 +3500,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -3521,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
@@ -3568,23 +3580,27 @@
       <c r="AX16" t="n">
         <v>0</v>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Pavo (33%)</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -3607,7 +3623,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -3644,16 +3660,16 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5615</v>
+        <v>0.6576</v>
       </c>
       <c r="W17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -3665,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -3674,10 +3690,10 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
@@ -3686,10 +3702,10 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3722,30 +3738,26 @@
         <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>St. Hippolyt (67%), Havens (33%), Pavo (33%), Marstall (33%)</t>
-        </is>
-      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3754,7 +3766,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -3773,7 +3785,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -3816,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>0</v>
@@ -3831,7 +3843,7 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3843,7 +3855,7 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
@@ -3888,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
@@ -3896,27 +3908,23 @@
       <c r="AX18" t="n">
         <v>0</v>
       </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>St. Hippolyt (67%), Pavo (33%)</t>
-        </is>
-      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -4068,21 +4076,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -4101,7 +4109,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -4138,7 +4146,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -4159,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -4219,32 +4227,28 @@
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -4267,7 +4271,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -4304,7 +4308,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6576</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
@@ -4313,19 +4317,19 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -4349,16 +4353,16 @@
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4367,7 +4371,7 @@
         <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -4382,35 +4386,31 @@
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
       </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Marstall (67%), Eggersmann (67%), Höveler (67%), St. Hippolyt (67%)</t>
-        </is>
-      </c>
+      <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -4470,7 +4470,7 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
@@ -4482,10 +4482,10 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -4524,7 +4524,7 @@
         <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4533,7 +4533,7 @@
         <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -4556,22 +4556,18 @@
       <c r="AX22" t="n">
         <v>0</v>
       </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Höveler (100%), Eggersmann (33%)</t>
-        </is>
-      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4599,7 +4595,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -4636,28 +4632,28 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5615</v>
+        <v>0.6576</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -4669,22 +4665,22 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AM23" t="n">
         <v>0</v>
@@ -4699,10 +4695,10 @@
         <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AS23" t="n">
         <v>0</v>
@@ -4711,29 +4707,33 @@
         <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AV23" t="n">
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Pavo (100%), Marstall (100%), St. Hippolyt (100%), Höveler (50%), Nösenberger (50%)</t>
+        </is>
+      </c>
       <c r="AZ23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4798,7 +4798,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -4807,19 +4807,19 @@
         <v>0.67</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -4843,10 +4843,10 @@
         <v>0.33</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AM24" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AS24" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AW24" t="n">
         <v>0.33</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>Pavo (67%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (100%), Pavo (67%), Höveler (67%), St. Hippolyt (67%)</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr"/>
@@ -4894,17 +4894,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -4973,19 +4973,19 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -5006,13 +5006,13 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
         <v>0</v>
@@ -5024,10 +5024,10 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
         <v>0</v>
@@ -5042,39 +5042,35 @@
         <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
         <v>0</v>
       </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Marstall (100%), Höveler (67%), St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -5130,7 +5126,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -5222,21 +5218,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -5255,7 +5251,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -5298,7 +5294,7 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -5331,7 +5327,7 @@
         <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AJ27" t="n">
         <v>0</v>
@@ -5378,23 +5374,27 @@
       <c r="AX27" t="n">
         <v>0</v>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Pavo (67%)</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -5454,16 +5454,16 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>0.6576</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -5487,10 +5487,10 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -5499,7 +5499,7 @@
         <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5540,27 +5540,23 @@
       <c r="AX28" t="n">
         <v>0</v>
       </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Marstall (67%), Pavo (33%)</t>
-        </is>
-      </c>
+      <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -5583,7 +5579,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -5629,7 +5625,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -5665,7 +5661,7 @@
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5706,23 +5702,27 @@
       <c r="AX29" t="n">
         <v>0</v>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Marstall (67%)</t>
+        </is>
+      </c>
       <c r="AZ29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -5788,22 +5788,22 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -5815,22 +5815,22 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AM30" t="n">
         <v>0</v>
@@ -5845,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
         <v>0</v>
@@ -5857,20 +5857,20 @@
         <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
         <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>Marstall (100%), St. Hippolyt (100%), Pavo (67%), Höveler (67%), Nösenberger (33%)</t>
+          <t>Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr"/>
@@ -5878,17 +5878,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -5954,13 +5954,13 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -5969,7 +5969,7 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -5981,7 +5981,7 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
@@ -5990,10 +5990,10 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -6002,7 +6002,7 @@
         <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6026,17 +6026,17 @@
         <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
         <v>0</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>Pavo (100%), St. Hippolyt (100%), Marstall (33%), Eggersmann (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr"/>
@@ -6044,12 +6044,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -6135,28 +6135,28 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK32" t="n">
         <v>0</v>
@@ -6192,7 +6192,7 @@
         <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW32" t="n">
         <v>0</v>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>Havens (100%), Pavo (100%)</t>
+          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr"/>
@@ -6210,17 +6210,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -6280,13 +6280,13 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0.5615</v>
+        <v>0.7935</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -6295,13 +6295,13 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -6313,7 +6313,7 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH33" t="n">
         <v>0</v>
@@ -6340,7 +6340,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ33" t="n">
         <v>0</v>
@@ -6361,28 +6361,32 @@
         <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX33" t="n">
         <v>0</v>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Pavo (33%), Höveler (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -6405,7 +6409,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -6451,19 +6455,19 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -6484,28 +6488,28 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AR34" t="n">
         <v>0</v>
@@ -6520,7 +6524,7 @@
         <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW34" t="n">
         <v>0</v>
@@ -6528,23 +6532,27 @@
       <c r="AX34" t="n">
         <v>0</v>
       </c>
-      <c r="AY34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Marstall (100%), Eggersmann (67%), Höveler (67%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -6567,7 +6575,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -6610,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -6637,7 +6645,7 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH35" t="n">
         <v>0</v>
@@ -6690,18 +6698,22 @@
       <c r="AX35" t="n">
         <v>0</v>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Pavo (67%)</t>
+        </is>
+      </c>
       <c r="AZ35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6766,16 +6778,16 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
         <v>0.33</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Z36" t="n">
         <v>0</v>
@@ -6787,7 +6799,7 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -6796,13 +6808,13 @@
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG36" t="n">
         <v>0.33</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -6811,7 +6823,7 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6844,17 +6856,17 @@
         <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX36" t="n">
         <v>0</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Havens (100%), Marstall (67%), St. Hippolyt (67%), Pavo (33%)</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr"/>
@@ -6862,21 +6874,21 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -6932,7 +6944,7 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0.5615</v>
+        <v>0.6576</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
@@ -7024,12 +7036,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -7038,7 +7050,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -7057,7 +7069,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -7100,16 +7112,16 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
@@ -7127,10 +7139,10 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -7148,7 +7160,7 @@
         <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -7157,7 +7169,7 @@
         <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
         <v>0</v>
@@ -7180,31 +7192,27 @@
       <c r="AX38" t="n">
         <v>0</v>
       </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Pavo (33%), Eggersmann (33%), Höveler (33%)</t>
-        </is>
-      </c>
+      <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -7269,7 +7277,7 @@
         <v>0.67</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -7281,7 +7289,7 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -7296,16 +7304,16 @@
         <v>0.67</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -7338,17 +7346,17 @@
         <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AX39" t="n">
         <v>0</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Marstall (33%)</t>
+          <t>Pavo (67%), St. Hippolyt (67%)</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr"/>
@@ -7356,17 +7364,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -7432,22 +7440,22 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -7459,7 +7467,7 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AH40" t="n">
         <v>0</v>
@@ -7468,10 +7476,10 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7489,7 +7497,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AR40" t="n">
         <v>0</v>
@@ -7504,17 +7512,17 @@
         <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
         <v>0</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>Pavo (67%), Marstall (67%), Höveler (67%), St. Hippolyt (67%)</t>
+          <t>Pavo (33%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr"/>
@@ -7522,17 +7530,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -7555,7 +7563,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -7592,7 +7600,7 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -7604,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7649,7 +7657,7 @@
         <v>0</v>
       </c>
       <c r="AO41" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP41" t="n">
         <v>0</v>
@@ -7678,27 +7686,23 @@
       <c r="AX41" t="n">
         <v>0</v>
       </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Eggersmann (33%)</t>
-        </is>
-      </c>
+      <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -7721,7 +7725,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -7758,13 +7762,13 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -7779,7 +7783,7 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -7791,7 +7795,7 @@
         <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH42" t="n">
         <v>0</v>
@@ -7836,7 +7840,7 @@
         <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW42" t="n">
         <v>0</v>
@@ -7844,23 +7848,27 @@
       <c r="AX42" t="n">
         <v>0</v>
       </c>
-      <c r="AY42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Pavo (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -7923,16 +7931,16 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7941,28 +7949,28 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
         <v>0</v>
@@ -7974,7 +7982,7 @@
         <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8001,14 +8009,14 @@
         <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX43" t="n">
         <v>0</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>Marstall (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (100%), Havens (33%)</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr"/>
@@ -8016,21 +8024,21 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -8086,28 +8094,28 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -8122,7 +8130,7 @@
         <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -8131,7 +8139,7 @@
         <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -8152,7 +8160,7 @@
         <v>0</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AS44" t="n">
         <v>0</v>
@@ -8167,14 +8175,14 @@
         <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX44" t="n">
         <v>0</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>Marstall (33%), Höveler (33%)</t>
+          <t>Pavo (67%), St. Hippolyt (67%)</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr"/>
@@ -8182,17 +8190,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -8252,7 +8260,7 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
@@ -8344,12 +8352,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -8414,20 +8422,20 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="Y46" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z46" t="n">
         <v>0.67</v>
       </c>
-      <c r="Z46" t="n">
-        <v>0</v>
-      </c>
       <c r="AA46" t="n">
         <v>0</v>
       </c>
@@ -8435,7 +8443,7 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -8447,29 +8455,29 @@
         <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK46" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="n">
         <v>0.67</v>
       </c>
-      <c r="AL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>0</v>
-      </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
@@ -8495,14 +8503,14 @@
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AX46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>Pavo (100%), St. Hippolyt (100%), Marstall (67%)</t>
+          <t>Pavo (67%), Eggersmann (67%), St. Hippolyt (67%), Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr"/>
@@ -8510,21 +8518,21 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -8543,7 +8551,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -8586,13 +8594,13 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -8601,7 +8609,7 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -8613,19 +8621,19 @@
         <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8634,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -8658,30 +8666,26 @@
         <v>0</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX47" t="n">
         <v>0</v>
       </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Eggersmann (33%)</t>
-        </is>
-      </c>
+      <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -8709,7 +8713,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -8755,19 +8759,19 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -8791,7 +8795,7 @@
         <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8800,16 +8804,16 @@
         <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR48" t="n">
         <v>0</v>
@@ -8827,32 +8831,36 @@
         <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX48" t="n">
         <v>0</v>
       </c>
-      <c r="AY48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Eggersmann (100%), Höveler (100%), St. Hippolyt (67%), Marstall (33%)</t>
+        </is>
+      </c>
       <c r="AZ48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -8871,7 +8879,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -8908,31 +8916,31 @@
         <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>0.6576</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB49" t="n">
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -8941,7 +8949,7 @@
         <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH49" t="n">
         <v>0</v>
@@ -8950,10 +8958,10 @@
         <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8971,7 +8979,7 @@
         <v>0</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR49" t="n">
         <v>0</v>
@@ -8986,35 +8994,39 @@
         <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX49" t="n">
         <v>0</v>
       </c>
-      <c r="AY49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>St. Hippolyt (100%), Havens (33%), Pavo (33%), Marstall (33%), Höveler (33%)</t>
+        </is>
+      </c>
       <c r="AZ49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -9076,22 +9088,22 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Y50" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -9103,7 +9115,7 @@
         <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AH50" t="n">
         <v>0</v>
@@ -9115,7 +9127,7 @@
         <v>0.33</v>
       </c>
       <c r="AK50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -9130,7 +9142,7 @@
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ50" t="n">
         <v>0</v>
@@ -9148,17 +9160,17 @@
         <v>0</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX50" t="n">
         <v>0</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>Marstall (100%), Pavo (67%), St. Hippolyt (67%), Höveler (33%)</t>
+          <t>Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr"/>
@@ -9166,12 +9178,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -9242,43 +9254,43 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB51" t="n">
         <v>0</v>
       </c>
       <c r="AC51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
         <v>0.67</v>
       </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AH51" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AK51" t="n">
         <v>0.33</v>
@@ -9287,19 +9299,19 @@
         <v>0</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN51" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR51" t="n">
         <v>0</v>
@@ -9314,17 +9326,17 @@
         <v>0</v>
       </c>
       <c r="AV51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW51" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AX51" t="n">
         <v>0</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Eggersmann (33%)</t>
+          <t>Pavo (100%), St. Hippolyt (100%), Marstall (67%), Eggersmann (67%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr"/>
@@ -9352,7 +9364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9422,12 +9434,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -9456,99 +9468,99 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.912</v>
+        <v>0.841</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
       </c>
       <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.681</v>
+        <v>0.592</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H4" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0.681</v>
+        <v>0.443</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9558,46 +9570,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.681</v>
+        <v>0.443</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I6" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -9606,17 +9618,17 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0.681</v>
+        <v>0.443</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9626,17 +9638,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -9660,12 +9672,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -9691,42 +9703,8 @@
       </c>
       <c r="J9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Gelenkunterstützung für Pferde</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E10">
+  <conditionalFormatting sqref="E2:E9">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -9748,7 +9726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9818,12 +9796,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -9832,7 +9810,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -9853,28 +9831,28 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -9895,24 +9873,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Marstall (100%), St. Hippolyt (100%), Pavo (67%), Eggersmann (33%), Höveler (33%)</t>
+          <t>Pavo (67%), Havens (33%), Marstall (33%), Eggersmann (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -9937,19 +9915,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9979,19 +9957,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>St. Hippolyt (67%), Havens (33%), Pavo (33%), Marstall (33%)</t>
+          <t>Pavo (67%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -10000,7 +9978,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -10021,28 +9999,28 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>St. Hippolyt (67%), Pavo (33%)</t>
+          <t>Marstall (100%), St. Hippolyt (100%), Pavo (100%), Höveler (67%), Eggersmann (33%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -10063,28 +10041,28 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>St. Hippolyt (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -10105,19 +10083,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Marstall (67%), Eggersmann (67%), Höveler (67%), St. Hippolyt (67%)</t>
+          <t>Pavo (100%), Marstall (100%), St. Hippolyt (100%), Höveler (50%), Nösenberger (50%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -10147,28 +10125,28 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Höveler (100%), Eggersmann (33%)</t>
+          <t>Marstall (100%), Pavo (67%), Höveler (67%), St. Hippolyt (67%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -10189,24 +10167,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Pavo (67%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (67%)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -10231,28 +10209,28 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Marstall (100%), Höveler (67%), St. Hippolyt (33%)</t>
+          <t>Marstall (67%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -10273,28 +10251,28 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Marstall (67%), Pavo (33%)</t>
+          <t>Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10315,24 +10293,24 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Marstall (100%), St. Hippolyt (100%), Pavo (67%), Höveler (67%), Nösenberger (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -10357,24 +10335,24 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Pavo (100%), St. Hippolyt (100%), Marstall (33%), Eggersmann (33%)</t>
+          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -10399,24 +10377,24 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Havens (100%), Pavo (100%)</t>
+          <t>Pavo (33%), Höveler (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -10441,28 +10419,28 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (100%), Eggersmann (67%), Höveler (67%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -10483,24 +10461,24 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Pavo (33%), Eggersmann (33%), Höveler (33%)</t>
+          <t>Pavo (67%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -10525,28 +10503,28 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Marstall (33%)</t>
+          <t>Havens (100%), Marstall (67%), St. Hippolyt (67%), Pavo (33%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -10567,24 +10545,24 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Pavo (67%), Marstall (67%), Höveler (67%), St. Hippolyt (67%)</t>
+          <t>Pavo (67%), St. Hippolyt (67%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -10609,24 +10587,24 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Eggersmann (33%)</t>
+          <t>Pavo (33%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -10651,24 +10629,24 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Marstall (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -10693,28 +10671,28 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Marstall (33%), Höveler (33%)</t>
+          <t>Pavo (100%), Havens (33%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10735,24 +10713,24 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Pavo (100%), St. Hippolyt (100%), Marstall (67%)</t>
+          <t>Pavo (67%), St. Hippolyt (67%)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -10777,24 +10755,24 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Eggersmann (33%)</t>
+          <t>Pavo (67%), Eggersmann (67%), St. Hippolyt (67%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -10819,24 +10797,24 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Marstall (100%), Pavo (67%), St. Hippolyt (67%), Höveler (33%)</t>
+          <t>Eggersmann (100%), Höveler (100%), St. Hippolyt (67%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -10861,12 +10839,96 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Eggersmann (33%)</t>
+          <t>St. Hippolyt (100%), Havens (33%), Pavo (33%), Marstall (33%), Höveler (33%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Pferde Vitamine und Mineralstoffe</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>own_only</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Pavo (33%), Marstall (33%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Pferde Vitamine und Mineralstoffe</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>own_only</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Pavo (100%), St. Hippolyt (100%), Marstall (67%), Eggersmann (67%), Höveler (33%)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E26">
+  <conditionalFormatting sqref="E2:E28">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -10888,7 +10950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -10958,21 +11020,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -10996,21 +11058,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -11034,21 +11096,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -11072,17 +11134,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -11110,21 +11172,21 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -11148,21 +11210,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -11186,17 +11248,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -11224,17 +11286,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -11300,17 +11362,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -11338,21 +11400,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -11376,17 +11438,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -11414,12 +11476,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -11452,17 +11514,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -11490,21 +11552,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -11525,46 +11587,8 @@
       </c>
       <c r="J16" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Natürliche Pferdepflege</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E17">
+  <conditionalFormatting sqref="E2:E16">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -11662,94 +11686,94 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5.170000000000002</v>
+        <v>6.380000000000003</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.0172</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0213</v>
+        <v>0.0517</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.0345</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0638</v>
+        <v>0.0345</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.0172</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9149</v>
+        <v>0.8276</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.0172</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>5.830000000000002</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.0566</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.0377</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.0189</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.8679</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.0189</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.299999999999999</v>
+        <v>5.510000000000002</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -11758,33 +11782,33 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0333</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.0399</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8333</v>
+        <v>0.9002</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1333</v>
+        <v>0.0399</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -11818,55 +11842,55 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8.360000000000007</v>
+        <v>3.399999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0132</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0395</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0263</v>
+        <v>0.1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0395</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0395</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0132</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0789</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -11875,58 +11899,58 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6854</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2087</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6.050000000000006</v>
+        <v>1.53</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0182</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0182</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0182</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0182</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9273</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -11935,25 +11959,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>4.239999999999999</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.0401</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.0401</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -11965,7 +11989,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.9198</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -11974,16 +11998,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -12004,64 +12028,64 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5.720000000000002</v>
+        <v>6.729999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0192</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0769</v>
+        <v>0.0505</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0577</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.0743</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0192</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8269</v>
+        <v>0.8499</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.0253</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4.51</v>
+        <v>1.19</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -12082,64 +12106,64 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7428</v>
+        <v>0.8571</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2572</v>
+        <v>0.1429</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4.51</v>
+        <v>3.41</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0244</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0244</v>
+        <v>0.0968</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0244</v>
+        <v>0.129</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0488</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7561</v>
+        <v>0.7742</v>
       </c>
       <c r="K13" t="n">
-        <v>0.122</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4.839999999999999</v>
+        <v>5.610000000000004</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -12148,37 +12172,37 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1136</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0455</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0227</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.9216</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0455</v>
+        <v>0.0784</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3.560000000000001</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -12190,16 +12214,16 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.0702</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.0702</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.8596</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -12208,16 +12232,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4.179999999999999</v>
+        <v>5.829999999999999</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -12226,37 +12250,37 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0526</v>
+        <v>0.0755</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.0755</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0263</v>
+        <v>0.0377</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.0566</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7895</v>
+        <v>0.7547</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.17</v>
+        <v>1.86</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -12268,34 +12292,34 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0213</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.0645</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8085</v>
+        <v>0.871</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1702</v>
+        <v>0.0645</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.720000000000003</v>
+        <v>3.3</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -12304,76 +12328,76 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.0333</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.0667</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0192</v>
+        <v>0.1333</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8269</v>
+        <v>0.7667</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.609999999999999</v>
+        <v>7.039999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0196</v>
+        <v>0.0313</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.0313</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0392</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0392</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.098</v>
+        <v>0.1406</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7451</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0588</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>9.040000000000006</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -12382,37 +12406,37 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.0852</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.0608</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.0608</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.0608</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.6593</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.429999999999999</v>
+        <v>4.929999999999999</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -12421,214 +12445,214 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1011</v>
+        <v>0.0345</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.14</v>
+        <v>0.0345</v>
       </c>
       <c r="I21" t="n">
-        <v>0.14</v>
+        <v>0.0345</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5194</v>
+        <v>0.8276</v>
       </c>
       <c r="K21" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.7</v>
+        <v>9.460000000000008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.0116</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.0698</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.0349</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.0814</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>0.0349</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8</v>
+        <v>0.7326</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2</v>
+        <v>0.0349</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>11.33000000000001</v>
+        <v>3.950000000000001</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0097</v>
+        <v>0.0304</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0291</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0388</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0291</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0291</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.767</v>
+        <v>0.9392</v>
       </c>
       <c r="K23" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.0304</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>4.619999999999998</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>0.0476</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>0.0238</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.7857</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>0.07140000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7.700000000000007</v>
+        <v>6.49</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0429</v>
+        <v>0.0169</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0429</v>
+        <v>0.0678</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0429</v>
+        <v>0.0678</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0143</v>
+        <v>0.0678</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0286</v>
+        <v>0.0339</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7857</v>
+        <v>0.7288</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0429</v>
+        <v>0.0169</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>7.380000000000007</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>0.0149</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.0149</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.0447</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>0.0149</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.0745</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.836</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -12637,16 +12661,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3.19</v>
+        <v>9.680000000000009</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -12655,37 +12679,37 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.0114</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.0682</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0345</v>
+        <v>0.0341</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1724</v>
+        <v>0.0114</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7931</v>
+        <v>0.7955</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>0.0795</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>4.300000000000002</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -12694,19 +12718,19 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.0279</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.0279</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.0279</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.9163</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -12715,16 +12739,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -12745,7 +12769,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -12754,64 +12778,64 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5.720000000000003</v>
+        <v>6.160000000000006</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.0179</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0192</v>
+        <v>0.0357</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0385</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8653999999999999</v>
+        <v>0.9464</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -12823,25 +12847,25 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.5</v>
+        <v>0.8182</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4</v>
+        <v>0.09089999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -12862,142 +12886,142 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.9091</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.09089999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>11.79</v>
+        <v>2.670000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>0.009299999999999999</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0.009299999999999999</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.028</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0373</v>
+        <v>0.0524</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8321</v>
+        <v>0.8951</v>
       </c>
       <c r="K33" t="n">
-        <v>0.028</v>
+        <v>0.0524</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4.510000000000001</v>
+        <v>3.85</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0244</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0732</v>
+        <v>0.3143</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0244</v>
+        <v>0.0571</v>
       </c>
       <c r="H34" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0857</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0732</v>
+        <v>0.2</v>
       </c>
       <c r="J34" t="n">
-        <v>0.6098</v>
+        <v>0.2571</v>
       </c>
       <c r="K34" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0857</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.87</v>
+        <v>2.889999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>0.0588</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.0588</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.09089999999999999</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8182</v>
+        <v>0.8824</v>
       </c>
       <c r="K35" t="n">
-        <v>0.09089999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.53</v>
+        <v>3.52</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -13009,16 +13033,16 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.0313</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2222</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1111</v>
+        <v>0.0313</v>
       </c>
       <c r="J36" t="n">
-        <v>0.6667</v>
+        <v>0.9375</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -13027,16 +13051,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4.950000000000002</v>
+        <v>5.500000000000002</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -13045,37 +13069,37 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0222</v>
+        <v>0.1309</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0222</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>0.0673</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0667</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8667</v>
+        <v>0.7582</v>
       </c>
       <c r="K37" t="n">
-        <v>0.0222</v>
+        <v>0.0436</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8.949999999999998</v>
+        <v>1.53</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -13084,33 +13108,33 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0369</v>
+        <v>0.1111</v>
       </c>
       <c r="I38" t="n">
-        <v>0.076</v>
+        <v>0.1111</v>
       </c>
       <c r="J38" t="n">
-        <v>0.7542</v>
+        <v>0.6667</v>
       </c>
       <c r="K38" t="n">
-        <v>0.114</v>
+        <v>0.1111</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -13135,25 +13159,25 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="K39" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3.229999999999999</v>
+        <v>2.719999999999999</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -13162,10 +13186,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0526</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0526</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -13174,7 +13198,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8947000000000001</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -13183,16 +13207,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4.399999999999999</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -13201,37 +13225,37 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.675</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7.480000000000002</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -13240,43 +13264,43 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0735</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0147</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0147</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0588</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6618000000000001</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.1765</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2.04</v>
+        <v>3.559999999999999</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>0.0478</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -13285,70 +13309,70 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0833</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0.9167</v>
+        <v>0.8596</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>0.0927</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>8.580000000000007</v>
+        <v>1.53</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0256</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0128</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0385</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0513</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7949000000000001</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -13363,34 +13387,34 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>0.0217</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.913</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>0.06519999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3.959999999999999</v>
+        <v>1.53</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0278</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -13399,34 +13423,34 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0278</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0556</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0.7778</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0.1111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -13441,31 +13465,31 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.09089999999999999</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8182</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0.09089999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1.53</v>
+        <v>1.19</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -13474,37 +13498,37 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>0.2857</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1111</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.7778</v>
+        <v>0.5714</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1111</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2.169999999999999</v>
+        <v>3.699999999999999</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -13516,34 +13540,34 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0599</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0599</v>
+        <v>0.0459</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.8802</v>
+        <v>0.9081</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>0.0459</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.19</v>
+        <v>7.299999999999999</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -13552,61 +13576,61 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2857</v>
+        <v>0.0466</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>0.0233</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>0.0466</v>
       </c>
       <c r="J50" t="n">
-        <v>0.7143</v>
+        <v>0.8137</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>0.0699</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>7.459999999999998</v>
+        <v>1.7</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0228</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0228</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0228</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0228</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.8633</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0456</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/public/downloads/drift_radar.xlsx
+++ b/public/downloads/drift_radar.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-24 → 2026-04-26</t>
+          <t>2026-04-25 → 2026-04-27</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42 / 50  (84 %)</t>
+          <t>40 / 50  (80 %)</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -561,7 +561,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3.3 %</t>
+          <t>3.5 %</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2.0 %</t>
+          <t>2.7 %</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3.3 %</t>
+          <t>4.6 %</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4.7 %</t>
+          <t>3.3 %</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2.3×</t>
+          <t>1.7×</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1185,32 +1185,32 @@
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>0.912</v>
+        <v>0.841</v>
       </c>
       <c r="F2" t="n">
-        <v>1.414</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.333</v>
+        <v>0.443</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
         <v>0.4385</v>
@@ -1240,22 +1240,22 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y2" t="n">
         <v>0.67</v>
       </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -1270,22 +1270,22 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AL2" t="n">
         <v>0.67</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -1294,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
@@ -1326,12 +1326,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1343,32 +1343,32 @@
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.841</v>
+        <v>0.681</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.414</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="H3" t="n">
-        <v>0.443</v>
+        <v>0.223</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7923</v>
+        <v>0.5615</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1383,16 +1383,16 @@
         <v>0.5615</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4385</v>
+        <v>0.2077</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>0.9385</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -1401,10 +1401,10 @@
         <v>0.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -1425,13 +1425,13 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
@@ -1440,13 +1440,13 @@
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1470,10 +1470,10 @@
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
@@ -1501,16 +1501,16 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.592</v>
+        <v>0.681</v>
       </c>
       <c r="F4" t="n">
-        <v>0.821</v>
+        <v>1.414</v>
       </c>
       <c r="G4" t="n">
         <v>0.67</v>
       </c>
       <c r="H4" t="n">
-        <v>0.333</v>
+        <v>0.223</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         <v>0.67</v>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
         <v>0.2077</v>
@@ -1541,22 +1541,22 @@
         <v>0.5615</v>
       </c>
       <c r="S4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7923</v>
+        <v>0.5615</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y4" t="n">
         <v>0.33</v>
@@ -1583,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AH4" t="n">
         <v>0.33</v>
@@ -1595,10 +1595,10 @@
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AW4" t="n">
         <v>1</v>
@@ -1642,21 +1642,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>0.443</v>
@@ -1690,7 +1690,7 @@
         <v>0.33</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
         <v>0.0615</v>
@@ -1717,7 +1717,7 @@
         <v>0.33</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1753,7 +1753,7 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1786,10 +1786,10 @@
         <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
@@ -1800,17 +1800,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1872,47 +1872,47 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
         <v>0.67</v>
       </c>
-      <c r="Y6" t="n">
-        <v>0.33</v>
-      </c>
       <c r="Z6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
         <v>0.67</v>
       </c>
-      <c r="AA6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
@@ -1920,13 +1920,13 @@
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
         <v>0</v>
@@ -1947,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
@@ -1958,17 +1958,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -2057,7 +2057,7 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -2102,10 +2102,10 @@
         <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
@@ -2116,12 +2116,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0.443</v>
@@ -2164,7 +2164,7 @@
         <v>0.33</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
         <v>0.0615</v>
@@ -2182,10 +2182,10 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X8" t="n">
         <v>0.33</v>
@@ -2203,13 +2203,13 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -2218,7 +2218,7 @@
         <v>0.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2263,7 +2263,7 @@
         <v>0.33</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
@@ -2274,17 +2274,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -2346,10 +2346,10 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -2376,7 +2376,7 @@
         <v>0.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -2385,7 +2385,7 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2418,10 +2418,10 @@
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AW9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
@@ -2432,42 +2432,38 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.443</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1.414</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="I10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
         <v>0</v>
       </c>
@@ -2481,16 +2477,16 @@
         <v>0.5615</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2508,10 +2504,10 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -2523,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -2535,10 +2531,10 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -2547,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2580,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
@@ -2594,65 +2590,61 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.707</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>own_only</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2685,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2742,35 +2734,31 @@
         <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Pavo (33%)</t>
-        </is>
-      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -2793,7 +2781,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -2830,31 +2818,31 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2863,7 +2851,7 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
@@ -2872,7 +2860,7 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2881,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
@@ -2890,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
         <v>0</v>
@@ -2908,39 +2896,35 @@
         <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Pavo (67%), Havens (33%), Marstall (33%), Eggersmann (33%), Höveler (33%)</t>
-        </is>
-      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -2996,7 +2980,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -3005,10 +2989,10 @@
         <v>0.33</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -3017,7 +3001,7 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -3029,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -3041,7 +3025,7 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -3050,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3074,17 +3058,17 @@
         <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>Pavo (33%), St. Hippolyt (33%)</t>
+          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Eggersmann (33%)</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr"/>
@@ -3092,17 +3076,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -3125,7 +3109,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -3168,10 +3152,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -3195,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -3204,10 +3188,10 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3248,22 +3232,18 @@
       <c r="AX14" t="n">
         <v>0</v>
       </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Pavo (67%), Marstall (33%)</t>
-        </is>
-      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3272,7 +3252,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -3328,28 +3308,28 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6576</v>
+        <v>0.5615</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Y15" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -3361,28 +3341,28 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AL15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3391,7 +3371,7 @@
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3409,14 +3389,14 @@
         <v>0.33</v>
       </c>
       <c r="AW15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Marstall (100%), St. Hippolyt (100%), Pavo (100%), Höveler (67%), Eggersmann (33%)</t>
+          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr"/>
@@ -3424,12 +3404,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3500,22 +3480,22 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -3533,31 +3513,31 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -3572,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
@@ -3582,7 +3562,7 @@
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Marstall (100%), Eggersmann (67%), Höveler (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr"/>
@@ -3590,21 +3570,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -3623,7 +3603,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -3666,22 +3646,22 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -3693,22 +3673,22 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM17" t="n">
         <v>0</v>
@@ -3723,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -3732,41 +3712,45 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AU17" t="n">
         <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Marstall (100%), St. Hippolyt (100%), Pavo (100%), Höveler (33%), Nösenberger (33%)</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -3822,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5615</v>
+        <v>0.7935</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3914,12 +3898,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -4076,21 +4060,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -4109,7 +4093,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -4146,16 +4130,16 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -4167,7 +4151,7 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -4179,16 +4163,16 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -4227,32 +4211,36 @@
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%)</t>
+        </is>
+      </c>
       <c r="AZ20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -4271,7 +4259,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -4308,28 +4296,28 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.6576</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -4341,22 +4329,22 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM21" t="n">
         <v>0</v>
@@ -4371,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -4383,34 +4371,38 @@
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Marstall (100%), St. Hippolyt (100%), Pavo (100%), Nösenberger (50%), Höveler (33%)</t>
+        </is>
+      </c>
       <c r="AZ21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -4433,7 +4425,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -4470,28 +4462,28 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -4503,7 +4495,7 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH22" t="n">
         <v>0</v>
@@ -4512,7 +4504,7 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -4530,10 +4522,10 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -4551,32 +4543,36 @@
         <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX22" t="n">
         <v>0</v>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Pavo (33%), Marstall (33%), Höveler (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4632,28 +4628,28 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6576</v>
+        <v>0.5615</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Y23" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -4662,25 +4658,25 @@
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AG23" t="n">
         <v>0.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AI23" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
         <v>0.67</v>
       </c>
-      <c r="AK23" t="n">
-        <v>1</v>
-      </c>
       <c r="AL23" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
         <v>0</v>
@@ -4695,10 +4691,10 @@
         <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
         <v>0</v>
@@ -4707,20 +4703,20 @@
         <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>Pavo (100%), Marstall (100%), St. Hippolyt (100%), Höveler (50%), Nösenberger (50%)</t>
+          <t>Havens (67%), Marstall (67%), Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr"/>
@@ -4728,17 +4724,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -4798,55 +4794,55 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y24" t="n">
         <v>0.67</v>
       </c>
-      <c r="Y24" t="n">
-        <v>1</v>
-      </c>
       <c r="Z24" t="n">
         <v>0</v>
       </c>
       <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
         <v>0.67</v>
       </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1</v>
-      </c>
       <c r="AL24" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
         <v>0</v>
@@ -4861,10 +4857,10 @@
         <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
         <v>0</v>
@@ -4876,7 +4872,7 @@
         <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
         <v>0.33</v>
@@ -4886,7 +4882,7 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>Marstall (100%), Pavo (67%), Höveler (67%), St. Hippolyt (67%)</t>
+          <t>Marstall (67%), Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr"/>
@@ -4894,17 +4890,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -4927,7 +4923,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -4970,22 +4966,22 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -4997,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH25" t="n">
         <v>0</v>
@@ -5006,16 +5002,16 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN25" t="n">
         <v>0</v>
@@ -5024,10 +5020,10 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AR25" t="n">
         <v>0</v>
@@ -5042,31 +5038,35 @@
         <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX25" t="n">
         <v>0</v>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Marstall (100%), Höveler (67%), Pavo (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -5126,7 +5126,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0.5615</v>
+        <v>0.6576</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -5218,21 +5218,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -5288,28 +5288,28 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -5327,13 +5327,13 @@
         <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5342,16 +5342,16 @@
         <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR27" t="n">
         <v>0</v>
@@ -5369,14 +5369,14 @@
         <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX27" t="n">
         <v>0</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>Pavo (67%)</t>
+          <t>Eggersmann (100%), Höveler (100%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr"/>
@@ -5384,17 +5384,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -5454,7 +5454,7 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0.6576</v>
+        <v>0.5615</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -5546,12 +5546,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5622,22 +5622,22 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -5649,7 +5649,7 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH29" t="n">
         <v>0</v>
@@ -5658,10 +5658,10 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5670,13 +5670,13 @@
         <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ29" t="n">
         <v>0</v>
@@ -5697,14 +5697,14 @@
         <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX29" t="n">
         <v>0</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>Marstall (67%)</t>
+          <t>Pavo (100%), Eggersmann (100%), St. Hippolyt (100%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr"/>
@@ -5712,21 +5712,21 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -5782,16 +5782,16 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -5815,10 +5815,10 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -5830,7 +5830,7 @@
         <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>Marstall (33%)</t>
+          <t>Pavo (100%), Havens (33%)</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr"/>
@@ -5878,12 +5878,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -5954,7 +5954,7 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -5981,7 +5981,7 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
@@ -6034,11 +6034,7 @@
       <c r="AX31" t="n">
         <v>0</v>
       </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Pavo (33%)</t>
-        </is>
-      </c>
+      <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -6210,17 +6206,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -6280,7 +6276,7 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0.7935</v>
+        <v>0.5615</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -6295,13 +6291,13 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -6340,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
         <v>0</v>
@@ -6361,14 +6357,14 @@
         <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
         <v>0</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>Pavo (33%), Höveler (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr"/>
@@ -6376,17 +6372,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -6409,7 +6405,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -6446,7 +6442,7 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -6455,19 +6451,19 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -6488,28 +6484,28 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
         <v>0</v>
@@ -6524,7 +6520,7 @@
         <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
         <v>0</v>
@@ -6532,27 +6528,23 @@
       <c r="AX34" t="n">
         <v>0</v>
       </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Marstall (100%), Eggersmann (67%), Höveler (67%), St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -6575,7 +6567,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -6618,7 +6610,7 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -6645,7 +6637,7 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
         <v>0</v>
@@ -6698,31 +6690,27 @@
       <c r="AX35" t="n">
         <v>0</v>
       </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Pavo (67%)</t>
-        </is>
-      </c>
+      <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -6741,7 +6729,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -6778,16 +6766,16 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
         <v>0</v>
@@ -6799,7 +6787,7 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -6808,13 +6796,13 @@
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -6823,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6859,16 +6847,12 @@
         <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
         <v>0</v>
       </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Havens (100%), Marstall (67%), St. Hippolyt (67%), Pavo (33%)</t>
-        </is>
-      </c>
+      <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -7036,21 +7020,21 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -7069,7 +7053,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -7106,16 +7090,16 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -7127,7 +7111,7 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -7145,7 +7129,7 @@
         <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AJ38" t="n">
         <v>0</v>
@@ -7154,7 +7138,7 @@
         <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AM38" t="n">
         <v>0</v>
@@ -7187,23 +7171,27 @@
         <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX38" t="n">
         <v>0</v>
       </c>
-      <c r="AY38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Marstall (67%), Pavo (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -7212,7 +7200,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -7274,7 +7262,7 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -7289,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -7301,7 +7289,7 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AH39" t="n">
         <v>0</v>
@@ -7349,14 +7337,14 @@
         <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AX39" t="n">
         <v>0</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>Pavo (67%), St. Hippolyt (67%)</t>
+          <t>Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr"/>
@@ -7364,17 +7352,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -7397,7 +7385,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -7434,22 +7422,22 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
@@ -7467,7 +7455,7 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
         <v>0</v>
@@ -7476,7 +7464,7 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
         <v>0</v>
@@ -7494,10 +7482,10 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
         <v>0</v>
@@ -7520,31 +7508,27 @@
       <c r="AX40" t="n">
         <v>0</v>
       </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Pavo (33%), Marstall (33%), Höveler (33%)</t>
-        </is>
-      </c>
+      <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -7692,17 +7676,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -7783,7 +7767,7 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -7840,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
         <v>0</v>
@@ -7850,7 +7834,7 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr"/>
@@ -7858,17 +7842,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -7931,10 +7915,10 @@
         <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -7952,19 +7936,19 @@
         <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AH43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -8016,7 +8000,7 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>Pavo (100%), Havens (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr"/>
@@ -8024,17 +8008,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -8057,7 +8041,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -8094,13 +8078,13 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -8115,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -8130,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -8175,32 +8159,28 @@
         <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX44" t="n">
         <v>0</v>
       </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Pavo (67%), St. Hippolyt (67%)</t>
-        </is>
-      </c>
+      <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -8223,7 +8203,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -8260,31 +8240,31 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB45" t="n">
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -8293,7 +8273,7 @@
         <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH45" t="n">
         <v>0</v>
@@ -8302,7 +8282,7 @@
         <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK45" t="n">
         <v>0</v>
@@ -8311,7 +8291,7 @@
         <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN45" t="n">
         <v>0</v>
@@ -8320,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ45" t="n">
         <v>0</v>
@@ -8338,26 +8318,30 @@
         <v>0</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX45" t="n">
         <v>0</v>
       </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Pavo (67%), Havens (33%), Marstall (33%), Eggersmann (33%), Höveler (33%)</t>
+        </is>
+      </c>
       <c r="AZ45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -8366,7 +8350,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -8385,7 +8369,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -8428,13 +8412,13 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -8443,7 +8427,7 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -8458,16 +8442,16 @@
         <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -8476,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -8503,36 +8487,32 @@
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
         <v>0</v>
       </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Pavo (67%), Eggersmann (67%), St. Hippolyt (67%), Marstall (33%)</t>
-        </is>
-      </c>
+      <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -8551,7 +8531,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -8591,28 +8571,28 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB47" t="n">
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AE47" t="n">
         <v>0</v>
@@ -8621,7 +8601,7 @@
         <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH47" t="n">
         <v>0</v>
@@ -8630,10 +8610,10 @@
         <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8651,7 +8631,7 @@
         <v>0</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR47" t="n">
         <v>0</v>
@@ -8666,31 +8646,35 @@
         <v>0</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX47" t="n">
         <v>0</v>
       </c>
-      <c r="AY47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>St. Hippolyt (100%), Pavo (67%), Havens (33%), Marstall (33%), Höveler (33%)</t>
+        </is>
+      </c>
       <c r="AZ47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -8756,43 +8740,43 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="Z48" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
         <v>1</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
         <v>1</v>
       </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
+      <c r="AH48" t="n">
         <v>0.67</v>
       </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0</v>
-      </c>
       <c r="AI48" t="n">
         <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK48" t="n">
         <v>0.33</v>
@@ -8804,41 +8788,41 @@
         <v>0</v>
       </c>
       <c r="AN48" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW48" t="n">
         <v>1</v>
       </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AX48" t="n">
         <v>0</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>Eggersmann (100%), Höveler (100%), St. Hippolyt (67%), Marstall (33%)</t>
+          <t>Pavo (100%), Marstall (100%), St. Hippolyt (100%), Eggersmann (67%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr"/>
@@ -8846,17 +8830,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -8919,28 +8903,28 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
         <v>0</v>
@@ -8952,13 +8936,13 @@
         <v>0.33</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AK49" t="n">
         <v>0.33</v>
@@ -8970,7 +8954,7 @@
         <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -8979,7 +8963,7 @@
         <v>0</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR49" t="n">
         <v>0</v>
@@ -8994,17 +8978,17 @@
         <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AX49" t="n">
         <v>0</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Havens (33%), Pavo (33%), Marstall (33%), Höveler (33%)</t>
+          <t>Pavo (67%), Marstall (67%), Eggersmann (67%), St. Hippolyt (67%)</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr"/>
@@ -9012,12 +8996,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -9026,7 +9010,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -9045,7 +9029,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -9088,10 +9072,10 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -9115,7 +9099,7 @@
         <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
         <v>0</v>
@@ -9124,7 +9108,7 @@
         <v>0</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK50" t="n">
         <v>0</v>
@@ -9168,31 +9152,27 @@
       <c r="AX50" t="n">
         <v>0</v>
       </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>Pavo (33%), Marstall (33%)</t>
-        </is>
-      </c>
+      <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -9248,7 +9228,7 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>0.6576</v>
       </c>
       <c r="W51" t="n">
         <v>0</v>
@@ -9257,61 +9237,61 @@
         <v>1</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
         <v>0</v>
       </c>
       <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
         <v>1</v>
       </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ51" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN51" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR51" t="n">
         <v>0</v>
@@ -9326,17 +9306,17 @@
         <v>0</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX51" t="n">
         <v>0</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>Pavo (100%), St. Hippolyt (100%), Marstall (67%), Eggersmann (67%), Höveler (33%)</t>
+          <t>Pavo (100%)</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr"/>
@@ -9364,7 +9344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9434,12 +9414,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -9451,11 +9431,11 @@
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>0.912</v>
+        <v>0.841</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -9468,12 +9448,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -9485,17 +9465,17 @@
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.841</v>
+        <v>0.681</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="J3" t="inlineStr"/>
     </row>
@@ -9519,7 +9499,7 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.592</v>
+        <v>0.681</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
@@ -9529,28 +9509,28 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>0.443</v>
@@ -9570,17 +9550,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -9604,17 +9584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -9638,12 +9618,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -9652,7 +9632,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0.443</v>
@@ -9672,17 +9652,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -9703,8 +9683,76 @@
       </c>
       <c r="J9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Pferdefutter Ergänzungsmittel</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pferde Nahrungsergänzung</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E9">
+  <conditionalFormatting sqref="E2:E11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -9726,7 +9774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9796,12 +9844,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -9810,7 +9858,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -9831,24 +9879,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Eggersmann (33%)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -9873,19 +9921,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Pavo (67%), Havens (33%), Marstall (33%), Eggersmann (33%), Höveler (33%)</t>
+          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9915,19 +9963,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (100%), Eggersmann (67%), Höveler (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9936,7 +9984,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -9957,24 +10005,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Pavo (67%), Marstall (33%)</t>
+          <t>Marstall (100%), St. Hippolyt (100%), Pavo (100%), Höveler (33%), Nösenberger (33%)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -9999,28 +10047,28 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Marstall (100%), St. Hippolyt (100%), Pavo (100%), Höveler (67%), Eggersmann (33%)</t>
+          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -10041,28 +10089,28 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Marstall (100%), St. Hippolyt (100%), Pavo (100%), Nösenberger (50%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -10083,24 +10131,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pavo (100%), Marstall (100%), St. Hippolyt (100%), Höveler (50%), Nösenberger (50%)</t>
+          <t>Pavo (33%), Marstall (33%), Höveler (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -10125,28 +10173,28 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Marstall (100%), Pavo (67%), Höveler (67%), St. Hippolyt (67%)</t>
+          <t>Havens (67%), Marstall (67%), Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -10167,24 +10215,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Pavo (67%)</t>
+          <t>Marstall (67%), Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -10209,28 +10257,28 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Marstall (67%)</t>
+          <t>Marstall (100%), Höveler (67%), Pavo (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -10251,24 +10299,24 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Marstall (33%)</t>
+          <t>Eggersmann (100%), Höveler (100%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -10293,19 +10341,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Pavo (100%), Eggersmann (100%), St. Hippolyt (100%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -10335,24 +10383,24 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (100%), Havens (33%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -10377,24 +10425,24 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Pavo (33%), Höveler (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -10419,28 +10467,28 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Marstall (100%), Eggersmann (67%), Höveler (67%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -10461,24 +10509,24 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Pavo (67%)</t>
+          <t>Marstall (67%), Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -10503,28 +10551,28 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Havens (100%), Marstall (67%), St. Hippolyt (67%), Pavo (33%)</t>
+          <t>Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -10545,24 +10593,24 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Pavo (67%), St. Hippolyt (67%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -10587,24 +10635,24 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), Höveler (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -10629,24 +10677,24 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (67%), Havens (33%), Marstall (33%), Eggersmann (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -10671,28 +10719,28 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Pavo (100%), Havens (33%)</t>
+          <t>St. Hippolyt (100%), Pavo (67%), Havens (33%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10713,7 +10761,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Pavo (67%), St. Hippolyt (67%)</t>
+          <t>Pavo (100%), Marstall (100%), St. Hippolyt (100%), Eggersmann (67%), Höveler (33%)</t>
         </is>
       </c>
     </row>
@@ -10755,28 +10803,28 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Pavo (67%), Eggersmann (67%), St. Hippolyt (67%), Marstall (33%)</t>
+          <t>Pavo (67%), Marstall (67%), Eggersmann (67%), St. Hippolyt (67%)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -10797,138 +10845,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Eggersmann (100%), Höveler (100%), St. Hippolyt (67%), Marstall (33%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>own_only</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>St. Hippolyt (100%), Havens (33%), Pavo (33%), Marstall (33%), Höveler (33%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>3</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>own_only</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Pavo (33%), Marstall (33%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>own_only</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Pavo (100%), St. Hippolyt (100%), Marstall (67%), Eggersmann (67%), Höveler (33%)</t>
+          <t>Pavo (100%)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E28">
+  <conditionalFormatting sqref="E2:E25">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -10950,7 +10872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11020,21 +10942,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -11058,17 +10980,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -11096,21 +11018,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -11134,12 +11056,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -11172,17 +11094,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -11210,17 +11132,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -11248,17 +11170,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -11286,12 +11208,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -11324,17 +11246,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -11362,21 +11284,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -11438,17 +11360,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -11476,21 +11398,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -11514,21 +11436,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -11587,8 +11509,46 @@
       </c>
       <c r="J16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Pferde Vitamine und Mineralstoffe</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E16">
+  <conditionalFormatting sqref="E2:E17">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -11686,79 +11646,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6.380000000000003</v>
+        <v>10.14000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0172</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0517</v>
+        <v>0.0542</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0345</v>
+        <v>0.0108</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0345</v>
+        <v>0.0542</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0172</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8276</v>
+        <v>0.8481</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0172</v>
+        <v>0.0325</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5.830000000000002</v>
+        <v>6.710000000000005</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.0164</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0566</v>
+        <v>0.0492</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.0328</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0377</v>
+        <v>0.0492</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0189</v>
+        <v>0.0164</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8679</v>
+        <v>0.8033</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0189</v>
+        <v>0.0328</v>
       </c>
     </row>
     <row r="4">
@@ -11773,7 +11733,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.510000000000002</v>
+        <v>7.370000000000005</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -11782,37 +11742,37 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02</v>
+        <v>0.0597</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.0299</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.0149</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0399</v>
+        <v>0.0299</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9002</v>
+        <v>0.7612</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0399</v>
+        <v>0.1045</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -11821,19 +11781,19 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.0557</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.1115</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.8328</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -11842,28 +11802,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3.399999999999999</v>
+        <v>3.569999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.0476</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.0476</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -11872,25 +11832,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.85</v>
+        <v>0.9048</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>5.390000000000003</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -11905,31 +11865,31 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.0408</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.9184</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.0408</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.53</v>
+        <v>3.52</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -11938,10 +11898,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.1563</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -11950,7 +11910,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0.7187</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -11959,28 +11919,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4.239999999999999</v>
+        <v>3.229999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.0526</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0401</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0401</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.0526</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -11989,7 +11949,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9198</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -11998,25 +11958,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>4.239999999999999</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.0401</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.0401</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -12028,7 +11988,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.9198</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -12037,16 +11997,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6.729999999999999</v>
+        <v>3.23</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -12055,76 +12015,76 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0505</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0743</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8499</v>
+        <v>0.5263</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0253</v>
+        <v>0.4737</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.19</v>
+        <v>9.900000000000009</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.0111</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.0667</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.0444</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.0667</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.0556</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8571</v>
+        <v>0.7222</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1429</v>
+        <v>0.0333</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.41</v>
+        <v>1.53</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -12133,10 +12093,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0968</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.129</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -12145,7 +12105,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7742</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -12154,55 +12114,55 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5.610000000000004</v>
+        <v>9.680000000000003</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.0227</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.0114</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.0341</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.1705</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9216</v>
+        <v>0.4773</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0784</v>
+        <v>0.1932</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.560000000000001</v>
+        <v>7.070000000000004</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -12214,73 +12174,73 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0702</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0702</v>
+        <v>0.0156</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8596</v>
+        <v>0.9222</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.0622</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.829999999999999</v>
+        <v>7.04</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0755</v>
+        <v>0.25</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0755</v>
+        <v>0.0156</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0377</v>
+        <v>0.0625</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0566</v>
+        <v>0.125</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7547</v>
+        <v>0.4375</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.0781</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.86</v>
+        <v>3.710000000000001</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -12292,34 +12252,34 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.0674</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0645</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.0674</v>
       </c>
       <c r="J17" t="n">
-        <v>0.871</v>
+        <v>0.8652</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3.3</v>
+        <v>3.390000000000002</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -12328,19 +12288,19 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0333</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0667</v>
+        <v>0.0413</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1333</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7667</v>
+        <v>0.9587</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -12349,55 +12309,55 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7.039999999999999</v>
+        <v>8.160000000000011</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0313</v>
+        <v>0.0135</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0313</v>
+        <v>0.0135</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.0404</v>
       </c>
       <c r="H19" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.0135</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1406</v>
+        <v>0.0674</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.8517</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9.040000000000006</v>
+        <v>1.7</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -12406,121 +12366,121 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0852</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0608</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0608</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0608</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6593</v>
+        <v>0.9</v>
       </c>
       <c r="K20" t="n">
-        <v>0.073</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.929999999999999</v>
+        <v>5.930000000000001</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.0202</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0345</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0345</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0345</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8276</v>
+        <v>0.7926</v>
       </c>
       <c r="K21" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.1872</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>9.460000000000008</v>
+        <v>4.569999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0116</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0698</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0349</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0814</v>
+        <v>0.0372</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0349</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7326</v>
+        <v>0.8162</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0349</v>
+        <v>0.1466</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3.950000000000001</v>
+        <v>5.500000000000004</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0304</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -12529,148 +12489,148 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9392</v>
+        <v>0.9</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0304</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4.619999999999998</v>
+        <v>3.739999999999999</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>0.0455</v>
       </c>
       <c r="G24" t="n">
-        <v>0.07140000000000001</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0238</v>
+        <v>0.0455</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7857</v>
+        <v>0.8636</v>
       </c>
       <c r="K24" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0455</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6.49</v>
+        <v>6.930000000000005</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0169</v>
+        <v>0.0317</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0678</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0678</v>
+        <v>0.0635</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0678</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0339</v>
+        <v>0.0159</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7288</v>
+        <v>0.8254</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0169</v>
+        <v>0.0635</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7.380000000000007</v>
+        <v>1.71</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0149</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0149</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0447</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0149</v>
+        <v>0.0702</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0745</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.836</v>
+        <v>0.8596</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>0.0702</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9.680000000000009</v>
+        <v>1.19</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -12679,37 +12639,37 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0114</v>
+        <v>0.1429</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0682</v>
+        <v>0.2857</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0341</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0114</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7955</v>
+        <v>0.5714</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4.300000000000002</v>
+        <v>7.590000000000002</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -12718,37 +12678,37 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0279</v>
+        <v>0.1304</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0279</v>
+        <v>0.0435</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0279</v>
+        <v>0.058</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9163</v>
+        <v>0.6522</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.7</v>
+        <v>3.399999999999999</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -12757,7 +12717,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -12769,37 +12729,37 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6.160000000000006</v>
+        <v>3.559999999999999</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0179</v>
+        <v>0.0478</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0357</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -12808,31 +12768,31 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9464</v>
+        <v>0.8596</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>0.0927</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.09089999999999999</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -12847,10 +12807,10 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8182</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.09089999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -12895,16 +12855,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2.670000000000001</v>
+        <v>7.370000000000004</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -12913,37 +12873,37 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>0.0597</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.0597</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>0.0746</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0524</v>
+        <v>0.0448</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8951</v>
+        <v>0.7313</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0524</v>
+        <v>0.0299</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3.85</v>
+        <v>6.729999999999999</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -12952,76 +12912,76 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3143</v>
+        <v>0.0505</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0571</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0857</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2</v>
+        <v>0.0253</v>
       </c>
       <c r="J34" t="n">
-        <v>0.2571</v>
+        <v>0.8247</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2.889999999999999</v>
+        <v>6.089999999999998</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0588</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0588</v>
+        <v>0.0279</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>0.0279</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>0.0279</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8824</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>0.0558</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3.52</v>
+        <v>8.429999999999998</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -13030,22 +12990,22 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0313</v>
+        <v>0.0202</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>0.0391</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0313</v>
+        <v>0.0403</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9375</v>
+        <v>0.7794</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>0.0403</v>
       </c>
     </row>
     <row r="37">
@@ -13060,7 +13020,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5.500000000000002</v>
+        <v>6.600000000000002</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -13069,76 +13029,76 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1309</v>
+        <v>0.1106</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0673</v>
+        <v>0.0924</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.7582</v>
+        <v>0.7788</v>
       </c>
       <c r="K37" t="n">
-        <v>0.0436</v>
+        <v>0.0182</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1.53</v>
+        <v>8.140000000000009</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1111</v>
+        <v>0.0135</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1111</v>
+        <v>0.0135</v>
       </c>
       <c r="J38" t="n">
-        <v>0.6667</v>
+        <v>0.9054</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1111</v>
+        <v>0.0135</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -13159,25 +13119,25 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.719999999999999</v>
+        <v>5.609999999999999</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -13186,19 +13146,19 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>0.098</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.1176</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>0.0392</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>0.098</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0.6471</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -13207,12 +13167,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -13246,25 +13206,25 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>7.129999999999999</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>0.0238</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>0.0477</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -13273,67 +13233,67 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>0.0477</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>0.1192</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3.559999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0478</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>0.057</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>0.0761</v>
       </c>
       <c r="J43" t="n">
-        <v>0.8596</v>
+        <v>0.7718</v>
       </c>
       <c r="K43" t="n">
-        <v>0.0927</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.53</v>
+        <v>2.53</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -13345,16 +13305,16 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>0.1304</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>0.0435</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -13363,16 +13323,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5.06</v>
+        <v>1.19</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -13387,31 +13347,31 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0217</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.913</v>
+        <v>0.8571</v>
       </c>
       <c r="K45" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.1429</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -13432,7 +13392,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -13441,16 +13401,16 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -13465,31 +13425,31 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>0.0362</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>0.8913</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>0.0725</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -13498,10 +13458,10 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.2857</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -13510,7 +13470,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.5714</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -13519,16 +13479,16 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3.699999999999999</v>
+        <v>1.53</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -13543,31 +13503,31 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0459</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.9081</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>0.0459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7.299999999999999</v>
+        <v>1.53</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -13576,37 +13536,37 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0466</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0233</v>
+        <v>0.1111</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0466</v>
+        <v>0.1111</v>
       </c>
       <c r="J50" t="n">
-        <v>0.8137</v>
+        <v>0.6667</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0699</v>
+        <v>0.1111</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1.7</v>
+        <v>8.450000000000003</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -13618,19 +13578,19 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>0.0426</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>0.0142</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0.7846</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>0.0852</v>
       </c>
     </row>
   </sheetData>

--- a/public/downloads/drift_radar.xlsx
+++ b/public/downloads/drift_radar.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-25 → 2026-04-27</t>
+          <t>2026-04-26 → 2026-04-28</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3.5 %</t>
+          <t>4.1 %</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4.6 %</t>
+          <t>5.3 %</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3.3 %</t>
+          <t>4.3 %</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.7×</t>
+          <t>2.0×</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y2" t="n">
         <v>0.67</v>
@@ -1270,13 +1270,13 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK2" t="n">
         <v>0.33</v>
@@ -1326,17 +1326,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -1359,16 +1359,16 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.2077</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5615</v>
+        <v>0.9385</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1383,25 +1383,25 @@
         <v>0.5615</v>
       </c>
       <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
         <v>0.67</v>
       </c>
-      <c r="T3" t="n">
-        <v>2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.2077</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.9385</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.33</v>
-      </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -1425,13 +1425,13 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
@@ -1470,13 +1470,13 @@
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr"/>
@@ -1484,17 +1484,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1517,29 +1517,29 @@
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="O4" t="n">
         <v>0.67</v>
       </c>
-      <c r="L4" t="n">
-        <v>4</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0.2077</v>
       </c>
-      <c r="N4" t="n">
+      <c r="R4" t="n">
         <v>0.9385</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.5615</v>
-      </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
@@ -1550,16 +1550,16 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1583,13 +1583,13 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
@@ -1598,7 +1598,7 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -1628,13 +1628,13 @@
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AW4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr"/>
@@ -1659,16 +1659,16 @@
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0.443</v>
+        <v>0.681</v>
       </c>
       <c r="F5" t="n">
         <v>1.414</v>
       </c>
       <c r="G5" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="H5" t="n">
-        <v>0.11</v>
+        <v>0.223</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -1687,16 +1687,16 @@
         <v>0.5615</v>
       </c>
       <c r="O5" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0615</v>
+        <v>0.2077</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7923</v>
+        <v>0.9385</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1744,7 +1744,7 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1789,7 +1789,7 @@
         <v>0.33</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
@@ -1800,12 +1800,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1817,16 +1817,16 @@
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.443</v>
+        <v>0.681</v>
       </c>
       <c r="F6" t="n">
         <v>1.414</v>
       </c>
       <c r="G6" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="H6" t="n">
-        <v>0.11</v>
+        <v>0.223</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -1845,28 +1845,28 @@
         <v>0.5615</v>
       </c>
       <c r="O6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7923</v>
+        <v>0.5615</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.2077</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.9385</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1875,10 +1875,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1911,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1944,10 +1944,10 @@
         <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
@@ -1958,33 +1958,33 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.443</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="F7" t="n">
         <v>1.414</v>
       </c>
       <c r="G7" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.11</v>
+        <v>0.167</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -2003,28 +2003,28 @@
         <v>0.5615</v>
       </c>
       <c r="O7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T7" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0.0615</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.7923</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.0945</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5615</v>
+        <v>0.9055</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -2116,17 +2116,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -2185,10 +2185,10 @@
         <v>0.5615</v>
       </c>
       <c r="W8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -2203,19 +2203,19 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
@@ -2260,10 +2260,10 @@
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
@@ -2274,17 +2274,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -2340,10 +2340,10 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X9" t="n">
         <v>0.33</v>
@@ -2361,13 +2361,13 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
         <v>0.33</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
@@ -2480,7 +2480,7 @@
         <v>0.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
         <v>0.0615</v>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
         <v>0.33</v>
@@ -2531,52 +2531,52 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
         <v>0.67</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1</v>
       </c>
       <c r="AW10" t="n">
         <v>1</v>
@@ -2737,7 +2737,7 @@
         <v>0.67</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
@@ -2748,21 +2748,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -2818,16 +2818,16 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2851,16 +2851,16 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2899,32 +2899,36 @@
         <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Pavo (67%), Marstall (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -2986,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Z13" t="n">
         <v>0.33</v>
@@ -3001,32 +3005,32 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
         <v>0.67</v>
       </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
@@ -3061,14 +3065,14 @@
         <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Eggersmann (33%)</t>
+          <t>Marstall (67%), Eggersmann (33%)</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr"/>
@@ -3076,12 +3080,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3109,7 +3113,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -3146,13 +3150,13 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -3167,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -3179,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -3224,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW14" t="n">
         <v>0</v>
@@ -3232,27 +3236,31 @@
       <c r="AX14" t="n">
         <v>0</v>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Pavo (67%), Havens (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -3271,7 +3279,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -3308,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -3329,7 +3337,7 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -3341,7 +3349,7 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -3353,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3386,7 +3394,7 @@
         <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
@@ -3394,31 +3402,27 @@
       <c r="AX15" t="n">
         <v>0</v>
       </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -3474,28 +3478,28 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5615</v>
+        <v>0.6576</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
         <v>1</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AA16" t="n">
         <v>0.33</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -3510,31 +3514,31 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AK16" t="n">
         <v>1</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
         <v>0.33</v>
@@ -3546,7 +3550,7 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AU16" t="n">
         <v>0</v>
@@ -3555,14 +3559,14 @@
         <v>0.33</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>Marstall (100%), Eggersmann (67%), Höveler (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (100%), St. Hippolyt (100%), Pavo (100%), Eggersmann (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr"/>
@@ -3570,12 +3574,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3584,7 +3588,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -3640,16 +3644,16 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6576</v>
+        <v>0.5615</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Y17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -3658,10 +3662,10 @@
         <v>0.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -3679,16 +3683,16 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
         <v>0</v>
@@ -3700,10 +3704,10 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -3712,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
         <v>0</v>
@@ -3721,14 +3725,14 @@
         <v>0.67</v>
       </c>
       <c r="AW17" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>Marstall (100%), St. Hippolyt (100%), Pavo (100%), Höveler (33%), Nösenberger (33%)</t>
+          <t>St. Hippolyt (67%), Pavo (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr"/>
@@ -3736,17 +3740,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -3806,7 +3810,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7935</v>
+        <v>0.5615</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3898,17 +3902,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -4060,21 +4064,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -4093,7 +4097,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -4130,16 +4134,16 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -4151,7 +4155,7 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -4163,16 +4167,16 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -4211,27 +4215,23 @@
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%)</t>
-        </is>
-      </c>
+      <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -4296,28 +4296,28 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6576</v>
+        <v>0.5615</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -4329,22 +4329,22 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
         <v>0</v>
@@ -4359,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -4371,33 +4371,29 @@
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Marstall (100%), St. Hippolyt (100%), Pavo (100%), Nösenberger (50%), Höveler (33%)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4425,7 +4421,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -4462,28 +4458,28 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -4495,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
         <v>0</v>
@@ -4504,7 +4500,7 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -4522,10 +4518,10 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -4543,32 +4539,28 @@
         <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
         <v>0</v>
       </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Pavo (33%), Marstall (33%), Höveler (33%), St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -4591,7 +4583,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -4631,13 +4623,13 @@
         <v>0.5615</v>
       </c>
       <c r="W23" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -4649,7 +4641,7 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -4658,13 +4650,13 @@
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -4673,7 +4665,7 @@
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4709,32 +4701,28 @@
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
         <v>0</v>
       </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>Havens (67%), Marstall (67%), Pavo (33%), St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -4757,7 +4745,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -4800,10 +4788,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -4815,7 +4803,7 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -4830,7 +4818,7 @@
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -4839,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4875,36 +4863,32 @@
         <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
         <v>0</v>
       </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Marstall (67%), Pavo (33%), St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -4960,28 +4944,28 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0.5615</v>
+        <v>0.6576</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
         <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0.67</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -4996,10 +4980,10 @@
         <v>0.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ25" t="n">
         <v>0.67</v>
@@ -5011,7 +4995,7 @@
         <v>1</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
         <v>0</v>
@@ -5020,7 +5004,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
         <v>0.67</v>
@@ -5035,20 +5019,20 @@
         <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>Marstall (100%), Höveler (67%), Pavo (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (100%), Pavo (100%), Höveler (67%), St. Hippolyt (67%), Nösenberger (50%)</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr"/>
@@ -5056,17 +5040,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -5089,7 +5073,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -5126,28 +5110,28 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0.6576</v>
+        <v>0.5615</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -5159,7 +5143,7 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH26" t="n">
         <v>0</v>
@@ -5168,16 +5152,16 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN26" t="n">
         <v>0</v>
@@ -5186,10 +5170,10 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR26" t="n">
         <v>0</v>
@@ -5204,31 +5188,35 @@
         <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX26" t="n">
         <v>0</v>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Marstall (100%), Höveler (100%), Pavo (67%), St. Hippolyt (67%), Eggersmann (33%)</t>
+        </is>
+      </c>
       <c r="AZ26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -5288,28 +5276,28 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -5321,7 +5309,7 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH27" t="n">
         <v>0</v>
@@ -5333,7 +5321,7 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5342,16 +5330,16 @@
         <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
         <v>0</v>
@@ -5369,14 +5357,14 @@
         <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
         <v>0</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>Eggersmann (100%), Höveler (100%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr"/>
@@ -5384,17 +5372,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -5546,21 +5534,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -5616,28 +5604,28 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>0.6576</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -5649,19 +5637,19 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
         <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5670,13 +5658,13 @@
         <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
         <v>0</v>
@@ -5697,14 +5685,14 @@
         <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
         <v>0</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>Pavo (100%), Eggersmann (100%), St. Hippolyt (100%), Marstall (33%), Höveler (33%)</t>
+          <t>Pavo (50%)</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr"/>
@@ -5712,17 +5700,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -5788,7 +5776,7 @@
         <v>0.33</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -5797,80 +5785,80 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
       </c>
       <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
         <v>0.67</v>
       </c>
-      <c r="AH30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
       <c r="AX30" t="n">
         <v>0</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>Pavo (100%), Havens (33%)</t>
+          <t>St. Hippolyt (67%), Havens (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr"/>
@@ -5878,17 +5866,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -5911,7 +5899,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -5954,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -5969,7 +5957,7 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -5984,16 +5972,16 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -6029,32 +6017,36 @@
         <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX31" t="n">
         <v>0</v>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Pavo (67%), Marstall (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -6110,7 +6102,7 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -6119,7 +6111,7 @@
         <v>0.33</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -6143,22 +6135,22 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
         <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
         <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AM32" t="n">
         <v>0</v>
@@ -6188,17 +6180,17 @@
         <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX32" t="n">
         <v>0</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (67%), Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr"/>
@@ -6206,17 +6198,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -6276,7 +6268,7 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -6285,7 +6277,7 @@
         <v>0.33</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -6318,7 +6310,7 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK33" t="n">
         <v>0</v>
@@ -6364,7 +6356,7 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr"/>
@@ -6372,17 +6364,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -6405,7 +6397,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -6448,16 +6440,16 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -6475,7 +6467,7 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH34" t="n">
         <v>0</v>
@@ -6484,7 +6476,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK34" t="n">
         <v>0</v>
@@ -6502,7 +6494,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ34" t="n">
         <v>0</v>
@@ -6528,23 +6520,27 @@
       <c r="AX34" t="n">
         <v>0</v>
       </c>
-      <c r="AY34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Pavo (33%), Marstall (33%), Höveler (33%)</t>
+        </is>
+      </c>
       <c r="AZ34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -6604,7 +6600,7 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.7935</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -6696,21 +6692,21 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -6729,7 +6725,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -6766,7 +6762,7 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -6775,19 +6771,19 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -6808,28 +6804,28 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR36" t="n">
         <v>0</v>
@@ -6844,35 +6840,39 @@
         <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX36" t="n">
         <v>0</v>
       </c>
-      <c r="AY36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Marstall (100%), Eggersmann (67%), Höveler (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -6928,13 +6928,13 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0.6576</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -6961,7 +6961,7 @@
         <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH37" t="n">
         <v>0</v>
@@ -7014,27 +7014,31 @@
       <c r="AX37" t="n">
         <v>0</v>
       </c>
-      <c r="AY37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Pavo (33%)</t>
+        </is>
+      </c>
       <c r="AZ37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -7093,52 +7097,52 @@
         <v>0.5615</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="X38" t="n">
         <v>0.33</v>
       </c>
       <c r="Y38" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
         <v>0.67</v>
       </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0</v>
-      </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
         <v>0</v>
@@ -7171,14 +7175,14 @@
         <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
         <v>0</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>Marstall (67%), Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Havens (67%), Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr"/>
@@ -7186,17 +7190,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -7219,7 +7223,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -7262,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
         <v>0</v>
@@ -7277,7 +7281,7 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -7289,7 +7293,7 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
         <v>0</v>
@@ -7337,32 +7341,28 @@
         <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
         <v>0</v>
       </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Pavo (33%), St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -7422,7 +7422,7 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
@@ -7514,21 +7514,21 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -7676,17 +7676,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -7752,13 +7752,13 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -7767,7 +7767,7 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -7779,19 +7779,19 @@
         <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7800,7 +7800,7 @@
         <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -7824,17 +7824,17 @@
         <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX42" t="n">
         <v>0</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Pavo (100%), Eggersmann (67%), St. Hippolyt (67%), Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr"/>
@@ -7842,21 +7842,21 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -7918,13 +7918,13 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7933,7 +7933,7 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -7945,10 +7945,10 @@
         <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -7957,7 +7957,7 @@
         <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7966,7 +7966,7 @@
         <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -7993,14 +7993,14 @@
         <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX43" t="n">
         <v>0</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>St. Hippolyt (100%), Pavo (67%), Marstall (67%), Eggersmann (33%)</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr"/>
@@ -8008,21 +8008,21 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -8078,13 +8078,13 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -8102,19 +8102,19 @@
         <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -8164,27 +8164,31 @@
       <c r="AX44" t="n">
         <v>0</v>
       </c>
-      <c r="AY44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Pavo (100%), Havens (33%)</t>
+        </is>
+      </c>
       <c r="AZ44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -8203,7 +8207,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -8243,28 +8247,28 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
         <v>0</v>
@@ -8273,7 +8277,7 @@
         <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
         <v>0</v>
@@ -8282,7 +8286,7 @@
         <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
         <v>0</v>
@@ -8291,7 +8295,7 @@
         <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="n">
         <v>0</v>
@@ -8300,7 +8304,7 @@
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ45" t="n">
         <v>0</v>
@@ -8318,30 +8322,26 @@
         <v>0</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX45" t="n">
         <v>0</v>
       </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>Pavo (67%), Havens (33%), Marstall (33%), Eggersmann (33%), Höveler (33%)</t>
-        </is>
-      </c>
+      <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -8350,7 +8350,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -8412,13 +8412,13 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -8427,7 +8427,7 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -8439,19 +8439,19 @@
         <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -8487,28 +8487,32 @@
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX46" t="n">
         <v>0</v>
       </c>
-      <c r="AY46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Eggersmann (100%), Pavo (67%), St. Hippolyt (67%), Marstall (33%)</t>
+        </is>
+      </c>
       <c r="AZ46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -8571,67 +8575,67 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AB47" t="n">
         <v>0</v>
       </c>
       <c r="AC47" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN47" t="n">
         <v>1</v>
       </c>
-      <c r="AD47" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>0</v>
-      </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AR47" t="n">
         <v>0</v>
@@ -8646,17 +8650,17 @@
         <v>0</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AX47" t="n">
         <v>0</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Havens (33%), Marstall (33%), Höveler (33%)</t>
+          <t>Eggersmann (100%), Höveler (100%), Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr"/>
@@ -8664,17 +8668,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -8697,7 +8701,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -8740,22 +8744,22 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -8767,19 +8771,19 @@
         <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8788,7 +8792,7 @@
         <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -8797,7 +8801,7 @@
         <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR48" t="n">
         <v>0</v>
@@ -8812,35 +8816,31 @@
         <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX48" t="n">
         <v>0</v>
       </c>
-      <c r="AY48" t="inlineStr">
-        <is>
-          <t>Pavo (100%), Marstall (100%), St. Hippolyt (100%), Eggersmann (67%), Höveler (33%)</t>
-        </is>
-      </c>
+      <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -8909,86 +8909,86 @@
         <v>0.67</v>
       </c>
       <c r="Y49" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
         <v>0.67</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV49" t="n">
         <v>0.67</v>
       </c>
-      <c r="AA49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>0</v>
-      </c>
       <c r="AW49" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AX49" t="n">
         <v>0</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>Pavo (67%), Marstall (67%), Eggersmann (67%), St. Hippolyt (67%)</t>
+          <t>St. Hippolyt (100%), Pavo (67%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr"/>
@@ -8996,12 +8996,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -9158,21 +9158,21 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -9228,95 +9228,95 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>0.6576</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X51" t="n">
         <v>1</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB51" t="n">
         <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AF51" t="n">
         <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW51" t="n">
         <v>1</v>
       </c>
-      <c r="AJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>0</v>
-      </c>
       <c r="AX51" t="n">
         <v>0</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>Pavo (100%)</t>
+          <t>Pavo (100%), St. Hippolyt (100%), Marstall (67%), Havens (33%), Eggersmann (33%)</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr"/>
@@ -9448,17 +9448,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -9469,30 +9469,30 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -9503,10 +9503,10 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.67</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -9533,14 +9533,14 @@
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0.443</v>
+        <v>0.681</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9550,12 +9550,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -9567,68 +9567,68 @@
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.443</v>
+        <v>0.681</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.443</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -9652,17 +9652,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -9844,21 +9844,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -9879,19 +9879,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Eggersmann (33%)</t>
+          <t>Pavo (67%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -9921,24 +9921,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (67%), Eggersmann (33%)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Marstall (100%), Eggersmann (67%), Höveler (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (67%), Havens (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
@@ -10005,28 +10005,28 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Marstall (100%), St. Hippolyt (100%), Pavo (100%), Höveler (33%), Nösenberger (33%)</t>
+          <t>Marstall (100%), St. Hippolyt (100%), Pavo (100%), Eggersmann (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%)</t>
+          <t>St. Hippolyt (67%), Pavo (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
@@ -10089,19 +10089,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Marstall (100%), St. Hippolyt (100%), Pavo (100%), Nösenberger (50%), Höveler (33%)</t>
+          <t>Marstall (100%), Pavo (100%), Höveler (67%), St. Hippolyt (67%), Nösenberger (50%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -10131,24 +10131,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), Höveler (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (100%), Höveler (100%), Pavo (67%), St. Hippolyt (67%), Eggersmann (33%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -10173,28 +10173,28 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Havens (67%), Marstall (67%), Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -10215,19 +10215,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Marstall (67%), Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (50%)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -10257,24 +10257,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Marstall (100%), Höveler (67%), Pavo (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
+          <t>St. Hippolyt (67%), Havens (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -10299,28 +10299,28 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Eggersmann (100%), Höveler (100%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (67%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10341,24 +10341,24 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Pavo (100%), Eggersmann (100%), St. Hippolyt (100%), Marstall (33%), Höveler (33%)</t>
+          <t>Marstall (67%), Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Pavo (100%), Havens (33%)</t>
+          <t>Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
     </row>
@@ -10425,24 +10425,24 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -10467,28 +10467,28 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Marstall (100%), Eggersmann (67%), Höveler (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -10509,24 +10509,24 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Marstall (67%), Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -10551,24 +10551,24 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Havens (67%), Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -10593,28 +10593,28 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Pavo (100%), Eggersmann (67%), St. Hippolyt (67%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10635,19 +10635,19 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>St. Hippolyt (100%), Pavo (67%), Marstall (67%), Eggersmann (33%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -10677,24 +10677,24 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Pavo (67%), Havens (33%), Marstall (33%), Eggersmann (33%), Höveler (33%)</t>
+          <t>Pavo (100%), Havens (33%)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -10719,24 +10719,24 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Havens (33%), Marstall (33%), Höveler (33%)</t>
+          <t>Eggersmann (100%), Pavo (67%), St. Hippolyt (67%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -10761,24 +10761,24 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Pavo (100%), Marstall (100%), St. Hippolyt (100%), Eggersmann (67%), Höveler (33%)</t>
+          <t>Eggersmann (100%), Höveler (100%), Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -10803,28 +10803,28 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Pavo (67%), Marstall (67%), Eggersmann (67%), St. Hippolyt (67%)</t>
+          <t>St. Hippolyt (100%), Pavo (67%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Pavo (100%)</t>
+          <t>Pavo (100%), St. Hippolyt (100%), Marstall (67%), Havens (33%), Eggersmann (33%)</t>
         </is>
       </c>
     </row>
@@ -10942,21 +10942,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -10980,17 +10980,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -11018,17 +11018,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -11056,21 +11056,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -11094,17 +11094,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -11170,17 +11170,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -11208,7 +11208,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -11246,17 +11246,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -11284,21 +11284,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -11322,21 +11322,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -11360,17 +11360,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -11398,21 +11398,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -11436,21 +11436,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -11474,21 +11474,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -11512,12 +11512,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -11526,7 +11526,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -11655,19 +11655,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10.14000000000001</v>
+        <v>9.150000000000011</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0542</v>
+        <v>0.0481</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0108</v>
+        <v>0.012</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0542</v>
+        <v>0.0481</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -11676,88 +11676,88 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8481</v>
+        <v>0.8557</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0325</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6.710000000000005</v>
+        <v>7.930000000000006</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0164</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0492</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0328</v>
+        <v>0.0416</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0492</v>
+        <v>0.0277</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0164</v>
+        <v>0.0139</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.0416</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8033</v>
+        <v>0.7642</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0328</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.370000000000005</v>
+        <v>4.229999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.0402</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0597</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0299</v>
+        <v>0.0402</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0149</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0299</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7612</v>
+        <v>0.9196</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1045</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -11772,7 +11772,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.05</v>
+        <v>2.04</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -11781,19 +11781,19 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0557</v>
+        <v>0.0833</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1115</v>
+        <v>0.1667</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8328</v>
+        <v>0.75</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -11802,55 +11802,55 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3.569999999999999</v>
+        <v>7.150000000000007</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.0308</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.0308</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0476</v>
+        <v>0.0308</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.0308</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9048</v>
+        <v>0.8154</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.390000000000003</v>
+        <v>4.160000000000002</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -11859,37 +11859,37 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.0577</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0408</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9184</v>
+        <v>0.8534</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3.52</v>
+        <v>3.629999999999999</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -11898,19 +11898,19 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1563</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.0606</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7187</v>
+        <v>0.9394</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -11919,28 +11919,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.229999999999999</v>
+        <v>3.52</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0526</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0526</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -11949,7 +11949,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.7812</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -11967,16 +11967,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.239999999999999</v>
+        <v>2.889999999999999</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0401</v>
+        <v>0.0588</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0401</v>
+        <v>0.0588</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -11988,7 +11988,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9198</v>
+        <v>0.8824</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -12036,58 +12036,58 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9.900000000000009</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0111</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0667</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0444</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0667</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0556</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7222</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.53</v>
+        <v>3.569999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.0476</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12096,7 +12096,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.0476</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -12105,7 +12105,7 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0.9048</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -12114,55 +12114,55 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9.680000000000003</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0227</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0114</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0341</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.09089999999999999</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1705</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4773</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1932</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.070000000000004</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -12180,67 +12180,67 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0156</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9222</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0622</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7.04</v>
+        <v>4.090000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0156</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0156</v>
+        <v>0.0293</v>
       </c>
       <c r="F16" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0156</v>
+        <v>0.0611</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0625</v>
+        <v>0.0293</v>
       </c>
       <c r="I16" t="n">
-        <v>0.125</v>
+        <v>0.0611</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4375</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0781</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3.710000000000001</v>
+        <v>6.860000000000004</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -12252,34 +12252,34 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0674</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0674</v>
+        <v>0.016</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8652</v>
+        <v>0.9038</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.08019999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3.390000000000002</v>
+        <v>5.06</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -12288,76 +12288,76 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0413</v>
+        <v>0.1087</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.1087</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9587</v>
+        <v>0.6304</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.0217</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.160000000000011</v>
+        <v>2.090000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0135</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0135</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0404</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0135</v>
+        <v>0.0526</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0674</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8517</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.0526</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.7</v>
+        <v>3.080000000000001</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -12366,76 +12366,76 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.1071</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.1071</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9</v>
+        <v>0.7143</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5.930000000000001</v>
+        <v>7.369999999999998</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.0149</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0202</v>
+        <v>0.0149</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.0448</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.0149</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.0746</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.1343</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7926</v>
+        <v>0.5224</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1872</v>
+        <v>0.1791</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4.569999999999999</v>
+        <v>7.480000000000001</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -12444,76 +12444,76 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.1029</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.0294</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0372</v>
+        <v>0.0147</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>0.0735</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8162</v>
+        <v>0.6324</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1466</v>
+        <v>0.1471</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5.500000000000004</v>
+        <v>8.800000000000008</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>0.0125</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.0375</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.02</v>
+        <v>0.0375</v>
       </c>
       <c r="I23" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="K23" t="n">
-        <v>0.06</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3.739999999999999</v>
+        <v>6.089999999999998</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -12522,115 +12522,115 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0455</v>
+        <v>0.0279</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.0279</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0455</v>
+        <v>0.0279</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8636</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0455</v>
+        <v>0.0558</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6.930000000000005</v>
+        <v>6.31</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0317</v>
+        <v>0.019</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0635</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0159</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8254</v>
+        <v>0.7861</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0635</v>
+        <v>0.1949</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.71</v>
+        <v>5.610000000000002</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.0392</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.0784</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0702</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8596</v>
+        <v>0.8431</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0702</v>
+        <v>0.0392</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.19</v>
+        <v>5.829999999999998</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -12639,121 +12639,121 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1429</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2857</v>
+        <v>0.0566</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>0.0377</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5714</v>
+        <v>0.6792</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>0.0377</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7.590000000000002</v>
+        <v>6.710000000000005</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.0164</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1304</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0435</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>0.058</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.058</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6522</v>
+        <v>0.8361</v>
       </c>
       <c r="K28" t="n">
-        <v>0.058</v>
+        <v>0.0164</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3.399999999999999</v>
+        <v>7.410000000000004</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>0.0162</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.0324</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.85</v>
+        <v>0.8043</v>
       </c>
       <c r="K29" t="n">
-        <v>0.05</v>
+        <v>0.081</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3.559999999999999</v>
+        <v>6.35</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0478</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -12762,40 +12762,40 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8596</v>
+        <v>0.948</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>5.409999999999998</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.0314</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.0314</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -12804,67 +12804,67 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>0.0314</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.8743</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.0314</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>6.490000000000006</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>0.0339</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.0339</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>0.0169</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>0.0169</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.8814</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>0.0169</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.370000000000004</v>
+        <v>6.959999999999999</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -12873,37 +12873,37 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0597</v>
+        <v>0.0489</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0597</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0746</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0448</v>
+        <v>0.0489</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7313</v>
+        <v>0.8046</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0299</v>
+        <v>0.0977</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6.729999999999999</v>
+        <v>1.19</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -12912,19 +12912,19 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0505</v>
+        <v>0.1429</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.09959999999999999</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0253</v>
+        <v>0.1429</v>
       </c>
       <c r="J34" t="n">
-        <v>0.8247</v>
+        <v>0.7143</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -12933,16 +12933,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6.089999999999998</v>
+        <v>3.220000000000002</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -12951,76 +12951,76 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0279</v>
+        <v>0.0435</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>0.0435</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0279</v>
+        <v>0.0435</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0279</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.7826</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0558</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8.429999999999998</v>
+        <v>7.919999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>0.0139</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>0.0139</v>
       </c>
       <c r="F36" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.2083</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0202</v>
+        <v>0.0139</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0391</v>
+        <v>0.0694</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0403</v>
+        <v>0.1528</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7794</v>
+        <v>0.5</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0403</v>
+        <v>0.0278</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6.600000000000002</v>
+        <v>6.119999999999999</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -13029,72 +13029,72 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1106</v>
+        <v>0.0556</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0924</v>
+        <v>0.0278</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>0.1111</v>
       </c>
       <c r="J37" t="n">
-        <v>0.7788</v>
+        <v>0.7222</v>
       </c>
       <c r="K37" t="n">
-        <v>0.0182</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8.140000000000009</v>
+        <v>6.390000000000006</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0135</v>
+        <v>0.0172</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0135</v>
+        <v>0.0172</v>
       </c>
       <c r="J38" t="n">
-        <v>0.9054</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>0.0135</v>
+        <v>0.0689</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -13128,16 +13128,16 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5.609999999999999</v>
+        <v>4.389999999999999</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -13146,19 +13146,19 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.098</v>
+        <v>0.0387</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1176</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0392</v>
+        <v>0.1162</v>
       </c>
       <c r="I40" t="n">
-        <v>0.098</v>
+        <v>0.0387</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6471</v>
+        <v>0.8064</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -13167,16 +13167,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -13185,7 +13185,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -13197,34 +13197,34 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7.129999999999999</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0238</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0477</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -13233,67 +13233,67 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0477</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7616000000000001</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.1192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>8.94</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.057</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0761</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7718</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0.057</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2.53</v>
+        <v>3.729999999999999</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -13305,34 +13305,34 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1304</v>
+        <v>0.0456</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0435</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.866</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>0.0885</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1.19</v>
+        <v>2.04</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -13341,7 +13341,7 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>0.0833</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -13350,28 +13350,28 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>0.0833</v>
       </c>
       <c r="J45" t="n">
-        <v>0.8571</v>
+        <v>0.75</v>
       </c>
       <c r="K45" t="n">
-        <v>0.1429</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -13392,25 +13392,25 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>0.9167</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4.69</v>
+        <v>1.19</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -13419,33 +13419,33 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>0.2857</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0362</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8913</v>
+        <v>0.5714</v>
       </c>
       <c r="K47" t="n">
-        <v>0.0725</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -13479,16 +13479,16 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1.53</v>
+        <v>2.21</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -13509,25 +13509,25 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0.9231</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>0.0769</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.53</v>
+        <v>9.599999999999998</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -13536,37 +13536,37 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>0.0708</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>0.0354</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1111</v>
+        <v>0.0344</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1111</v>
+        <v>0.0354</v>
       </c>
       <c r="J50" t="n">
-        <v>0.6667</v>
+        <v>0.7885</v>
       </c>
       <c r="K50" t="n">
-        <v>0.1111</v>
+        <v>0.0354</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>8.450000000000003</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -13578,19 +13578,19 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.07340000000000001</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0426</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0142</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.7846</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0852</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/public/downloads/drift_radar.xlsx
+++ b/public/downloads/drift_radar.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-26 → 2026-04-28</t>
+          <t>2026-04-27 → 2026-04-29</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40 / 50  (80 %)</t>
+          <t>39 / 50  (78 %)</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -561,7 +561,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4.1 %</t>
+          <t>3.8 %</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2.7 %</t>
+          <t>2.6 %</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4.3 %</t>
+          <t>3.3 %</t>
         </is>
       </c>
     </row>
@@ -1185,32 +1185,32 @@
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>0.841</v>
+        <v>0.912</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.414</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.443</v>
+        <v>0.333</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7923</v>
+        <v>0.5615</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0.33</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1315,7 +1315,7 @@
         <v>0.33</v>
       </c>
       <c r="AW2" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -1326,61 +1326,61 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.681</v>
+        <v>0.912</v>
       </c>
       <c r="F3" t="n">
         <v>1.414</v>
       </c>
       <c r="G3" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.223</v>
+        <v>0.333</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2077</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9385</v>
+        <v>0.5615</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.4385</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5615</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1392,16 +1392,16 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -1425,10 +1425,10 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
@@ -1470,13 +1470,13 @@
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AW3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr"/>
@@ -1484,33 +1484,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.681</v>
+        <v>0.443</v>
       </c>
       <c r="F4" t="n">
         <v>1.414</v>
       </c>
       <c r="G4" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="H4" t="n">
-        <v>0.223</v>
+        <v>0.11</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -1529,16 +1529,16 @@
         <v>0.5615</v>
       </c>
       <c r="O4" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2077</v>
+        <v>0.0615</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9385</v>
+        <v>0.7923</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1550,13 +1550,13 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1583,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
@@ -1642,12 +1642,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1656,19 +1656,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0.681</v>
+        <v>0.443</v>
       </c>
       <c r="F5" t="n">
         <v>1.414</v>
       </c>
       <c r="G5" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="H5" t="n">
-        <v>0.223</v>
+        <v>0.11</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -1687,16 +1687,16 @@
         <v>0.5615</v>
       </c>
       <c r="O5" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2077</v>
+        <v>0.0615</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9385</v>
+        <v>0.7923</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1708,10 +1708,10 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -1735,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
         <v>0.67</v>
@@ -1800,33 +1800,33 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.681</v>
+        <v>0.443</v>
       </c>
       <c r="F6" t="n">
         <v>1.414</v>
       </c>
       <c r="G6" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="H6" t="n">
-        <v>0.223</v>
+        <v>0.11</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
@@ -1845,28 +1845,28 @@
         <v>0.5615</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="S6" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2077</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9385</v>
+        <v>0.7935</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1875,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1944,10 +1944,10 @@
         <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
@@ -1975,16 +1975,16 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.443</v>
       </c>
       <c r="F7" t="n">
         <v>1.414</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="H7" t="n">
-        <v>0.167</v>
+        <v>0.11</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
@@ -2015,16 +2015,16 @@
         <v>0.5615</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0945</v>
+        <v>0.0615</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9055</v>
+        <v>0.7923</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -2116,17 +2116,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -2149,29 +2149,29 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="N8" t="n">
+        <v>0.7923</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.5615</v>
       </c>
-      <c r="O8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.0615</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.7923</v>
-      </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
@@ -2182,7 +2182,7 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -2260,10 +2260,10 @@
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
@@ -2274,17 +2274,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -2322,7 +2322,7 @@
         <v>0.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
         <v>0.0615</v>
@@ -2340,13 +2340,13 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -2355,28 +2355,28 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
         <v>0.67</v>
       </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2418,10 +2418,10 @@
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
@@ -2432,17 +2432,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2465,29 +2465,29 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="N10" t="n">
+        <v>0.7923</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>0.5615</v>
       </c>
-      <c r="O10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.0615</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.7923</v>
-      </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
@@ -2498,13 +2498,13 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="Y10" t="n">
         <v>0.33</v>
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -2531,10 +2531,10 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AH10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -2543,10 +2543,10 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
@@ -2558,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ10" t="n">
         <v>0</v>
@@ -2582,7 +2582,7 @@
         <v>1</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr"/>
@@ -2590,17 +2590,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2635,28 +2635,28 @@
         <v>0.7923</v>
       </c>
       <c r="O11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="U11" t="n">
         <v>0.0615</v>
       </c>
-      <c r="R11" t="n">
+      <c r="V11" t="n">
         <v>0.7923</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -2748,65 +2748,61 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.707</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>own_only</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2824,23 +2820,23 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
         <v>0.67</v>
       </c>
-      <c r="Y12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
@@ -2851,80 +2847,76 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW12" t="n">
         <v>0.67</v>
       </c>
-      <c r="AH12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Pavo (67%), Marstall (33%), St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -2947,7 +2939,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -2984,7 +2976,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2993,10 +2985,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -3029,7 +3021,7 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -3038,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3070,31 +3062,27 @@
       <c r="AX13" t="n">
         <v>0</v>
       </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Marstall (67%), Eggersmann (33%)</t>
-        </is>
-      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -3153,16 +3141,16 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0.67</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -3171,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -3183,11 +3171,11 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
         <v>0.67</v>
       </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
       <c r="AI14" t="n">
         <v>0</v>
       </c>
@@ -3195,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3204,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3228,17 +3216,17 @@
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Pavo (67%), Havens (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (100%), Pavo (67%), St. Hippolyt (67%), Eggersmann (33%)</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr"/>
@@ -3246,21 +3234,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -3279,7 +3267,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -3316,28 +3304,28 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -3349,7 +3337,7 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -3358,16 +3346,16 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
@@ -3376,10 +3364,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3394,35 +3382,39 @@
         <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Marstall (100%), Höveler (100%), St. Hippolyt (67%), Pavo (33%), Eggersmann (33%)</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -3478,28 +3470,28 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6576</v>
+        <v>0.5615</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Y16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -3511,28 +3503,28 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3541,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -3550,23 +3542,23 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
         <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>Marstall (100%), St. Hippolyt (100%), Pavo (100%), Eggersmann (33%), Höveler (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr"/>
@@ -3574,17 +3566,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -3607,7 +3599,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -3644,13 +3636,13 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5615</v>
+        <v>0.6576</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -3659,13 +3651,13 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -3677,7 +3669,7 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
@@ -3704,7 +3696,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
         <v>0</v>
@@ -3722,35 +3714,31 @@
         <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>St. Hippolyt (67%), Pavo (33%), Höveler (33%)</t>
-        </is>
-      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -3902,21 +3890,21 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -3972,7 +3960,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -4064,21 +4052,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -4097,7 +4085,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -4143,10 +4131,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -4155,7 +4143,7 @@
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -4176,19 +4164,19 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4212,31 +4200,35 @@
         <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Marstall (100%), Eggersmann (67%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -4259,7 +4251,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -4296,10 +4288,10 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -4311,19 +4303,19 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -4356,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ21" t="n">
         <v>0</v>
@@ -4377,32 +4369,36 @@
         <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>St. Hippolyt (67%), Havens (33%), Höveler (33%)</t>
+        </is>
+      </c>
       <c r="AZ21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -4421,7 +4417,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -4464,22 +4460,22 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -4494,34 +4490,34 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -4530,37 +4526,41 @@
         <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AU22" t="n">
         <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+        <v>0.67</v>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Pavo (100%), Marstall (100%), St. Hippolyt (100%), Eggersmann (33%), Höveler (33%)</t>
+        </is>
+      </c>
       <c r="AZ22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -4712,21 +4712,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -4782,7 +4782,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.6576</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -4874,21 +4874,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -4944,28 +4944,28 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6576</v>
+        <v>0.5615</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -4977,22 +4977,22 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
         <v>0</v>
@@ -5007,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
         <v>0</v>
@@ -5019,38 +5019,34 @@
         <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
         <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Marstall (100%), Pavo (100%), Höveler (67%), St. Hippolyt (67%), Nösenberger (50%)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -5110,7 +5106,7 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -5119,13 +5115,13 @@
         <v>0.67</v>
       </c>
       <c r="Y26" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AA26" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -5146,34 +5142,34 @@
         <v>0.67</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AL26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AR26" t="n">
         <v>0</v>
@@ -5191,14 +5187,14 @@
         <v>0.67</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AX26" t="n">
         <v>0</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>Marstall (100%), Höveler (100%), Pavo (67%), St. Hippolyt (67%), Eggersmann (33%)</t>
+          <t>Pavo (67%), Marstall (67%), Eggersmann (67%), St. Hippolyt (67%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr"/>
@@ -5206,17 +5202,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -5276,16 +5272,16 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="X27" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -5297,28 +5293,28 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -5354,7 +5350,7 @@
         <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW27" t="n">
         <v>0</v>
@@ -5364,7 +5360,7 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Pavo (100%), Havens (67%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr"/>
@@ -5372,17 +5368,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -5442,7 +5438,7 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -5534,21 +5530,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -5567,7 +5563,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -5604,13 +5600,13 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0.6576</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -5643,7 +5639,7 @@
         <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
         <v>0</v>
@@ -5690,31 +5686,27 @@
       <c r="AX29" t="n">
         <v>0</v>
       </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>Pavo (50%)</t>
-        </is>
-      </c>
+      <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -5733,7 +5725,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -5773,7 +5765,7 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -5785,19 +5777,19 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -5830,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
         <v>0</v>
@@ -5851,32 +5843,28 @@
         <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
         <v>0</v>
       </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>St. Hippolyt (67%), Havens (33%), Höveler (33%)</t>
-        </is>
-      </c>
+      <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -5942,13 +5930,13 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -5972,16 +5960,16 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5990,7 +5978,7 @@
         <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6024,7 +6012,7 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>Pavo (67%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr"/>
@@ -6032,21 +6020,21 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -6108,23 +6096,23 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
         <v>0.67</v>
       </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AD32" t="n">
         <v>0</v>
       </c>
@@ -6135,13 +6123,13 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH32" t="n">
         <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
         <v>0</v>
@@ -6150,47 +6138,47 @@
         <v>0</v>
       </c>
       <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
         <v>0.67</v>
       </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0</v>
-      </c>
       <c r="AW32" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AX32" t="n">
         <v>0</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>Marstall (67%), Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (67%), St. Hippolyt (67%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr"/>
@@ -6198,21 +6186,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -6289,7 +6277,7 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -6304,7 +6292,7 @@
         <v>0.33</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -6346,7 +6334,7 @@
         <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW33" t="n">
         <v>0</v>
@@ -6356,7 +6344,7 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%)</t>
+          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr"/>
@@ -6364,12 +6352,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6449,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -6494,7 +6482,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
         <v>0</v>
@@ -6522,7 +6510,7 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), Höveler (33%)</t>
+          <t>Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr"/>
@@ -6530,17 +6518,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -6563,7 +6551,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -6600,58 +6588,58 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0.7935</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN35" t="n">
         <v>0</v>
@@ -6663,7 +6651,7 @@
         <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR35" t="n">
         <v>0</v>
@@ -6681,32 +6669,36 @@
         <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX35" t="n">
         <v>0</v>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>St. Hippolyt (100%), Pavo (67%), Marstall (67%), Havens (33%), Eggersmann (33%)</t>
+        </is>
+      </c>
       <c r="AZ35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -6725,7 +6717,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -6762,7 +6754,7 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -6771,19 +6763,19 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -6804,28 +6796,28 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
         <v>0</v>
@@ -6840,39 +6832,35 @@
         <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
         <v>0</v>
       </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Marstall (100%), Eggersmann (67%), Höveler (33%), St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -6891,7 +6879,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -6928,13 +6916,13 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -6961,7 +6949,7 @@
         <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
         <v>0</v>
@@ -7014,27 +7002,23 @@
       <c r="AX37" t="n">
         <v>0</v>
       </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Pavo (33%)</t>
-        </is>
-      </c>
+      <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -7057,7 +7041,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -7097,13 +7081,13 @@
         <v>0.5615</v>
       </c>
       <c r="W38" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -7124,13 +7108,13 @@
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -7139,7 +7123,7 @@
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -7180,27 +7164,23 @@
       <c r="AX38" t="n">
         <v>0</v>
       </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Havens (67%), Pavo (33%), Marstall (33%)</t>
-        </is>
-      </c>
+      <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -7223,7 +7203,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -7269,7 +7249,7 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -7302,7 +7282,7 @@
         <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK39" t="n">
         <v>0</v>
@@ -7346,27 +7326,31 @@
       <c r="AX39" t="n">
         <v>0</v>
       </c>
-      <c r="AY39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Marstall (33%)</t>
+        </is>
+      </c>
       <c r="AZ39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -7385,7 +7369,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -7422,28 +7406,28 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -7455,22 +7439,22 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM40" t="n">
         <v>0</v>
@@ -7485,10 +7469,10 @@
         <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AS40" t="n">
         <v>0</v>
@@ -7497,34 +7481,38 @@
         <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AV40" t="n">
         <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+        <v>0.67</v>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Pavo (100%), Marstall (100%), Nösenberger (67%), St. Hippolyt (67%), Höveler (33%)</t>
+        </is>
+      </c>
       <c r="AZ40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -7547,7 +7535,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -7590,13 +7578,13 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7605,7 +7593,7 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -7617,28 +7605,28 @@
         <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -7665,28 +7653,32 @@
         <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX41" t="n">
         <v>0</v>
       </c>
-      <c r="AY41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Pavo (67%), Eggersmann (67%), St. Hippolyt (67%), Marstall (33%)</t>
+        </is>
+      </c>
       <c r="AZ41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -7752,22 +7744,22 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>0.33</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB42" t="n">
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -7779,10 +7771,10 @@
         <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -7791,7 +7783,7 @@
         <v>0.33</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7800,13 +7792,13 @@
         <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ42" t="n">
         <v>0</v>
@@ -7824,17 +7816,17 @@
         <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
         <v>0</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>Pavo (100%), Eggersmann (67%), St. Hippolyt (67%), Marstall (33%)</t>
+          <t>Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr"/>
@@ -7842,21 +7834,21 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -7912,19 +7904,19 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X43" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -7933,7 +7925,7 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -7942,13 +7934,13 @@
         <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -7957,7 +7949,7 @@
         <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7966,7 +7958,7 @@
         <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -7993,14 +7985,14 @@
         <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AX43" t="n">
         <v>0</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Marstall (67%), Eggersmann (33%)</t>
+          <t>Havens (33%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr"/>
@@ -8008,17 +8000,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -8081,13 +8073,13 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -8099,28 +8091,28 @@
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK44" t="n">
         <v>0</v>
@@ -8159,14 +8151,14 @@
         <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX44" t="n">
         <v>0</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>Pavo (100%), Havens (33%)</t>
+          <t>Pavo (67%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr"/>
@@ -8174,21 +8166,21 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -8336,12 +8328,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -8369,7 +8361,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -8412,13 +8404,13 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -8427,7 +8419,7 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -8439,19 +8431,19 @@
         <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -8460,7 +8452,7 @@
         <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -8487,36 +8479,32 @@
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
         <v>0</v>
       </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Eggersmann (100%), Pavo (67%), St. Hippolyt (67%), Marstall (33%)</t>
-        </is>
-      </c>
+      <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -8572,7 +8560,7 @@
         <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W47" t="n">
         <v>0</v>
@@ -8581,13 +8569,13 @@
         <v>0.33</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
         <v>0</v>
@@ -8611,7 +8599,7 @@
         <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AJ47" t="n">
         <v>0</v>
@@ -8620,22 +8608,22 @@
         <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AM47" t="n">
         <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR47" t="n">
         <v>0</v>
@@ -8660,7 +8648,7 @@
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>Eggersmann (100%), Höveler (100%), Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr"/>
@@ -8668,17 +8656,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -8738,7 +8726,7 @@
         <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W48" t="n">
         <v>0</v>
@@ -8830,17 +8818,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -8906,65 +8894,65 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
         <v>0.67</v>
       </c>
-      <c r="Y49" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0</v>
-      </c>
       <c r="AA49" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AB49" t="n">
         <v>0</v>
       </c>
       <c r="AC49" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ49" t="n">
         <v>1</v>
       </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AR49" t="n">
         <v>0</v>
       </c>
@@ -8978,17 +8966,17 @@
         <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AX49" t="n">
         <v>0</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Marstall (33%), Höveler (33%)</t>
+          <t>Höveler (100%), Eggersmann (67%), Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr"/>
@@ -8996,21 +8984,21 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -9029,7 +9017,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -9075,10 +9063,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -9111,7 +9099,7 @@
         <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -9120,7 +9108,7 @@
         <v>0</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
@@ -9152,23 +9140,27 @@
       <c r="AX50" t="n">
         <v>0</v>
       </c>
-      <c r="AY50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Marstall (67%), Eggersmann (33%)</t>
+        </is>
+      </c>
       <c r="AZ50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -9231,19 +9223,19 @@
         <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="Y51" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
         <v>0.67</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0.33</v>
       </c>
       <c r="AB51" t="n">
         <v>0</v>
@@ -9255,43 +9247,43 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
         <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
         <v>0.67</v>
       </c>
-      <c r="AI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ51" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR51" t="n">
         <v>0</v>
@@ -9306,7 +9298,7 @@
         <v>0</v>
       </c>
       <c r="AV51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW51" t="n">
         <v>1</v>
@@ -9316,7 +9308,7 @@
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>Pavo (100%), St. Hippolyt (100%), Marstall (67%), Havens (33%), Eggersmann (33%)</t>
+          <t>St. Hippolyt (100%), Pavo (67%), Höveler (67%), Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr"/>
@@ -9344,7 +9336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9431,11 +9423,11 @@
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>0.841</v>
+        <v>0.912</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -9448,31 +9440,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.681</v>
+        <v>0.912</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -9482,31 +9474,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.681</v>
+        <v>0.443</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -9516,12 +9508,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9530,17 +9522,17 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0.681</v>
+        <v>0.443</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9550,34 +9542,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.681</v>
+        <v>0.443</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I6" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr"/>
     </row>
@@ -9601,7 +9593,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.443</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
@@ -9611,24 +9603,24 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -9639,10 +9631,10 @@
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -9652,17 +9644,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -9686,17 +9678,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -9707,10 +9699,10 @@
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -9720,17 +9712,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -9744,15 +9736,49 @@
         <v>0.33</v>
       </c>
       <c r="H11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pferde Nahrungsergänzung</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E11">
+  <conditionalFormatting sqref="E2:E12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -9774,7 +9800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9844,21 +9870,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -9879,24 +9905,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Pavo (67%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (100%), Pavo (67%), St. Hippolyt (67%), Eggersmann (33%)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -9921,24 +9947,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Marstall (67%), Eggersmann (33%)</t>
+          <t>Marstall (100%), Höveler (100%), St. Hippolyt (67%), Pavo (33%), Eggersmann (33%)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -9963,28 +9989,28 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Pavo (67%), Havens (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -10005,24 +10031,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Marstall (100%), St. Hippolyt (100%), Pavo (100%), Eggersmann (33%), Höveler (33%)</t>
+          <t>Marstall (100%), Eggersmann (67%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -10047,24 +10073,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>St. Hippolyt (67%), Pavo (33%), Höveler (33%)</t>
+          <t>St. Hippolyt (67%), Havens (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -10089,24 +10115,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Marstall (100%), Pavo (100%), Höveler (67%), St. Hippolyt (67%), Nösenberger (50%)</t>
+          <t>Pavo (100%), Marstall (100%), St. Hippolyt (100%), Eggersmann (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -10131,24 +10157,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Marstall (100%), Höveler (100%), Pavo (67%), St. Hippolyt (67%), Eggersmann (33%)</t>
+          <t>Pavo (67%), Marstall (67%), Eggersmann (67%), St. Hippolyt (67%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -10173,28 +10199,28 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Pavo (100%), Havens (67%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -10215,24 +10241,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Pavo (50%)</t>
+          <t>Pavo (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -10257,28 +10283,28 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>St. Hippolyt (67%), Havens (33%), Höveler (33%)</t>
+          <t>Pavo (67%), St. Hippolyt (67%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -10299,28 +10325,28 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Pavo (67%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10341,24 +10367,24 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Marstall (67%), Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -10383,24 +10409,24 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%)</t>
+          <t>St. Hippolyt (100%), Pavo (67%), Marstall (67%), Havens (33%), Eggersmann (33%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -10425,28 +10451,28 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), Höveler (33%)</t>
+          <t>Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -10467,24 +10493,24 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Marstall (100%), Eggersmann (67%), Höveler (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (100%), Marstall (100%), Nösenberger (67%), St. Hippolyt (67%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -10509,24 +10535,24 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Pavo (67%), Eggersmann (67%), St. Hippolyt (67%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -10551,24 +10577,24 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Havens (67%), Pavo (33%), Marstall (33%)</t>
+          <t>Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -10593,19 +10619,19 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Pavo (100%), Eggersmann (67%), St. Hippolyt (67%), Marstall (33%)</t>
+          <t>Havens (33%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -10614,7 +10640,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10635,28 +10661,28 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Marstall (67%), Eggersmann (33%)</t>
+          <t>Pavo (67%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -10677,24 +10703,24 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Pavo (100%), Havens (33%)</t>
+          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -10719,24 +10745,24 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Eggersmann (100%), Pavo (67%), St. Hippolyt (67%), Marstall (33%)</t>
+          <t>Höveler (100%), Eggersmann (67%), Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -10761,7 +10787,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Eggersmann (100%), Höveler (100%), Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (67%), Eggersmann (33%)</t>
         </is>
       </c>
     </row>
@@ -10803,54 +10829,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Marstall (33%), Höveler (33%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>own_only</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Pavo (100%), St. Hippolyt (100%), Marstall (67%), Havens (33%), Eggersmann (33%)</t>
+          <t>St. Hippolyt (100%), Pavo (67%), Höveler (67%), Marstall (33%)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E25">
+  <conditionalFormatting sqref="E2:E24">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -10942,21 +10926,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -10980,17 +10964,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -11018,17 +11002,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -11056,17 +11040,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -11132,21 +11116,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -11170,17 +11154,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -11208,7 +11192,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -11218,7 +11202,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -11246,17 +11230,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -11284,21 +11268,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -11322,12 +11306,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -11336,7 +11320,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -11360,21 +11344,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -11398,17 +11382,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -11436,21 +11420,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -11474,17 +11458,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -11512,21 +11496,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -11655,106 +11639,106 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.150000000000011</v>
+        <v>10.37</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0481</v>
+        <v>0.053</v>
       </c>
       <c r="F2" t="n">
-        <v>0.012</v>
+        <v>0.0212</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0481</v>
+        <v>0.0424</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.0106</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.0106</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8557</v>
+        <v>0.8197</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0361</v>
+        <v>0.0424</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.930000000000006</v>
+        <v>7.379999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0416</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0277</v>
+        <v>0.023</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0139</v>
+        <v>0.023</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0416</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7642</v>
+        <v>0.8862</v>
       </c>
       <c r="K3" t="n">
-        <v>0.111</v>
+        <v>0.0447</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4.229999999999999</v>
+        <v>5.500000000000002</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0402</v>
+        <v>0.02</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9196</v>
+        <v>0.88</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -11763,16 +11747,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.04</v>
+        <v>4.619999999999999</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -11781,61 +11765,61 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0833</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.0238</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1667</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.75</v>
+        <v>0.8333</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.0476</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7.150000000000007</v>
+        <v>1.26</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0308</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0308</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0308</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0308</v>
+        <v>0.1111</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8154</v>
+        <v>0.7778</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0615</v>
+        <v>0.1111</v>
       </c>
     </row>
     <row r="7">
@@ -11850,28 +11834,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.160000000000002</v>
+        <v>6.270000000000004</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.0175</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0577</v>
+        <v>0.0526</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.0175</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0526</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.0175</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8534</v>
+        <v>0.8421</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -11880,16 +11864,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3.629999999999999</v>
+        <v>3.23</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -11904,31 +11888,31 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0606</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9394</v>
+        <v>0.5263</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.4737</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -11937,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.09379999999999999</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -11949,7 +11933,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7812</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -11958,115 +11942,115 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.889999999999999</v>
+        <v>6.600000000000003</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0588</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0588</v>
+        <v>0.05</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.0333</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.0167</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.0167</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8824</v>
+        <v>0.7667</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.1167</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3.23</v>
+        <v>7.810000000000006</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.0423</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.0282</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.0282</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.0423</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5263</v>
+        <v>0.8028</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4737</v>
+        <v>0.0563</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>5.059999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.0336</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.1008</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.1324</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.7332</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -12075,55 +12059,55 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.569999999999999</v>
+        <v>8.470000000000006</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0476</v>
+        <v>0.013</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0476</v>
+        <v>0.0519</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.0519</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9048</v>
+        <v>0.7662</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.0519</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>3.229999999999999</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -12144,103 +12128,103 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.9474</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>0.0526</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>6.050000000000003</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>0.0182</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.0727</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.0182</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.8545</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4.090000000000001</v>
+        <v>5.829999999999998</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0293</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0611</v>
+        <v>0.0566</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0293</v>
+        <v>0.1132</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0611</v>
+        <v>0.0377</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8191000000000001</v>
+        <v>0.6604</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.0377</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6.860000000000004</v>
+        <v>8.280000000000003</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -12249,37 +12233,37 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.0725</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.0737</v>
       </c>
       <c r="I17" t="n">
-        <v>0.016</v>
+        <v>0.0435</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9038</v>
+        <v>0.7234</v>
       </c>
       <c r="K17" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.06</v>
+        <v>10.01000000000001</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -12288,37 +12272,37 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.044</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1087</v>
+        <v>0.0659</v>
       </c>
       <c r="H18" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.022</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1087</v>
+        <v>0.0659</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6304</v>
+        <v>0.7582</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0217</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.090000000000001</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -12333,235 +12317,235 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0526</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8947000000000001</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0526</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3.080000000000001</v>
+        <v>9.470000000000002</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>0.0116</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.0116</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.1985</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1071</v>
+        <v>0.0116</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.0813</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1071</v>
+        <v>0.1278</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7143</v>
+        <v>0.5343</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.0232</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7.369999999999998</v>
+        <v>6.859999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0149</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0149</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0448</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0149</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0746</v>
+        <v>0.0481</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1343</v>
+        <v>0.0248</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5224</v>
+        <v>0.9023</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1791</v>
+        <v>0.0248</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7.480000000000001</v>
+        <v>8.270000000000008</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>0.0133</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1029</v>
+        <v>0.0133</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0294</v>
+        <v>0.0399</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0147</v>
+        <v>0.0266</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0735</v>
+        <v>0.0399</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6324</v>
+        <v>0.8537</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1471</v>
+        <v>0.0133</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8.800000000000008</v>
+        <v>10.12</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0125</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.0109</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0375</v>
+        <v>0.0217</v>
       </c>
       <c r="G23" t="n">
-        <v>0.05</v>
+        <v>0.0109</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0375</v>
+        <v>0.1087</v>
       </c>
       <c r="I23" t="n">
-        <v>0.05</v>
+        <v>0.1413</v>
       </c>
       <c r="J23" t="n">
-        <v>0.75</v>
+        <v>0.5109</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0625</v>
+        <v>0.1957</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6.089999999999998</v>
+        <v>8.540000000000003</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>0.0141</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0279</v>
+        <v>0.0422</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.0433</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0279</v>
+        <v>0.0281</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0279</v>
+        <v>0.0141</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.7857</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0558</v>
+        <v>0.0726</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6.31</v>
+        <v>2.310000000000001</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.0476</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -12573,37 +12557,37 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7861</v>
+        <v>0.9048</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1949</v>
+        <v>0.0476</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5.610000000000002</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0392</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0784</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -12612,25 +12596,25 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8431</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0392</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5.829999999999998</v>
+        <v>3.899999999999999</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -12639,40 +12623,40 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.09429999999999999</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0566</v>
+        <v>0.0436</v>
       </c>
       <c r="H27" t="n">
-        <v>0.09429999999999999</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0377</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6792</v>
+        <v>0.8282</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0377</v>
+        <v>0.1282</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6.710000000000005</v>
+        <v>1.87</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0164</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -12681,73 +12665,73 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.06560000000000001</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.1818</v>
       </c>
       <c r="I28" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8361</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0164</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7.410000000000004</v>
+        <v>1.19</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0162</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.06610000000000001</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0324</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8043</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0.081</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6.35</v>
+        <v>7.049999999999999</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -12756,19 +12740,19 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.0709</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.0723</v>
       </c>
       <c r="H30" t="n">
-        <v>0.052</v>
+        <v>0.0468</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.948</v>
+        <v>0.8099</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -12777,94 +12761,94 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5.409999999999998</v>
+        <v>9.959999999999999</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0314</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0314</v>
+        <v>0.1024</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.0171</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.0331</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0314</v>
+        <v>0.0683</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8743</v>
+        <v>0.7279</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0314</v>
+        <v>0.0512</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6.490000000000006</v>
+        <v>7.080000000000004</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0339</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0339</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0169</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0169</v>
+        <v>0.0311</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8814</v>
+        <v>0.9534</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0169</v>
+        <v>0.0155</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6.959999999999999</v>
+        <v>3.569999999999999</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -12873,7 +12857,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0489</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -12882,28 +12866,28 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0489</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8046</v>
+        <v>0.9524</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0977</v>
+        <v>0.0476</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -12912,7 +12896,7 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -12921,10 +12905,10 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0.7143</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -12933,16 +12917,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3.220000000000002</v>
+        <v>2.889999999999999</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -12951,76 +12935,76 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.0435</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0435</v>
+        <v>0.0588</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0435</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.7826</v>
+        <v>0.9412</v>
       </c>
       <c r="K35" t="n">
-        <v>0.08699999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7.919999999999999</v>
+        <v>2.04</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0139</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0139</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2083</v>
+        <v>0.0833</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0139</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0694</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1528</v>
+        <v>0.0833</v>
       </c>
       <c r="J36" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0278</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6.119999999999999</v>
+        <v>5.499999999999998</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -13029,37 +13013,37 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0556</v>
+        <v>0.1</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0278</v>
+        <v>0.02</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1111</v>
+        <v>0.08</v>
       </c>
       <c r="J37" t="n">
-        <v>0.7222</v>
+        <v>0.74</v>
       </c>
       <c r="K37" t="n">
-        <v>0.0833</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6.390000000000006</v>
+        <v>4.4</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -13068,37 +13052,37 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.175</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0172</v>
+        <v>0.075</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0172</v>
+        <v>0.15</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8967000000000001</v>
+        <v>0.525</v>
       </c>
       <c r="K38" t="n">
-        <v>0.0689</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>6.959999999999999</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -13107,7 +13091,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>0.0489</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -13116,76 +13100,76 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>0.0489</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.8046</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>0.0977</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4.389999999999999</v>
+        <v>8.970000000000006</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>0.0123</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0387</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1162</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0387</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8064</v>
+        <v>0.8774</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>0.1104</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1.7</v>
+        <v>7.119999999999998</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>0.0239</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1</v>
+        <v>0.0478</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -13197,25 +13181,25 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.8</v>
+        <v>0.8329</v>
       </c>
       <c r="K41" t="n">
-        <v>0.1</v>
+        <v>0.0955</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -13224,7 +13208,7 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -13233,10 +13217,10 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7143</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -13245,16 +13229,16 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>8.590000000000003</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -13269,70 +13253,70 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>0.0512</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>0.0128</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>0.8719</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3.729999999999999</v>
+        <v>5.409999999999998</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>0.0314</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>0.0314</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0456</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>0.0314</v>
       </c>
       <c r="J44" t="n">
-        <v>0.866</v>
+        <v>0.8743</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0885</v>
+        <v>0.0314</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -13341,7 +13325,7 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0833</v>
+        <v>0.1</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -13350,28 +13334,28 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0833</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="K45" t="n">
-        <v>0.0833</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2.04</v>
+        <v>6.799999999999999</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -13380,76 +13364,76 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>0.075</v>
       </c>
       <c r="J46" t="n">
-        <v>0.9167</v>
+        <v>0.75</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0833</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1.19</v>
+        <v>6.050000000000004</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>0.0182</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2857</v>
+        <v>0.0182</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>0.0182</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>0.0182</v>
       </c>
       <c r="J47" t="n">
-        <v>0.5714</v>
+        <v>0.9091</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>0.0182</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -13458,37 +13442,37 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>0.0167</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>0.0167</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>0.0667</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>0.7333</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>0.1167</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -13509,64 +13493,64 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.9231</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0.0769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>9.599999999999998</v>
+        <v>3.569999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>0.0476</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0708</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0354</v>
+        <v>0.0476</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0344</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0354</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0.7885</v>
+        <v>0.9048</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0354</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>5.049999999999999</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -13581,16 +13565,16 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>0.0673</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>0.899</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>0.0337</v>
       </c>
     </row>
   </sheetData>

--- a/public/downloads/drift_radar.xlsx
+++ b/public/downloads/drift_radar.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-27 → 2026-04-29</t>
+          <t>2026-04-28 → 2026-04-30</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -561,7 +561,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3.8 %</t>
+          <t>4.0 %</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2.6 %</t>
+          <t>3.3 %</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5.3 %</t>
+          <t>4.6 %</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3.3 %</t>
+          <t>4.0 %</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2.0×</t>
+          <t>1.4×</t>
         </is>
       </c>
     </row>
@@ -1237,13 +1237,13 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X2" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Z2" t="n">
         <v>0.33</v>
@@ -1264,16 +1264,16 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.33</v>
@@ -1282,10 +1282,10 @@
         <v>0.33</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
         <v>0.33</v>
@@ -1294,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.33</v>
@@ -1318,7 +1318,7 @@
         <v>0.67</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
@@ -1343,16 +1343,16 @@
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.912</v>
+        <v>0.681</v>
       </c>
       <c r="F3" t="n">
         <v>1.414</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="H3" t="n">
-        <v>0.333</v>
+        <v>0.223</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -1371,16 +1371,16 @@
         <v>0.5615</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4385</v>
+        <v>0.2077</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0.9385</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1398,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -1425,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
@@ -1470,7 +1470,7 @@
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -1484,33 +1484,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.443</v>
+        <v>0.681</v>
       </c>
       <c r="F4" t="n">
         <v>1.414</v>
       </c>
       <c r="G4" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="H4" t="n">
-        <v>0.11</v>
+        <v>0.223</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -1529,28 +1529,28 @@
         <v>0.5615</v>
       </c>
       <c r="O4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7923</v>
+        <v>0.5615</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.2077</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5615</v>
+        <v>0.9385</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1642,17 +1642,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -1708,22 +1708,22 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1735,25 +1735,25 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1762,16 +1762,16 @@
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AW5" t="n">
         <v>0.67</v>
@@ -1800,17 +1800,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1833,62 +1833,62 @@
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="N6" t="n">
+        <v>0.7923</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.5615</v>
       </c>
-      <c r="O6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0.0615</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.7923</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.7935</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
@@ -1899,22 +1899,22 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ6" t="n">
         <v>0</v>
@@ -1944,13 +1944,13 @@
         <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr"/>
@@ -1958,21 +1958,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>0.443</v>
@@ -1991,16 +1991,16 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -2015,22 +2015,22 @@
         <v>0.5615</v>
       </c>
       <c r="S7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7923</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -2057,7 +2057,7 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
@@ -2116,17 +2116,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -2182,28 +2182,28 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
@@ -2224,13 +2224,13 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2260,7 +2260,7 @@
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AW8" t="n">
         <v>0.33</v>
@@ -2274,17 +2274,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -2322,7 +2322,7 @@
         <v>0.33</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
         <v>0.0615</v>
@@ -2340,28 +2340,28 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.7935</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -2373,16 +2373,16 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2418,10 +2418,10 @@
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
@@ -2432,17 +2432,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2465,29 +2465,29 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0.0615</v>
       </c>
-      <c r="N10" t="n">
+      <c r="R10" t="n">
         <v>0.7923</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.5615</v>
-      </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0.67</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -2531,11 +2531,11 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AH10" t="n">
         <v>0.67</v>
       </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2582,7 +2582,7 @@
         <v>1</v>
       </c>
       <c r="AX10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr"/>
@@ -2590,21 +2590,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>0.337</v>
@@ -2635,50 +2635,50 @@
         <v>0.7923</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="S11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
-        <v>0.0615</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.7923</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -2701,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2734,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
@@ -2748,33 +2748,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.707</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>0.33</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
         <v>0.0615</v>
@@ -2805,22 +2805,22 @@
         <v>0.7923</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.7923</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2829,31 +2829,31 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
         <v>0.67</v>
       </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
       <c r="AH12" t="n">
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
@@ -2874,7 +2874,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ12" t="n">
         <v>0</v>
@@ -2892,10 +2892,10 @@
         <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
@@ -3144,13 +3144,13 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
         <v>0.67</v>
       </c>
-      <c r="Y14" t="n">
-        <v>1</v>
-      </c>
       <c r="Z14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -3174,17 +3174,17 @@
         <v>0</v>
       </c>
       <c r="AH14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
         <v>0.67</v>
       </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1</v>
-      </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
@@ -3192,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>Marstall (100%), Pavo (67%), St. Hippolyt (67%), Eggersmann (33%)</t>
+          <t>Pavo (100%), Marstall (67%), St. Hippolyt (67%)</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr"/>
@@ -3234,17 +3234,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -3304,44 +3304,44 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="X15" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1</v>
       </c>
-      <c r="Z15" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
@@ -3349,13 +3349,13 @@
         <v>0.33</v>
       </c>
       <c r="AK15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
@@ -3364,10 +3364,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3382,17 +3382,17 @@
         <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>Marstall (100%), Höveler (100%), St. Hippolyt (67%), Pavo (33%), Eggersmann (33%)</t>
+          <t>Pavo (100%), Havens (67%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr"/>
@@ -3400,17 +3400,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -3476,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
@@ -3556,27 +3556,23 @@
       <c r="AX16" t="n">
         <v>0</v>
       </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Pavo (33%)</t>
-        </is>
-      </c>
+      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -3599,7 +3595,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -3636,7 +3632,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6576</v>
+        <v>0.5615</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -3651,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -3696,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ17" t="n">
         <v>0</v>
@@ -3722,18 +3718,22 @@
       <c r="AX17" t="n">
         <v>0</v>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Höveler (33%)</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -3798,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3819,7 +3819,7 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3840,7 +3840,7 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW18" t="n">
         <v>0</v>
@@ -3884,27 +3884,31 @@
       <c r="AX18" t="n">
         <v>0</v>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Marstall (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -3923,7 +3927,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -3963,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -3975,19 +3979,19 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -4020,7 +4024,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AQ19" t="n">
         <v>0</v>
@@ -4041,32 +4045,36 @@
         <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Höveler (67%), Havens (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -4122,28 +4130,28 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5615</v>
+        <v>0.6576</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
         <v>1</v>
       </c>
       <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
         <v>0.67</v>
       </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -4155,40 +4163,40 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AK20" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AL20" t="n">
         <v>1</v>
       </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
       <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>0.67</v>
       </c>
-      <c r="AN20" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AS20" t="n">
         <v>0</v>
@@ -4197,20 +4205,20 @@
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>Marstall (100%), Eggersmann (67%), St. Hippolyt (33%)</t>
+          <t>Pavo (100%), Marstall (100%), St. Hippolyt (100%), Höveler (67%), Nösenberger (50%)</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr"/>
@@ -4218,21 +4226,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -4288,19 +4296,19 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W21" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AA21" t="n">
         <v>0.33</v>
@@ -4309,49 +4317,49 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AI21" t="n">
         <v>0.67</v>
       </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP21" t="n">
         <v>0.33</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -4366,17 +4374,17 @@
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX21" t="n">
         <v>0.67</v>
       </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>St. Hippolyt (67%), Havens (33%), Höveler (33%)</t>
+          <t>Marstall (100%), St. Hippolyt (100%), Pavo (67%), Eggersmann (67%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr"/>
@@ -4384,21 +4392,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -4417,7 +4425,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -4460,22 +4468,22 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -4490,34 +4498,34 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -4526,41 +4534,37 @@
         <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
         <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Pavo (100%), Marstall (100%), St. Hippolyt (100%), Eggersmann (33%), Höveler (33%)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -4583,7 +4587,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -4626,7 +4630,7 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -4635,13 +4639,13 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -4653,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
@@ -4680,7 +4684,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ23" t="n">
         <v>0</v>
@@ -4698,35 +4702,39 @@
         <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX23" t="n">
         <v>0</v>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>St. Hippolyt (100%), Pavo (67%), Höveler (33%)</t>
+        </is>
+      </c>
       <c r="AZ23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -4782,7 +4790,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0.6576</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -4874,17 +4882,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -4907,7 +4915,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -4944,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -4965,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -5022,7 +5030,7 @@
         <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW25" t="n">
         <v>0</v>
@@ -5030,23 +5038,27 @@
       <c r="AX25" t="n">
         <v>0</v>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -5106,28 +5118,28 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -5139,10 +5151,10 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5151,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -5160,7 +5172,7 @@
         <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5169,7 +5181,7 @@
         <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
         <v>0</v>
@@ -5184,17 +5196,17 @@
         <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AX26" t="n">
         <v>0</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>Pavo (67%), Marstall (67%), Eggersmann (67%), St. Hippolyt (67%), Höveler (33%)</t>
+          <t>St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr"/>
@@ -5202,21 +5214,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -5275,46 +5287,46 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -5332,7 +5344,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ27" t="n">
         <v>0</v>
@@ -5350,7 +5362,7 @@
         <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
         <v>0</v>
@@ -5360,7 +5372,7 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>Pavo (100%), Havens (67%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr"/>
@@ -5368,17 +5380,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -5530,21 +5542,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -5563,7 +5575,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -5600,16 +5612,16 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -5633,13 +5645,13 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH29" t="n">
         <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AJ29" t="n">
         <v>0</v>
@@ -5648,7 +5660,7 @@
         <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AM29" t="n">
         <v>0</v>
@@ -5686,27 +5698,31 @@
       <c r="AX29" t="n">
         <v>0</v>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Pavo (33%), Marstall (33%)</t>
+        </is>
+      </c>
       <c r="AZ29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -5725,7 +5741,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -5762,16 +5778,16 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -5795,19 +5811,19 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5848,23 +5864,27 @@
       <c r="AX30" t="n">
         <v>0</v>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Pavo (33%), Marstall (33%)</t>
+        </is>
+      </c>
       <c r="AZ30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -5887,7 +5907,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -5924,19 +5944,19 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -5945,7 +5965,7 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -5960,7 +5980,7 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -5978,7 +5998,7 @@
         <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6005,36 +6025,32 @@
         <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
         <v>0</v>
       </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Pavo (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -6053,7 +6069,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -6090,13 +6106,13 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -6105,13 +6121,13 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -6123,7 +6139,7 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
         <v>0</v>
@@ -6150,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
         <v>0</v>
@@ -6168,39 +6184,35 @@
         <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
         <v>0</v>
       </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Pavo (67%), St. Hippolyt (67%), Höveler (33%)</t>
-        </is>
-      </c>
+      <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -6256,28 +6268,28 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -6289,10 +6301,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -6301,16 +6313,16 @@
         <v>0.33</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -6319,7 +6331,7 @@
         <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR33" t="n">
         <v>0</v>
@@ -6337,14 +6349,14 @@
         <v>0.33</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX33" t="n">
         <v>0</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (100%), Eggersmann (67%), St. Hippolyt (67%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr"/>
@@ -6352,12 +6364,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6366,7 +6378,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -6422,7 +6434,7 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -6431,7 +6443,7 @@
         <v>0.33</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -6455,16 +6467,16 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
         <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
         <v>0</v>
@@ -6510,7 +6522,7 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr"/>
@@ -6518,17 +6530,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -6591,92 +6603,92 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
         <v>0.67</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
         <v>0.67</v>
       </c>
-      <c r="Z35" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1</v>
-      </c>
       <c r="AX35" t="n">
         <v>0</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Marstall (67%), Havens (33%), Eggersmann (33%)</t>
+          <t>Höveler (100%), St. Hippolyt (67%), Pavo (33%), Eggersmann (33%)</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr"/>
@@ -6684,21 +6696,21 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -6717,7 +6729,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -6760,13 +6772,13 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -6775,7 +6787,7 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -6790,7 +6802,7 @@
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -6808,7 +6820,7 @@
         <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -6835,12 +6847,16 @@
         <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX36" t="n">
         <v>0</v>
       </c>
-      <c r="AY36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Pavo (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -7008,17 +7024,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -7170,21 +7186,21 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -7246,10 +7262,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -7261,7 +7277,7 @@
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -7273,7 +7289,7 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH39" t="n">
         <v>0</v>
@@ -7282,7 +7298,7 @@
         <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
         <v>0</v>
@@ -7318,7 +7334,7 @@
         <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW39" t="n">
         <v>0</v>
@@ -7328,7 +7344,7 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>Marstall (33%)</t>
+          <t>Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr"/>
@@ -7336,17 +7352,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -7406,16 +7422,16 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -7424,10 +7440,10 @@
         <v>0.33</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -7439,22 +7455,22 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
         <v>0</v>
@@ -7466,13 +7482,13 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
         <v>0</v>
@@ -7481,20 +7497,20 @@
         <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
         <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>Pavo (100%), Marstall (100%), Nösenberger (67%), St. Hippolyt (67%), Höveler (33%)</t>
+          <t>Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr"/>
@@ -7502,12 +7518,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -7575,16 +7591,16 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X41" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
         <v>0.33</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7593,13 +7609,13 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -7608,13 +7624,13 @@
         <v>0.67</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
         <v>0.33</v>
@@ -7626,7 +7642,7 @@
         <v>0.33</v>
       </c>
       <c r="AN41" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -7653,14 +7669,14 @@
         <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AX41" t="n">
         <v>0</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>Pavo (67%), Eggersmann (67%), St. Hippolyt (67%), Marstall (33%)</t>
+          <t>Pavo (100%), St. Hippolyt (100%), Havens (33%), Marstall (33%), Eggersmann (33%)</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr"/>
@@ -7668,17 +7684,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -7744,7 +7760,7 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y42" t="n">
         <v>0.33</v>
@@ -7753,7 +7769,7 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
         <v>0</v>
@@ -7774,7 +7790,7 @@
         <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -7798,7 +7814,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
         <v>0</v>
@@ -7826,7 +7842,7 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>Marstall (33%), Höveler (33%)</t>
+          <t>Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr"/>
@@ -7834,17 +7850,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -7904,28 +7920,28 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -7934,10 +7950,10 @@
         <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH43" t="n">
         <v>0</v>
@@ -7946,10 +7962,10 @@
         <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AK43" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7964,7 +7980,7 @@
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AQ43" t="n">
         <v>0</v>
@@ -7985,14 +8001,14 @@
         <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX43" t="n">
         <v>0</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>Havens (33%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (67%), Höveler (67%), Pavo (33%)</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr"/>
@@ -8000,17 +8016,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -8033,7 +8049,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -8070,16 +8086,16 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -8091,7 +8107,7 @@
         <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -8106,13 +8122,13 @@
         <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
         <v>0</v>
@@ -8151,27 +8167,23 @@
         <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX44" t="n">
         <v>0</v>
       </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Pavo (67%), Marstall (33%), St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -8199,7 +8211,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -8245,7 +8257,7 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -8278,7 +8290,7 @@
         <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK45" t="n">
         <v>0</v>
@@ -8322,23 +8334,27 @@
       <c r="AX45" t="n">
         <v>0</v>
       </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Marstall (33%)</t>
+        </is>
+      </c>
       <c r="AZ45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -8361,7 +8377,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -8398,28 +8414,28 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB46" t="n">
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -8428,7 +8444,7 @@
         <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -8443,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -8458,7 +8474,7 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ46" t="n">
         <v>0</v>
@@ -8479,32 +8495,36 @@
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX46" t="n">
         <v>0</v>
       </c>
-      <c r="AY46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Havens (33%), Marstall (33%), Höveler (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -8560,19 +8580,19 @@
         <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -8581,7 +8601,7 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -8596,25 +8616,25 @@
         <v>0.33</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL47" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -8641,14 +8661,14 @@
         <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AX47" t="n">
         <v>0</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (67%), Marstall (67%), Eggersmann (67%), St. Hippolyt (67%)</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr"/>
@@ -8656,12 +8676,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -8726,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
         <v>0</v>
@@ -8818,12 +8838,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -8851,7 +8871,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -8888,28 +8908,28 @@
         <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W49" t="n">
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
         <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -8921,7 +8941,7 @@
         <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
         <v>0</v>
@@ -8942,7 +8962,7 @@
         <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -8951,7 +8971,7 @@
         <v>0</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR49" t="n">
         <v>0</v>
@@ -8969,16 +8989,12 @@
         <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX49" t="n">
         <v>0</v>
       </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Höveler (100%), Eggersmann (67%), Pavo (33%), St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -9075,7 +9091,7 @@
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -9135,14 +9151,14 @@
         <v>0</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX50" t="n">
         <v>0</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>Marstall (67%), Eggersmann (33%)</t>
+          <t>Marstall (67%), Eggersmann (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr"/>
@@ -9226,19 +9242,19 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y51" t="n">
         <v>0.67</v>
       </c>
-      <c r="Y51" t="n">
-        <v>0.33</v>
-      </c>
       <c r="Z51" t="n">
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AC51" t="n">
         <v>1</v>
@@ -9253,20 +9269,20 @@
         <v>0</v>
       </c>
       <c r="AG51" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" t="n">
         <v>0.67</v>
       </c>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AL51" t="n">
         <v>0</v>
       </c>
@@ -9280,7 +9296,7 @@
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AQ51" t="n">
         <v>0</v>
@@ -9289,7 +9305,7 @@
         <v>0</v>
       </c>
       <c r="AS51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AT51" t="n">
         <v>0</v>
@@ -9308,7 +9324,7 @@
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Höveler (67%), Marstall (33%)</t>
+          <t>Höveler (100%), St. Hippolyt (100%), Marstall (67%), Pavo (33%), Nösenberger (33%)</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr"/>
@@ -9336,7 +9352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9457,14 +9473,14 @@
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.912</v>
+        <v>0.681</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -9474,51 +9490,51 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.443</v>
+        <v>0.681</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -9542,17 +9558,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -9563,10 +9579,10 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9576,51 +9592,51 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>0.443</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -9644,17 +9660,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -9678,17 +9694,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -9699,10 +9715,10 @@
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -9712,21 +9728,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>0.337</v>
@@ -9736,49 +9752,15 @@
         <v>0.33</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Pferde Nahrungsergänzung</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E12">
+  <conditionalFormatting sqref="E2:E11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -9800,7 +9782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9905,24 +9887,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Marstall (100%), Pavo (67%), St. Hippolyt (67%), Eggersmann (33%)</t>
+          <t>Pavo (100%), Marstall (67%), St. Hippolyt (67%)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -9947,24 +9929,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Marstall (100%), Höveler (100%), St. Hippolyt (67%), Pavo (33%), Eggersmann (33%)</t>
+          <t>Pavo (100%), Havens (67%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -9989,24 +9971,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -10031,7 +10013,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Marstall (100%), Eggersmann (67%), St. Hippolyt (33%)</t>
+          <t>Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
@@ -10073,24 +10055,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>St. Hippolyt (67%), Havens (33%), Höveler (33%)</t>
+          <t>Höveler (67%), Havens (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -10115,28 +10097,28 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Pavo (100%), Marstall (100%), St. Hippolyt (100%), Eggersmann (33%), Höveler (33%)</t>
+          <t>Pavo (100%), Marstall (100%), St. Hippolyt (100%), Höveler (67%), Nösenberger (50%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -10157,24 +10139,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pavo (67%), Marstall (67%), Eggersmann (67%), St. Hippolyt (67%), Höveler (33%)</t>
+          <t>Marstall (100%), St. Hippolyt (100%), Pavo (67%), Eggersmann (67%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -10199,24 +10181,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Pavo (100%), Havens (67%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>St. Hippolyt (100%), Pavo (67%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -10241,24 +10223,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Pavo (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
+          <t>St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -10283,24 +10265,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Pavo (67%), St. Hippolyt (67%), Höveler (33%)</t>
+          <t>St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -10325,28 +10307,28 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10374,17 +10356,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -10409,24 +10391,24 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Marstall (67%), Havens (33%), Eggersmann (33%)</t>
+          <t>Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -10451,19 +10433,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Marstall (33%)</t>
+          <t>Marstall (100%), Eggersmann (67%), St. Hippolyt (67%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -10493,24 +10475,24 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Pavo (100%), Marstall (100%), Nösenberger (67%), St. Hippolyt (67%), Höveler (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -10535,24 +10517,24 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Pavo (67%), Eggersmann (67%), St. Hippolyt (67%), Marstall (33%)</t>
+          <t>Höveler (100%), St. Hippolyt (67%), Pavo (33%), Eggersmann (33%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -10577,28 +10559,28 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Marstall (33%), Höveler (33%)</t>
+          <t>Pavo (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -10619,28 +10601,28 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Havens (33%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10661,28 +10643,28 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Pavo (67%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -10703,24 +10685,24 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (100%), St. Hippolyt (100%), Havens (33%), Marstall (33%), Eggersmann (33%)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -10745,24 +10727,24 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Höveler (100%), Eggersmann (67%), Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -10787,24 +10769,24 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Marstall (67%), Eggersmann (33%)</t>
+          <t>Marstall (67%), Höveler (67%), Pavo (33%)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -10829,12 +10811,180 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Höveler (67%), Marstall (33%)</t>
+          <t>Marstall (33%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Natürliche Pferdepflege</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>own_only</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Havens (33%), Marstall (33%), Höveler (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Pferde Vitamine und Mineralstoffe</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>own_only</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Pavo (67%), Marstall (67%), Eggersmann (67%), St. Hippolyt (67%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Natürliche Pferdepflege</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>own_only</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Marstall (67%), Eggersmann (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Pferde Nahrungsergänzungsmittel</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>own_only</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Höveler (100%), St. Hippolyt (100%), Marstall (67%), Pavo (33%), Nösenberger (33%)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E24">
+  <conditionalFormatting sqref="E2:E28">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -10856,7 +11006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11002,17 +11152,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -11040,12 +11190,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -11054,7 +11204,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -11078,17 +11228,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -11116,21 +11266,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -11154,21 +11304,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -11192,21 +11342,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -11230,17 +11380,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -11268,21 +11418,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -11306,21 +11456,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -11344,21 +11494,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -11379,160 +11529,8 @@
       </c>
       <c r="J13" t="inlineStr"/>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Pferde Nahrungsergänzung</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E17">
+  <conditionalFormatting sqref="E2:E13">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -11639,31 +11637,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10.37</v>
+        <v>7.940000000000007</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.053</v>
+        <v>0.0277</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0212</v>
+        <v>0.0277</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0424</v>
+        <v>0.0554</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0106</v>
+        <v>0.0139</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0106</v>
+        <v>0.0277</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8197</v>
+        <v>0.806</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0424</v>
+        <v>0.0416</v>
       </c>
     </row>
     <row r="3">
@@ -11678,10 +11676,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.379999999999999</v>
+        <v>4.199999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -11690,73 +11688,73 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.023</v>
+        <v>0.0405</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8862</v>
+        <v>0.919</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0447</v>
+        <v>0.0405</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.500000000000002</v>
+        <v>7.160000000000005</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>0.0154</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.0307</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02</v>
+        <v>0.0307</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06</v>
+        <v>0.0461</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02</v>
+        <v>0.0154</v>
       </c>
       <c r="J4" t="n">
-        <v>0.88</v>
+        <v>0.831</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.0307</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.619999999999999</v>
+        <v>1.53</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -11765,10 +11763,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09520000000000001</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0238</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -11777,85 +11775,85 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8333</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.26</v>
+        <v>4.86</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.0226</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.0226</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1111</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.0226</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7778</v>
+        <v>0.8868</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1111</v>
+        <v>0.0453</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.270000000000004</v>
+        <v>2.379999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0175</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0526</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0175</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0526</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0175</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8421</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -11864,55 +11862,55 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3.23</v>
+        <v>5.830000000000002</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.0377</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.0189</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.0566</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.0377</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5263</v>
+        <v>0.8491</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.540000000000001</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -11927,133 +11925,133 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.0551</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.8898</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.0551</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6.600000000000003</v>
+        <v>3.059999999999999</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.0556</v>
       </c>
       <c r="F10" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0333</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0167</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0167</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7667</v>
+        <v>0.8889</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1167</v>
+        <v>0.0556</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7.810000000000006</v>
+        <v>5.229999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.0325</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0423</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0282</v>
+        <v>0.065</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0282</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0423</v>
+        <v>0.065</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8028</v>
+        <v>0.8375</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.059999999999999</v>
+        <v>9.240000000000009</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0336</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.0357</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1008</v>
+        <v>0.0238</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.0238</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1324</v>
+        <v>0.0476</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7332</v>
+        <v>0.8214</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.0476</v>
       </c>
     </row>
     <row r="13">
@@ -12068,31 +12066,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8.470000000000006</v>
+        <v>9.580000000000007</v>
       </c>
       <c r="D13" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.0115</v>
       </c>
       <c r="F13" t="n">
-        <v>0.039</v>
+        <v>0.0344</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0519</v>
+        <v>0.0459</v>
       </c>
       <c r="H13" t="n">
-        <v>0.026</v>
+        <v>0.0344</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0519</v>
+        <v>0.0459</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7662</v>
+        <v>0.7359</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0519</v>
+        <v>0.0919</v>
       </c>
     </row>
     <row r="14">
@@ -12107,7 +12105,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3.229999999999999</v>
+        <v>4.579999999999999</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -12128,64 +12126,64 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9474</v>
+        <v>0.9629</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0526</v>
+        <v>0.0371</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6.050000000000003</v>
+        <v>4.23</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0182</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0727</v>
+        <v>0.0402</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0182</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8545</v>
+        <v>0.8416</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0364</v>
+        <v>0.1182</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.829999999999998</v>
+        <v>12.67000000000001</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -12194,37 +12192,37 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.0868</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0566</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1132</v>
+        <v>0.0868</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0377</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6604</v>
+        <v>0.6788</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0377</v>
+        <v>0.06950000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8.280000000000003</v>
+        <v>11.11000000000001</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -12233,37 +12231,37 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0725</v>
+        <v>0.0495</v>
       </c>
       <c r="G17" t="n">
-        <v>0.029</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0737</v>
+        <v>0.0297</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0435</v>
+        <v>0.0594</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7234</v>
+        <v>0.7426</v>
       </c>
       <c r="K17" t="n">
-        <v>0.058</v>
+        <v>0.0396</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10.01000000000001</v>
+        <v>3.399999999999999</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -12272,37 +12270,37 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.044</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0659</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.022</v>
+        <v>0.05</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0659</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7582</v>
+        <v>0.85</v>
       </c>
       <c r="K18" t="n">
-        <v>0.044</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>8.119999999999997</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -12314,229 +12312,229 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.0419</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.0209</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.0209</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.8953</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.0209</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9.470000000000002</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0116</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0116</v>
+        <v>0.0135</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1985</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0116</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0813</v>
+        <v>0.0135</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1278</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5343</v>
+        <v>0.9055</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0232</v>
+        <v>0.0675</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.859999999999999</v>
+        <v>9.710000000000006</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.0113</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.0113</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0481</v>
+        <v>0.0227</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0248</v>
+        <v>0.034</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9023</v>
+        <v>0.8754</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0248</v>
+        <v>0.0113</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8.270000000000008</v>
+        <v>2.310000000000001</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0133</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0133</v>
+        <v>0.0476</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0399</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0266</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0399</v>
+        <v>0.0476</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8537</v>
+        <v>0.9048</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10.12</v>
+        <v>7.410000000000007</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0109</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0217</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0109</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1087</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1413</v>
+        <v>0.0148</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5109</v>
+        <v>0.865</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1957</v>
+        <v>0.1201</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8.540000000000003</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0141</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0422</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0433</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0281</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0141</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7857</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0726</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.310000000000001</v>
+        <v>1.53</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -12545,37 +12543,37 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>0.2222</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9048</v>
+        <v>0.7778</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>6.050000000000003</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -12584,10 +12582,10 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.0545</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.0182</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -12596,25 +12594,25 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.8909</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3.899999999999999</v>
+        <v>5.589999999999999</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -12623,37 +12621,37 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.0304</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0436</v>
+        <v>0.0608</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.0304</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>0.0304</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8282</v>
+        <v>0.8479</v>
       </c>
       <c r="K27" t="n">
-        <v>0.1282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1.87</v>
+        <v>8.839999999999998</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -12662,43 +12660,43 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.0385</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.0192</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1818</v>
+        <v>0.0769</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0769</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>0.0385</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.19</v>
+        <v>3.739999999999999</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>0.0294</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -12710,10 +12708,10 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>0.0294</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0.9412</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -12722,37 +12720,37 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7.049999999999999</v>
+        <v>5.940000000000003</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.0185</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0709</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0723</v>
+        <v>0.0185</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0468</v>
+        <v>0.0556</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8099</v>
+        <v>0.8704</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -12761,16 +12759,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9.959999999999999</v>
+        <v>5.609999999999999</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -12779,37 +12777,37 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1024</v>
+        <v>0.098</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0171</v>
+        <v>0.0588</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0331</v>
+        <v>0.1373</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0683</v>
+        <v>0.0784</v>
       </c>
       <c r="J31" t="n">
-        <v>0.7279</v>
+        <v>0.6078</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0512</v>
+        <v>0.0196</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7.080000000000004</v>
+        <v>2.72</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -12818,7 +12816,7 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -12827,28 +12825,28 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0311</v>
+        <v>0.1875</v>
       </c>
       <c r="J32" t="n">
-        <v>0.9534</v>
+        <v>0.6875</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3.569999999999999</v>
+        <v>6.93</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -12857,76 +12855,76 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>0.1746</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.0317</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>0.1587</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9524</v>
+        <v>0.4762</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0476</v>
+        <v>0.0159</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>10.56000000000001</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>0.0208</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.0417</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.0521</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>0.0312</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.7917</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>0.0521</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2.889999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -12938,7 +12936,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0588</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -12947,7 +12945,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9412</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -12956,16 +12954,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2.04</v>
+        <v>7.17</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -12974,22 +12972,22 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0833</v>
+        <v>0.2092</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.046</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>0.0697</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0833</v>
+        <v>0.0237</v>
       </c>
       <c r="J36" t="n">
-        <v>0.75</v>
+        <v>0.6513</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0833</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -13004,7 +13002,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5.499999999999998</v>
+        <v>5.829999999999999</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -13013,19 +13011,19 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>0.06</v>
+        <v>0.0377</v>
       </c>
       <c r="H37" t="n">
-        <v>0.02</v>
+        <v>0.0189</v>
       </c>
       <c r="I37" t="n">
-        <v>0.08</v>
+        <v>0.1132</v>
       </c>
       <c r="J37" t="n">
-        <v>0.74</v>
+        <v>0.7358</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -13034,55 +13032,55 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4.4</v>
+        <v>8.139999999999999</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>0.0135</v>
       </c>
       <c r="F38" t="n">
-        <v>0.05</v>
+        <v>0.027</v>
       </c>
       <c r="G38" t="n">
-        <v>0.175</v>
+        <v>0.0135</v>
       </c>
       <c r="H38" t="n">
-        <v>0.075</v>
+        <v>0.0946</v>
       </c>
       <c r="I38" t="n">
-        <v>0.15</v>
+        <v>0.1486</v>
       </c>
       <c r="J38" t="n">
-        <v>0.525</v>
+        <v>0.5135</v>
       </c>
       <c r="K38" t="n">
-        <v>0.025</v>
+        <v>0.1892</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>6.959999999999999</v>
+        <v>5.069999999999999</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -13091,7 +13089,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0489</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -13100,37 +13098,37 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0489</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.8046</v>
+        <v>0.9329</v>
       </c>
       <c r="K39" t="n">
-        <v>0.0977</v>
+        <v>0.06710000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8.970000000000006</v>
+        <v>3.87</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0123</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>0.0439</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -13139,40 +13137,40 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8774</v>
+        <v>0.8243</v>
       </c>
       <c r="K40" t="n">
-        <v>0.1104</v>
+        <v>0.0439</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>7.119999999999998</v>
+        <v>4.229999999999999</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0239</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0478</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>0.0402</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -13181,34 +13179,34 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.8329</v>
+        <v>0.9196</v>
       </c>
       <c r="K41" t="n">
-        <v>0.0955</v>
+        <v>0.0402</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1.19</v>
+        <v>2.54</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>0.0669</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -13217,10 +13215,10 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7143</v>
+        <v>0.9331</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -13229,16 +13227,16 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>8.590000000000003</v>
+        <v>1.35</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -13247,76 +13245,76 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>0.1259</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0512</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0128</v>
+        <v>0.1259</v>
       </c>
       <c r="J43" t="n">
-        <v>0.8719</v>
+        <v>0.7481</v>
       </c>
       <c r="K43" t="n">
-        <v>0.064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5.409999999999998</v>
+        <v>5.609999999999998</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0314</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0314</v>
+        <v>0.0196</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>0.098</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>0.1176</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0314</v>
+        <v>0.0784</v>
       </c>
       <c r="J44" t="n">
-        <v>0.8743</v>
+        <v>0.6667</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0314</v>
+        <v>0.0196</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1.7</v>
+        <v>5.23</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -13325,10 +13323,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1</v>
+        <v>0.0325</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>0.0325</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -13337,25 +13335,25 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.8</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6.799999999999999</v>
+        <v>8.380000000000004</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -13364,76 +13362,76 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.025</v>
+        <v>0.0131</v>
       </c>
       <c r="H46" t="n">
-        <v>0.05</v>
+        <v>0.0263</v>
       </c>
       <c r="I46" t="n">
-        <v>0.075</v>
+        <v>0.0131</v>
       </c>
       <c r="J46" t="n">
-        <v>0.75</v>
+        <v>0.895</v>
       </c>
       <c r="K46" t="n">
-        <v>0.05</v>
+        <v>0.0525</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>6.050000000000004</v>
+        <v>8.779999999999998</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0182</v>
+        <v>0.0194</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>0.0387</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0182</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0182</v>
+        <v>0.0194</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0182</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.9091</v>
+        <v>0.8257</v>
       </c>
       <c r="K47" t="n">
-        <v>0.0182</v>
+        <v>0.0968</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6.600000000000001</v>
+        <v>3.549999999999999</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -13442,37 +13440,37 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.05</v>
+        <v>0.093</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0167</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.0167</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0667</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.7333</v>
+        <v>0.8592</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1167</v>
+        <v>0.0479</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>8.040000000000004</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -13481,22 +13479,22 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>0.0137</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>0.0274</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>0.1231</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>0.7127</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>0.08210000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -13511,10 +13509,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3.569999999999999</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -13523,7 +13521,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.0476</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -13532,7 +13530,7 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0.9048</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -13550,7 +13548,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5.049999999999999</v>
+        <v>4.549999999999999</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -13565,16 +13563,16 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0673</v>
+        <v>0.0747</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.899</v>
+        <v>0.9253</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0337</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/public/downloads/drift_radar.xlsx
+++ b/public/downloads/drift_radar.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-28 → 2026-04-30</t>
+          <t>2026-04-29 → 2026-05-01</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39 / 50  (78 %)</t>
+          <t>36 / 50  (72 %)</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -561,7 +561,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4.0 %</t>
+          <t>4.6 %</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3.3 %</t>
+          <t>5.3 %</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4.6 %</t>
+          <t>5.3 %</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4.0 %</t>
+          <t>3.3 %</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.4×</t>
+          <t>1.6×</t>
         </is>
       </c>
     </row>
@@ -1237,10 +1237,10 @@
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="X2" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y2" t="n">
         <v>0.33</v>
@@ -1264,19 +1264,19 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
         <v>0.33</v>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
         <v>0.67</v>
@@ -1326,17 +1326,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -1359,88 +1359,88 @@
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.2077</v>
       </c>
       <c r="N3" t="n">
+        <v>0.9385</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
         <v>0.5615</v>
       </c>
-      <c r="O3" t="n">
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
         <v>0.67</v>
       </c>
-      <c r="P3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.2077</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.9385</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.33</v>
-      </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
         <v>0.67</v>
       </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AH3" t="n">
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
@@ -1452,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
@@ -1473,10 +1473,10 @@
         <v>0.67</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr"/>
@@ -1484,12 +1484,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>0.681</v>
@@ -1529,28 +1529,28 @@
         <v>0.5615</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>0.2077</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5615</v>
+        <v>0.9385</v>
       </c>
       <c r="S4" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2077</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9385</v>
+        <v>0.7935</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1559,7 +1559,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
@@ -1642,33 +1642,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0.443</v>
+        <v>0.681</v>
       </c>
       <c r="F5" t="n">
         <v>1.414</v>
       </c>
       <c r="G5" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="H5" t="n">
-        <v>0.11</v>
+        <v>0.223</v>
       </c>
       <c r="I5" t="b">
         <v>0</v>
@@ -1687,50 +1687,50 @@
         <v>0.5615</v>
       </c>
       <c r="O5" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="P5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.2077</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.9385</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0.0615</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.7923</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
@@ -1744,16 +1744,16 @@
         <v>0.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1762,16 +1762,16 @@
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1786,10 +1786,10 @@
         <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
@@ -1800,17 +1800,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -1836,7 +1836,7 @@
         <v>0.33</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>0.0615</v>
@@ -1866,16 +1866,16 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
@@ -1944,13 +1944,13 @@
         <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AW6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr"/>
@@ -1958,17 +1958,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1991,29 +1991,29 @@
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P7" t="n">
         <v>1</v>
       </c>
-      <c r="M7" t="n">
+      <c r="Q7" t="n">
         <v>0.0615</v>
       </c>
-      <c r="N7" t="n">
+      <c r="R7" t="n">
         <v>0.7923</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.5615</v>
-      </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
@@ -2033,19 +2033,19 @@
         <v>0.33</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -2069,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AQ7" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AT7" t="n">
         <v>0</v>
@@ -2102,10 +2102,10 @@
         <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
@@ -2116,21 +2116,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>0.443</v>
@@ -2149,16 +2149,16 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7923</v>
+        <v>0.5615</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -2173,16 +2173,16 @@
         <v>0.5615</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -2191,47 +2191,47 @@
         <v>0.67</v>
       </c>
       <c r="Y8" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
         <v>0.67</v>
       </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
         <v>0.67</v>
       </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1</v>
-      </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2260,10 +2260,10 @@
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
@@ -2274,17 +2274,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -2340,28 +2340,28 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7935</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -2373,19 +2373,19 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2394,16 +2394,16 @@
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2418,10 +2418,10 @@
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
@@ -2432,17 +2432,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2465,29 +2465,29 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="N10" t="n">
+        <v>0.7923</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>0.5615</v>
       </c>
-      <c r="O10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.0615</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.7923</v>
-      </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
@@ -2498,71 +2498,71 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA10" t="n">
         <v>0.67</v>
       </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK10" t="n">
         <v>1</v>
       </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AH10" t="n">
+      <c r="AL10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>0.67</v>
       </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AR10" t="n">
         <v>0</v>
       </c>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="AV10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW10" t="n">
         <v>0.67</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
@@ -2590,12 +2590,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2604,19 +2604,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0.337</v>
+        <v>0.443</v>
       </c>
       <c r="F11" t="n">
-        <v>0.707</v>
+        <v>1.414</v>
       </c>
       <c r="G11" t="n">
         <v>0.33</v>
       </c>
       <c r="H11" t="n">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
@@ -2635,16 +2635,16 @@
         <v>0.7923</v>
       </c>
       <c r="O11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7923</v>
+        <v>0.5615</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2662,10 +2662,10 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -2701,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2734,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AW11" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
@@ -2748,33 +2748,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.443</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1.414</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H12" t="n">
-        <v>0.33</v>
+        <v>0.11</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
@@ -2784,7 +2784,7 @@
         <v>0.33</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
         <v>0.0615</v>
@@ -2793,34 +2793,34 @@
         <v>0.7923</v>
       </c>
       <c r="O12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7923</v>
+        <v>0.5615</v>
       </c>
       <c r="S12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7923</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2829,13 +2829,13 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2847,13 +2847,13 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
@@ -2874,7 +2874,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
@@ -2906,42 +2906,38 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.443</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1.414</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="I13" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
         <v>0</v>
       </c>
@@ -2967,16 +2963,16 @@
         <v>0.5615</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -3068,77 +3064,73 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="b">
+      <c r="M14" t="n">
+        <v>0.0615</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.7923</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P14" t="n">
         <v>1</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>own_only</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
+      <c r="Q14" t="n">
+        <v>0.0615</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.7923</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
         <v>0.5615</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.5615</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -3147,19 +3139,19 @@
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -3171,241 +3163,229 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
         <v>1</v>
       </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
       <c r="AW14" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Pavo (100%), Marstall (67%), St. Hippolyt (67%)</t>
-        </is>
-      </c>
+      <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.0615</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.7923</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P15" t="n">
         <v>2</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="b">
+      <c r="Q15" t="n">
+        <v>0.0615</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.7923</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
         <v>1</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>own_only</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.5615</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.5615</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="X15" t="n">
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
         <v>1</v>
       </c>
-      <c r="Y15" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Pavo (100%), Havens (67%), Marstall (33%), St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3414,7 +3394,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -3433,7 +3413,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -3470,13 +3450,13 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -3491,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -3503,10 +3483,10 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -3548,7 +3528,7 @@
         <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
@@ -3556,27 +3536,31 @@
       <c r="AX16" t="n">
         <v>0</v>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>St. Hippolyt (67%), Pavo (33%)</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -3632,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -3641,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -3674,7 +3658,7 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -3720,7 +3704,7 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>Höveler (33%)</t>
+          <t>Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr"/>
@@ -3728,17 +3712,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -3798,13 +3782,13 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y18" t="n">
         <v>0.33</v>
@@ -3813,13 +3797,13 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3831,7 +3815,7 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
@@ -3858,7 +3842,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ18" t="n">
         <v>0</v>
@@ -3876,17 +3860,17 @@
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (67%), St. Hippolyt (67%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr"/>
@@ -3894,17 +3878,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -3927,7 +3911,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -3964,10 +3948,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W19" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -3979,19 +3963,19 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -4024,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
         <v>0</v>
@@ -4045,32 +4029,28 @@
         <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Höveler (67%), Havens (33%), St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -4130,25 +4110,25 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6576</v>
+        <v>0.5615</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="Y20" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>1</v>
@@ -4163,62 +4143,62 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AH20" t="n">
         <v>0.33</v>
       </c>
       <c r="AI20" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AK20" t="n">
         <v>0.67</v>
       </c>
       <c r="AL20" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW20" t="n">
         <v>1</v>
       </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
+      <c r="AX20" t="n">
         <v>0.67</v>
       </c>
-      <c r="AR20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1</v>
-      </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>Pavo (100%), Marstall (100%), St. Hippolyt (100%), Höveler (67%), Nösenberger (50%)</t>
+          <t>St. Hippolyt (100%), Pavo (67%), Marstall (67%), Eggersmann (67%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr"/>
@@ -4226,21 +4206,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -4259,7 +4239,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -4302,22 +4282,22 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -4329,37 +4309,37 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -4374,35 +4354,31 @@
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Marstall (100%), St. Hippolyt (100%), Pavo (67%), Eggersmann (67%), Höveler (33%)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -4425,7 +4401,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -4468,7 +4444,7 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -4495,7 +4471,7 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH22" t="n">
         <v>0</v>
@@ -4548,18 +4524,22 @@
       <c r="AX22" t="n">
         <v>0</v>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Pavo (33%)</t>
+        </is>
+      </c>
       <c r="AZ22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4568,7 +4548,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4587,7 +4567,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -4630,7 +4610,7 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -4639,13 +4619,13 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -4657,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
@@ -4684,7 +4664,7 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
         <v>0</v>
@@ -4702,35 +4682,31 @@
         <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
         <v>0</v>
       </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Höveler (33%)</t>
-        </is>
-      </c>
+      <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -4790,7 +4766,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -4882,17 +4858,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -4915,7 +4891,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -4952,7 +4928,7 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -4973,7 +4949,7 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -5030,7 +5006,7 @@
         <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
         <v>0</v>
@@ -5038,22 +5014,18 @@
       <c r="AX25" t="n">
         <v>0</v>
       </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5081,7 +5053,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -5139,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -5199,32 +5171,28 @@
         <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
         <v>0</v>
       </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -5284,28 +5252,28 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.6576</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -5323,16 +5291,16 @@
         <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM27" t="n">
         <v>0</v>
@@ -5344,35 +5312,35 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS27" t="n">
         <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AV27" t="n">
         <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>Pavo (33%), Höveler (33%)</t>
+          <t>Marstall (100%), Höveler (100%), Pavo (50%), Nösenberger (50%), St. Hippolyt (50%)</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr"/>
@@ -5380,17 +5348,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -5413,7 +5381,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -5450,13 +5418,13 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -5489,7 +5457,7 @@
         <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AJ28" t="n">
         <v>0</v>
@@ -5536,27 +5504,31 @@
       <c r="AX28" t="n">
         <v>0</v>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Pavo (33%)</t>
+        </is>
+      </c>
       <c r="AZ28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -5618,16 +5590,16 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -5645,13 +5617,13 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
         <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
         <v>0</v>
@@ -5660,7 +5632,7 @@
         <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
         <v>0</v>
@@ -5672,7 +5644,7 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ29" t="n">
         <v>0</v>
@@ -5700,7 +5672,7 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%)</t>
+          <t>Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr"/>
@@ -5708,21 +5680,21 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -5787,7 +5759,7 @@
         <v>0.33</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -5811,19 +5783,19 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5866,7 +5838,7 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr"/>
@@ -5874,17 +5846,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -5907,7 +5879,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -5950,10 +5922,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -5977,19 +5949,19 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -6030,18 +6002,22 @@
       <c r="AX31" t="n">
         <v>0</v>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Pavo (33%), Marstall (33%)</t>
+        </is>
+      </c>
       <c r="AZ31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6050,7 +6026,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -6069,7 +6045,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -6115,7 +6091,7 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -6148,7 +6124,7 @@
         <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK32" t="n">
         <v>0</v>
@@ -6192,23 +6168,27 @@
       <c r="AX32" t="n">
         <v>0</v>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Marstall (33%)</t>
+        </is>
+      </c>
       <c r="AZ32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -6268,7 +6248,7 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -6277,19 +6257,19 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Z33" t="n">
         <v>0.67</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -6310,10 +6290,10 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6331,7 +6311,7 @@
         <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
         <v>0</v>
@@ -6346,17 +6326,17 @@
         <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AX33" t="n">
         <v>0</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>Marstall (100%), Eggersmann (67%), St. Hippolyt (67%), Höveler (33%)</t>
+          <t>Eggersmann (67%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr"/>
@@ -6364,12 +6344,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6378,7 +6358,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -6434,7 +6414,7 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -6443,13 +6423,13 @@
         <v>0.33</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -6467,16 +6447,16 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH34" t="n">
         <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK34" t="n">
         <v>0</v>
@@ -6494,7 +6474,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AQ34" t="n">
         <v>0</v>
@@ -6522,7 +6502,7 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Höveler (67%), Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr"/>
@@ -6530,17 +6510,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -6606,37 +6586,37 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
         <v>1</v>
       </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
         <v>0.67</v>
       </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -6645,7 +6625,7 @@
         <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6654,7 +6634,7 @@
         <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -6663,32 +6643,32 @@
         <v>0</v>
       </c>
       <c r="AQ35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
         <v>1</v>
       </c>
-      <c r="AR35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>0</v>
-      </c>
       <c r="AW35" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AX35" t="n">
         <v>0</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>Höveler (100%), St. Hippolyt (67%), Pavo (33%), Eggersmann (33%)</t>
+          <t>St. Hippolyt (100%), Pavo (67%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr"/>
@@ -6696,17 +6676,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -6729,7 +6709,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -6772,13 +6752,13 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -6787,7 +6767,7 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -6802,7 +6782,7 @@
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -6820,7 +6800,7 @@
         <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -6847,36 +6827,32 @@
         <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
         <v>0</v>
       </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Pavo (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -6895,7 +6871,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -6938,22 +6914,22 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -6965,7 +6941,7 @@
         <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH37" t="n">
         <v>0</v>
@@ -6974,19 +6950,19 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
@@ -6995,7 +6971,7 @@
         <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR37" t="n">
         <v>0</v>
@@ -7010,31 +6986,35 @@
         <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX37" t="n">
         <v>0</v>
       </c>
-      <c r="AY37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Marstall (67%), Eggersmann (67%), St. Hippolyt (67%), Pavo (33%), Höveler (33%)</t>
+        </is>
+      </c>
       <c r="AZ37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -7057,7 +7037,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -7094,28 +7074,28 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -7127,16 +7107,16 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK38" t="n">
         <v>0</v>
@@ -7148,13 +7128,13 @@
         <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ38" t="n">
         <v>0</v>
@@ -7175,32 +7155,36 @@
         <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX38" t="n">
         <v>0</v>
       </c>
-      <c r="AY38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Pavo (33%), Marstall (33%), Eggersmann (33%), Höveler (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -7256,28 +7240,28 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X39" t="n">
         <v>0.33</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -7286,13 +7270,13 @@
         <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -7301,7 +7285,7 @@
         <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -7316,7 +7300,7 @@
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ39" t="n">
         <v>0</v>
@@ -7334,17 +7318,17 @@
         <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX39" t="n">
         <v>0</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (67%), St. Hippolyt (67%), Havens (33%), Pavo (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr"/>
@@ -7352,21 +7336,21 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -7428,7 +7412,7 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y40" t="n">
         <v>0.33</v>
@@ -7437,13 +7421,13 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -7455,7 +7439,7 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH40" t="n">
         <v>0</v>
@@ -7482,7 +7466,7 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
         <v>0</v>
@@ -7500,17 +7484,17 @@
         <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX40" t="n">
         <v>0</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>Marstall (33%), Höveler (33%)</t>
+          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr"/>
@@ -7518,17 +7502,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -7591,16 +7575,16 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0.33</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -7609,37 +7593,37 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
         <v>0</v>
@@ -7669,14 +7653,14 @@
         <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
         <v>0</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>Pavo (100%), St. Hippolyt (100%), Havens (33%), Marstall (33%), Eggersmann (33%)</t>
+          <t>Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr"/>
@@ -7684,12 +7668,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7698,7 +7682,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -7717,7 +7701,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -7760,10 +7744,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -7790,13 +7774,13 @@
         <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
         <v>0</v>
@@ -7840,27 +7824,23 @@
       <c r="AX42" t="n">
         <v>0</v>
       </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Pavo (33%), Marstall (33%)</t>
-        </is>
-      </c>
+      <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -7883,7 +7863,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -7920,22 +7900,22 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
@@ -7953,7 +7933,7 @@
         <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
         <v>0</v>
@@ -7962,7 +7942,7 @@
         <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
         <v>0</v>
@@ -7980,7 +7960,7 @@
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AQ43" t="n">
         <v>0</v>
@@ -8006,27 +7986,23 @@
       <c r="AX43" t="n">
         <v>0</v>
       </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Marstall (67%), Höveler (67%), Pavo (33%)</t>
-        </is>
-      </c>
+      <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -8086,7 +8062,7 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -8178,17 +8154,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -8251,10 +8227,10 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="n">
         <v>0.33</v>
@@ -8269,22 +8245,22 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AF45" t="n">
         <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -8326,7 +8302,7 @@
         <v>0</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW45" t="n">
         <v>0</v>
@@ -8336,7 +8312,7 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>Marstall (33%)</t>
+          <t>Pavo (100%), Havens (33%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr"/>
@@ -8344,21 +8320,21 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -8414,28 +8390,28 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -8444,13 +8420,13 @@
         <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -8459,7 +8435,7 @@
         <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -8474,7 +8450,7 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ46" t="n">
         <v>0</v>
@@ -8495,14 +8471,14 @@
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AX46" t="n">
         <v>0</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>Havens (33%), Marstall (33%), Höveler (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (100%), Marstall (67%), St. Hippolyt (67%)</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr"/>
@@ -8589,7 +8565,7 @@
         <v>0.67</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Z47" t="n">
         <v>0.67</v>
@@ -8613,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AH47" t="n">
         <v>0.67</v>
@@ -8625,13 +8601,13 @@
         <v>0.33</v>
       </c>
       <c r="AK47" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" t="n">
         <v>0.67</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>0.33</v>
       </c>
       <c r="AN47" t="n">
         <v>0.67</v>
@@ -8668,7 +8644,7 @@
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>Pavo (67%), Marstall (67%), Eggersmann (67%), St. Hippolyt (67%)</t>
+          <t>Pavo (67%), Eggersmann (67%), St. Hippolyt (67%), Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr"/>
@@ -8676,12 +8652,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -8709,7 +8685,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -8761,13 +8737,13 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -8806,7 +8782,7 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ48" t="n">
         <v>0</v>
@@ -8824,7 +8800,7 @@
         <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW48" t="n">
         <v>0</v>
@@ -8832,18 +8808,22 @@
       <c r="AX48" t="n">
         <v>0</v>
       </c>
-      <c r="AY48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Höveler (100%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -8871,7 +8851,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -8908,7 +8888,7 @@
         <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
         <v>0</v>
@@ -8920,16 +8900,16 @@
         <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB49" t="n">
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -8962,7 +8942,7 @@
         <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -8971,7 +8951,7 @@
         <v>0</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR49" t="n">
         <v>0</v>
@@ -8989,32 +8969,36 @@
         <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX49" t="n">
         <v>0</v>
       </c>
-      <c r="AY49" t="inlineStr"/>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Höveler (100%), St. Hippolyt (67%), Eggersmann (33%)</t>
+        </is>
+      </c>
       <c r="AZ49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -9076,22 +9060,22 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB50" t="n">
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -9103,7 +9087,7 @@
         <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH50" t="n">
         <v>0</v>
@@ -9115,7 +9099,7 @@
         <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -9124,13 +9108,13 @@
         <v>0</v>
       </c>
       <c r="AN50" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ50" t="n">
         <v>0</v>
@@ -9151,14 +9135,14 @@
         <v>0</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX50" t="n">
         <v>0</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>Marstall (67%), Eggersmann (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr"/>
@@ -9166,17 +9150,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -9242,19 +9226,19 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>1</v>
@@ -9272,31 +9256,31 @@
         <v>0.33</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK51" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ51" t="n">
         <v>0</v>
@@ -9305,7 +9289,7 @@
         <v>0</v>
       </c>
       <c r="AS51" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AT51" t="n">
         <v>0</v>
@@ -9324,7 +9308,7 @@
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>Höveler (100%), St. Hippolyt (100%), Marstall (67%), Pavo (33%), Nösenberger (33%)</t>
+          <t>St. Hippolyt (100%), Pavo (67%), Marstall (33%), Eggersmann (33%)</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr"/>
@@ -9352,7 +9336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9456,17 +9440,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -9477,10 +9461,10 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="H3" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -9490,12 +9474,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9504,7 +9488,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>0.681</v>
@@ -9514,41 +9498,41 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="I4" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0.443</v>
+        <v>0.681</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9558,17 +9542,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -9592,17 +9576,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -9613,10 +9597,10 @@
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9626,51 +9610,51 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>0.443</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -9694,17 +9678,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -9715,10 +9699,10 @@
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -9728,12 +9712,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -9742,25 +9726,161 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>0.337</v>
+        <v>0.443</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>0.33</v>
       </c>
       <c r="H11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pferde Vitamine und Mineralstoffe</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Gelenkunterstützung für Pferde</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Natürliche Pferdepflege</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pferde Nahrungsergänzung</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E11">
+  <conditionalFormatting sqref="E2:E15">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -9782,7 +9902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9852,21 +9972,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -9887,28 +10007,28 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Pavo (100%), Marstall (67%), St. Hippolyt (67%)</t>
+          <t>St. Hippolyt (67%), Pavo (33%)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -9929,24 +10049,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Pavo (100%), Havens (67%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -9971,28 +10091,28 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Höveler (33%)</t>
+          <t>Pavo (67%), St. Hippolyt (67%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -10013,24 +10133,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Marstall (33%), St. Hippolyt (33%)</t>
+          <t>St. Hippolyt (100%), Pavo (67%), Marstall (67%), Eggersmann (67%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -10055,7 +10175,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Höveler (67%), Havens (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
     </row>
@@ -10097,28 +10217,28 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Pavo (100%), Marstall (100%), St. Hippolyt (100%), Höveler (67%), Nösenberger (50%)</t>
+          <t>Marstall (100%), Höveler (100%), Pavo (50%), Nösenberger (50%), St. Hippolyt (50%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -10139,24 +10259,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Marstall (100%), St. Hippolyt (100%), Pavo (67%), Eggersmann (67%), Höveler (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -10181,28 +10301,28 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Höveler (33%)</t>
+          <t>Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -10223,24 +10343,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>St. Hippolyt (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -10265,28 +10385,28 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>St. Hippolyt (33%)</t>
+          <t>Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -10307,28 +10427,28 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Pavo (33%), Höveler (33%)</t>
+          <t>Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10349,24 +10469,24 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%)</t>
+          <t>Eggersmann (67%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -10391,24 +10511,24 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%)</t>
+          <t>Höveler (67%), Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -10433,28 +10553,28 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Marstall (100%), Eggersmann (67%), St. Hippolyt (67%), Höveler (33%)</t>
+          <t>St. Hippolyt (100%), Pavo (67%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -10475,24 +10595,24 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Marstall (67%), Eggersmann (67%), St. Hippolyt (67%), Pavo (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -10517,24 +10637,24 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Höveler (100%), St. Hippolyt (67%), Pavo (33%), Eggersmann (33%)</t>
+          <t>Pavo (33%), Marstall (33%), Eggersmann (33%), Höveler (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -10559,28 +10679,28 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Pavo (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (67%), St. Hippolyt (67%), Havens (33%), Pavo (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -10601,28 +10721,28 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10643,24 +10763,24 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Marstall (33%), Höveler (33%)</t>
+          <t>Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -10685,19 +10805,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Pavo (100%), St. Hippolyt (100%), Havens (33%), Marstall (33%), Eggersmann (33%)</t>
+          <t>Pavo (100%), Havens (33%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -10706,7 +10826,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -10727,24 +10847,24 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%)</t>
+          <t>Pavo (100%), Marstall (67%), St. Hippolyt (67%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -10769,19 +10889,19 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Marstall (67%), Höveler (67%), Pavo (33%)</t>
+          <t>Pavo (67%), Eggersmann (67%), St. Hippolyt (67%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -10811,24 +10931,24 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Marstall (33%)</t>
+          <t>Höveler (100%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -10853,19 +10973,19 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Havens (33%), Marstall (33%), Höveler (33%), St. Hippolyt (33%)</t>
+          <t>Höveler (100%), St. Hippolyt (67%), Eggersmann (33%)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -10874,7 +10994,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -10895,24 +11015,24 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Pavo (67%), Marstall (67%), Eggersmann (67%), St. Hippolyt (67%)</t>
+          <t>Pavo (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -10937,54 +11057,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Marstall (67%), Eggersmann (33%), St. Hippolyt (33%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>2</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>own_only</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Höveler (100%), St. Hippolyt (100%), Marstall (67%), Pavo (33%), Nösenberger (33%)</t>
+          <t>St. Hippolyt (100%), Pavo (67%), Marstall (33%), Eggersmann (33%)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E28">
+  <conditionalFormatting sqref="E2:E27">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -11006,7 +11084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11076,12 +11154,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -11114,17 +11192,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -11152,21 +11230,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -11190,17 +11268,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -11228,17 +11306,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -11266,17 +11344,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -11304,21 +11382,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -11342,17 +11420,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -11380,17 +11458,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -11418,17 +11496,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -11453,84 +11531,8 @@
       </c>
       <c r="J11" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E13">
+  <conditionalFormatting sqref="E2:E11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -11637,124 +11639,124 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.940000000000007</v>
+        <v>9.490000000000007</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0277</v>
+        <v>0.0232</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0277</v>
+        <v>0.0232</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0554</v>
+        <v>0.0464</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0139</v>
+        <v>0.0116</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0277</v>
+        <v>0.0232</v>
       </c>
       <c r="J2" t="n">
-        <v>0.806</v>
+        <v>0.8377</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0416</v>
+        <v>0.0348</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.199999999999999</v>
+        <v>4.739999999999999</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.0232</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.0232</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.919</v>
+        <v>0.884</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0405</v>
+        <v>0.0696</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.160000000000005</v>
+        <v>2.540000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0154</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0307</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0307</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0461</v>
+        <v>0.0551</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0154</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.831</v>
+        <v>0.8898</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0307</v>
+        <v>0.0551</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.53</v>
+        <v>6.579999999999998</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -11769,13 +11771,13 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.0258</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0.9742</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -11784,61 +11786,61 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4.86</v>
+        <v>3.23</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0226</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0226</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.1579</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0226</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8868</v>
+        <v>0.8421</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.379999999999999</v>
+        <v>6.059999999999999</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.0281</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -11847,76 +11849,76 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.0561</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0.8878</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.0281</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.830000000000002</v>
+        <v>8.250000000000009</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.0133</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0377</v>
+        <v>0.0267</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0189</v>
+        <v>0.0133</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0566</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0377</v>
+        <v>0.08</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8491</v>
+        <v>0.84</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.0267</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.540000000000001</v>
+        <v>3.049999999999999</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.0557</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -11925,265 +11927,265 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0551</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8898</v>
+        <v>0.9443</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0551</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.059999999999999</v>
+        <v>7.150000000000006</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0556</v>
+        <v>0.0154</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.0308</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.0462</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.0308</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8889</v>
+        <v>0.8462</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0556</v>
+        <v>0.0308</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5.229999999999999</v>
+        <v>3.379999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0325</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.065</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8375</v>
+        <v>0.8994</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.1006</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9.240000000000009</v>
+        <v>10.19</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0357</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0238</v>
+        <v>0.0334</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0238</v>
+        <v>0.0167</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0476</v>
+        <v>0.0667</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.0667</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8214</v>
+        <v>0.7831</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0476</v>
+        <v>0.0334</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9.580000000000007</v>
+        <v>8.810000000000009</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0115</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0344</v>
+        <v>0.0375</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0459</v>
+        <v>0.0375</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0344</v>
+        <v>0.025</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0459</v>
+        <v>0.0375</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7359</v>
+        <v>0.8002</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0919</v>
+        <v>0.0375</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4.579999999999999</v>
+        <v>8.470000000000006</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.0649</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9629</v>
+        <v>0.7662</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0371</v>
+        <v>0.0519</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4.23</v>
+        <v>4.739999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.0359</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.0717</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.0717</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8416</v>
+        <v>0.8207</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12.67000000000001</v>
+        <v>5.069999999999999</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -12192,76 +12194,76 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0868</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.008699999999999999</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0868</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0.06950000000000001</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6788</v>
+        <v>0.9329</v>
       </c>
       <c r="K16" t="n">
-        <v>0.06950000000000001</v>
+        <v>0.06710000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11.11000000000001</v>
+        <v>3.879999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.0438</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0495</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.07920000000000001</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0297</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0594</v>
+        <v>0.1753</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7426</v>
+        <v>0.6933</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0396</v>
+        <v>0.0876</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3.399999999999999</v>
+        <v>8.940000000000007</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -12276,31 +12278,31 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.0369</v>
       </c>
       <c r="J18" t="n">
-        <v>0.85</v>
+        <v>0.9016</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1</v>
+        <v>0.0615</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.119999999999997</v>
+        <v>6.930000000000005</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -12309,115 +12311,115 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.0317</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0419</v>
+        <v>0.0159</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0209</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0209</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8953</v>
+        <v>0.8889</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0209</v>
+        <v>0.0635</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8.890000000000001</v>
+        <v>9.480000000000006</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0135</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.0116</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.0232</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0135</v>
+        <v>0.0116</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.0348</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9055</v>
+        <v>0.9072</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0675</v>
+        <v>0.0116</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>9.710000000000006</v>
+        <v>2.53</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0113</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0113</v>
+        <v>0.0435</v>
       </c>
       <c r="G21" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0227</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.034</v>
+        <v>0.0435</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8754</v>
+        <v>0.913</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.310000000000001</v>
+        <v>6.490000000000001</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -12426,37 +12428,37 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0476</v>
+        <v>0.0339</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.0847</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.1017</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0476</v>
+        <v>0.0508</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9048</v>
+        <v>0.7119</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.0169</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.410000000000007</v>
+        <v>5.83</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -12465,76 +12467,76 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.0566</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.0377</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.0189</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0148</v>
+        <v>0.0755</v>
       </c>
       <c r="J23" t="n">
-        <v>0.865</v>
+        <v>0.8113</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1201</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>8.910000000000002</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>0.0123</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>0.0247</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.0123</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.0741</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>0.1358</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.5432</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>0.1975</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.53</v>
+        <v>8.370000000000008</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -12543,115 +12545,115 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.0394</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.0131</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2222</v>
+        <v>0.0394</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>0.1183</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7778</v>
+        <v>0.7109</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>0.0789</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6.050000000000003</v>
+        <v>10.24000000000001</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.0215</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0545</v>
+        <v>0.0322</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0182</v>
+        <v>0.043</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>0.0322</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.0322</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8909</v>
+        <v>0.7637</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0364</v>
+        <v>0.0752</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5.589999999999999</v>
+        <v>7.320000000000001</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>0.0164</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0304</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0608</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0304</v>
+        <v>0.0164</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0304</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8479</v>
+        <v>0.9508</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>0.0164</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8.839999999999998</v>
+        <v>6.049999999999999</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -12660,163 +12662,163 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0385</v>
+        <v>0.1273</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0192</v>
+        <v>0.0364</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0769</v>
+        <v>0.1091</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0769</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.75</v>
+        <v>0.5818</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0385</v>
+        <v>0.0545</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3.739999999999999</v>
+        <v>12.99</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.0169</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0294</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.0423</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.0508</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.0254</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0294</v>
+        <v>0.0593</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9412</v>
+        <v>0.7714</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>0.0339</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5.940000000000003</v>
+        <v>11.46</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0185</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0185</v>
+        <v>0.048</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0556</v>
+        <v>0.048</v>
       </c>
       <c r="I30" t="n">
-        <v>0.037</v>
+        <v>0.0288</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8704</v>
+        <v>0.7792</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>0.0384</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5.609999999999999</v>
+        <v>7.040000000000006</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.0156</v>
       </c>
       <c r="F31" t="n">
-        <v>0.098</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0588</v>
+        <v>0.0156</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1373</v>
+        <v>0.0469</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0784</v>
+        <v>0.0469</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6078</v>
+        <v>0.875</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2.72</v>
+        <v>2.21</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>0.0769</v>
       </c>
       <c r="F32" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -12825,10 +12827,10 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1875</v>
+        <v>0.0769</v>
       </c>
       <c r="J32" t="n">
-        <v>0.6875</v>
+        <v>0.8462</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -12837,16 +12839,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6.93</v>
+        <v>1.36</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -12855,82 +12857,82 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1746</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0317</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1587</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.4762</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>10.56000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0208</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0417</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0521</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0312</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0.7917</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0521</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.36</v>
+        <v>4.399999999999999</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>0.0386</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -12945,25 +12947,25 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0.9227</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>0.0386</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7.17</v>
+        <v>5.419999999999999</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -12972,19 +12974,19 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2092</v>
+        <v>0.0314</v>
       </c>
       <c r="G36" t="n">
-        <v>0.046</v>
+        <v>0.0314</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0697</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0237</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.6513</v>
+        <v>0.9373</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -12993,16 +12995,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5.829999999999999</v>
+        <v>5.610000000000001</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -13011,76 +13013,76 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.2157</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0377</v>
+        <v>0.0588</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0189</v>
+        <v>0.1569</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1132</v>
+        <v>0.1569</v>
       </c>
       <c r="J37" t="n">
-        <v>0.7358</v>
+        <v>0.3922</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>0.0196</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8.139999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.0135</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.027</v>
+        <v>0.1758</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0135</v>
+        <v>0.0387</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0946</v>
+        <v>0.0586</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1486</v>
+        <v>0.0199</v>
       </c>
       <c r="J38" t="n">
-        <v>0.5135</v>
+        <v>0.7069</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1892</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5.069999999999999</v>
+        <v>8.590000000000003</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -13092,34 +13094,34 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.0128</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>0.0256</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>0.0256</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9329</v>
+        <v>0.8847</v>
       </c>
       <c r="K39" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0512</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3.87</v>
+        <v>3.399999999999999</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -13128,37 +13130,37 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0439</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I40" t="n">
-        <v>0.08790000000000001</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8243</v>
+        <v>0.85</v>
       </c>
       <c r="K40" t="n">
-        <v>0.0439</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4.229999999999999</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -13170,7 +13172,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -13179,34 +13181,34 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.9196</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0.0402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2.54</v>
+        <v>4.249999999999999</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0669</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -13215,10 +13217,10 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="J42" t="n">
-        <v>0.9331</v>
+        <v>0.8</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -13227,55 +13229,55 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1.35</v>
+        <v>13.67</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1259</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>0.0241</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>0.0885</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1259</v>
+        <v>0.0885</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7481</v>
+        <v>0.654</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>0.0402</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5.609999999999998</v>
+        <v>3.869999999999999</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -13284,37 +13286,37 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0196</v>
+        <v>0.0439</v>
       </c>
       <c r="G44" t="n">
-        <v>0.098</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1176</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0784</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0.6667</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>0.0196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5.23</v>
+        <v>2.53</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -13323,10 +13325,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0325</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0325</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -13335,25 +13337,25 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.7352</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>0.2648</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8.380000000000004</v>
+        <v>6.249999999999998</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -13365,19 +13367,19 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0131</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0263</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0131</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0.895</v>
+        <v>0.9728</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0525</v>
+        <v>0.0272</v>
       </c>
     </row>
     <row r="47">
@@ -13392,46 +13394,46 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8.779999999999998</v>
+        <v>8.299999999999997</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0194</v>
+        <v>0.0205</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0387</v>
+        <v>0.041</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0194</v>
+        <v>0.0205</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8257</v>
+        <v>0.8157</v>
       </c>
       <c r="K47" t="n">
-        <v>0.0968</v>
+        <v>0.1024</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3.549999999999999</v>
+        <v>6.269999999999998</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -13440,37 +13442,37 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.093</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>0.0542</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>0.0271</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8592</v>
+        <v>0.8915</v>
       </c>
       <c r="K48" t="n">
-        <v>0.0479</v>
+        <v>0.0271</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8.040000000000004</v>
+        <v>2.869999999999999</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -13479,37 +13481,37 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.041</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0137</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.0274</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1231</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.7127</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>0.08210000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>7.079999999999998</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -13518,19 +13520,19 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>0.0466</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>0.8814</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -13539,16 +13541,16 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4.549999999999999</v>
+        <v>5.729999999999999</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -13560,19 +13562,19 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>0.0297</v>
       </c>
       <c r="H51" t="n">
-        <v>0.0747</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.9253</v>
+        <v>0.9407</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>0.0297</v>
       </c>
     </row>
   </sheetData>

--- a/public/downloads/drift_radar.xlsx
+++ b/public/downloads/drift_radar.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-29 → 2026-05-01</t>
+          <t>2026-04-30 → 2026-05-02</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36 / 50  (72 %)</t>
+          <t>33 / 50  (66 %)</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -561,7 +561,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4.6 %</t>
+          <t>5.8 %</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5.3 %</t>
+          <t>6.6 %</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5.3 %</t>
+          <t>7.3 %</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.6×</t>
+          <t>2.2×</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
+          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
+          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -1201,16 +1201,16 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.4385</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5615</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1225,62 +1225,62 @@
         <v>0.5615</v>
       </c>
       <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.4385</v>
-      </c>
-      <c r="V2" t="n">
+      <c r="Y2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
         <v>1</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
         <v>0.67</v>
       </c>
-      <c r="X2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AL2" t="n">
         <v>0.33</v>
       </c>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
@@ -1326,49 +1326,49 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
+          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
+          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.681</v>
+        <v>0.912</v>
       </c>
       <c r="F3" t="n">
         <v>1.414</v>
       </c>
       <c r="G3" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.223</v>
+        <v>0.333</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2077</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9385</v>
+        <v>0.5615</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1383,25 +1383,25 @@
         <v>0.5615</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.4385</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5615</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="X3" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
@@ -1422,22 +1422,22 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AL3" t="n">
         <v>0.33</v>
@@ -1470,13 +1470,13 @@
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AW3" t="n">
         <v>1</v>
       </c>
       <c r="AX3" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr"/>
@@ -1484,17 +1484,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1550,28 +1550,28 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7935</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1583,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -1595,7 +1595,7 @@
         <v>0.33</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1610,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ4" t="n">
         <v>0</v>
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AT4" t="n">
         <v>0</v>
@@ -1631,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
@@ -1642,21 +1642,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>0.681</v>
@@ -1714,10 +1714,10 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1741,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -1753,7 +1753,7 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1786,10 +1786,10 @@
         <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
@@ -1800,94 +1800,94 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.443</v>
+        <v>0.681</v>
       </c>
       <c r="F6" t="n">
         <v>1.414</v>
       </c>
       <c r="G6" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="H6" t="n">
-        <v>0.11</v>
+        <v>0.223</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.2077</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.9385</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="Y6" t="n">
         <v>1</v>
       </c>
-      <c r="M6" t="n">
-        <v>0.0615</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.7923</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.5615</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1899,19 +1899,19 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1920,13 +1920,13 @@
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AQ6" t="n">
         <v>0</v>
@@ -1944,10 +1944,10 @@
         <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
@@ -1958,61 +1958,61 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0.443</v>
+        <v>0.592</v>
       </c>
       <c r="F7" t="n">
-        <v>1.414</v>
+        <v>0.821</v>
       </c>
       <c r="G7" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="H7" t="n">
-        <v>0.11</v>
+        <v>0.333</v>
       </c>
       <c r="I7" t="b">
         <v>0</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="O7" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0615</v>
+        <v>0.2077</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7923</v>
+        <v>0.9385</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2033,79 +2033,79 @@
         <v>0.33</v>
       </c>
       <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
         <v>0.67</v>
       </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
         <v>0.67</v>
       </c>
-      <c r="AB7" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
       <c r="AW7" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
@@ -2116,21 +2116,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0.443</v>
@@ -2149,16 +2149,16 @@
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -2173,37 +2173,37 @@
         <v>0.5615</v>
       </c>
       <c r="S8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7923</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -2215,13 +2215,13 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
@@ -2242,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ8" t="n">
         <v>0</v>
@@ -2260,7 +2260,7 @@
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
@@ -2274,17 +2274,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -2340,28 +2340,28 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.7935</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -2373,19 +2373,19 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2394,16 +2394,16 @@
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2421,7 +2421,7 @@
         <v>0.33</v>
       </c>
       <c r="AW9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
@@ -2432,21 +2432,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>0.443</v>
@@ -2465,16 +2465,16 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7923</v>
+        <v>0.5615</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -2489,61 +2489,61 @@
         <v>0.5615</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y10" t="n">
         <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
         <v>0.67</v>
       </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>1</v>
@@ -2552,7 +2552,7 @@
         <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2561,7 +2561,7 @@
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
@@ -2590,17 +2590,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2623,40 +2623,40 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P11" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="Q11" t="n">
         <v>0.0615</v>
       </c>
-      <c r="N11" t="n">
+      <c r="R11" t="n">
         <v>0.7923</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
         <v>0.5615</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -2671,13 +2671,13 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2695,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ11" t="n">
         <v>0</v>
@@ -2734,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
@@ -2748,17 +2748,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -2784,7 +2784,7 @@
         <v>0.33</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0.0615</v>
@@ -2814,28 +2814,28 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2847,7 +2847,7 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
@@ -2856,28 +2856,28 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -2892,10 +2892,10 @@
         <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
@@ -2906,12 +2906,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>0.443</v>
@@ -2939,16 +2939,16 @@
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2963,22 +2963,22 @@
         <v>0.5615</v>
       </c>
       <c r="S13" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7923</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -2993,7 +2993,7 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -3005,10 +3005,10 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -3050,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
@@ -3064,33 +3064,33 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>0.337</v>
+        <v>0.443</v>
       </c>
       <c r="F14" t="n">
-        <v>0.707</v>
+        <v>1.414</v>
       </c>
       <c r="G14" t="n">
         <v>0.33</v>
       </c>
       <c r="H14" t="n">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -3100,7 +3100,7 @@
         <v>0.33</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
         <v>0.0615</v>
@@ -3109,16 +3109,16 @@
         <v>0.7923</v>
       </c>
       <c r="O14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7923</v>
+        <v>0.5615</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3130,28 +3130,28 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -3163,16 +3163,16 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -3190,7 +3190,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
         <v>0</v>
@@ -3208,7 +3208,7 @@
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
         <v>0</v>
@@ -3222,12 +3222,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3236,19 +3236,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>0.337</v>
+        <v>0.443</v>
       </c>
       <c r="F15" t="n">
-        <v>0.707</v>
+        <v>1.414</v>
       </c>
       <c r="G15" t="n">
         <v>0.33</v>
       </c>
       <c r="H15" t="n">
-        <v>0.22</v>
+        <v>0.11</v>
       </c>
       <c r="I15" t="b">
         <v>0</v>
@@ -3267,16 +3267,16 @@
         <v>0.7923</v>
       </c>
       <c r="O15" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7923</v>
+        <v>0.5615</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3294,7 +3294,7 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y15" t="n">
         <v>0.33</v>
@@ -3321,7 +3321,7 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -3366,10 +3366,10 @@
         <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW15" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
@@ -3380,53 +3380,49 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.443</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1.414</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="I16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>own_only</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -3471,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -3486,7 +3482,7 @@
         <v>0.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -3528,7 +3524,7 @@
         <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
@@ -3536,52 +3532,44 @@
       <c r="AX16" t="n">
         <v>0</v>
       </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>St. Hippolyt (67%), Pavo (33%)</t>
-        </is>
-      </c>
+      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.443</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.414</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>own_only</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
         <v>0</v>
       </c>
@@ -3607,16 +3595,16 @@
         <v>0.5615</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.7923</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -3625,13 +3613,13 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -3658,7 +3646,7 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -3676,7 +3664,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
         <v>0</v>
@@ -3702,52 +3690,44 @@
       <c r="AX17" t="n">
         <v>0</v>
       </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Marstall (33%), Höveler (33%)</t>
-        </is>
-      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.443</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.414</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>own_only</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
         <v>0</v>
       </c>
@@ -3761,16 +3741,16 @@
         <v>0.5615</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3782,13 +3762,13 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
         <v>0.33</v>
@@ -3797,13 +3777,13 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3815,19 +3795,19 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3842,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
         <v>0</v>
@@ -3860,39 +3840,35 @@
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Pavo (67%), St. Hippolyt (67%), Marstall (33%), Höveler (33%)</t>
-        </is>
-      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -3911,7 +3887,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -3954,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -3987,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
@@ -4034,7 +4010,11 @@
       <c r="AX19" t="n">
         <v>0</v>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Pavo (33%)</t>
+        </is>
+      </c>
       <c r="AZ19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -4119,13 +4099,13 @@
         <v>0.67</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="n">
         <v>0.67</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -4155,10 +4135,10 @@
         <v>0.33</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AM20" t="n">
         <v>0</v>
@@ -4167,13 +4147,13 @@
         <v>0.67</v>
       </c>
       <c r="AO20" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -4194,11 +4174,11 @@
         <v>1</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Marstall (67%), Eggersmann (67%), Höveler (33%)</t>
+          <t>Marstall (100%), St. Hippolyt (100%), Pavo (67%), Eggersmann (67%), Höveler (67%)</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr"/>
@@ -4206,17 +4186,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -4239,7 +4219,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -4282,7 +4262,7 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -4309,7 +4289,7 @@
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH21" t="n">
         <v>0</v>
@@ -4362,23 +4342,27 @@
       <c r="AX21" t="n">
         <v>0</v>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Pavo (33%)</t>
+        </is>
+      </c>
       <c r="AZ21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -4401,7 +4385,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -4444,7 +4428,7 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -4471,7 +4455,7 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
         <v>0</v>
@@ -4524,11 +4508,7 @@
       <c r="AX22" t="n">
         <v>0</v>
       </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Pavo (33%)</t>
-        </is>
-      </c>
+      <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -5273,7 +5253,7 @@
         <v>0.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -5285,7 +5265,7 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
         <v>0</v>
@@ -5315,7 +5295,7 @@
         <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AR27" t="n">
         <v>1</v>
@@ -5336,11 +5316,11 @@
         <v>0.33</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>Marstall (100%), Höveler (100%), Pavo (50%), Nösenberger (50%), St. Hippolyt (50%)</t>
+          <t>Marstall (100%), Höveler (100%), Pavo (50%), Nösenberger (50%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr"/>
@@ -5418,13 +5398,13 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0.5615</v>
+        <v>0.6576</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -5457,7 +5437,7 @@
         <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AJ28" t="n">
         <v>0</v>
@@ -5506,7 +5486,7 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Pavo (50%)</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr"/>
@@ -5514,17 +5494,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -5590,10 +5570,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -5605,7 +5585,7 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -5617,7 +5597,7 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH29" t="n">
         <v>0</v>
@@ -5626,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5665,14 +5645,14 @@
         <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX29" t="n">
         <v>0</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>Höveler (33%)</t>
+          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr"/>
@@ -5680,12 +5660,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5694,7 +5674,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -5756,7 +5736,7 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -5765,7 +5745,7 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -5789,7 +5769,7 @@
         <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
         <v>0</v>
@@ -5810,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ30" t="n">
         <v>0</v>
@@ -5838,7 +5818,7 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr"/>
@@ -6178,17 +6158,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -6260,7 +6240,7 @@
         <v>0.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -6269,7 +6249,7 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -6290,19 +6270,19 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -6329,14 +6309,14 @@
         <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
         <v>0</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>Eggersmann (67%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr"/>
@@ -6420,10 +6400,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -6447,7 +6427,7 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AH34" t="n">
         <v>0</v>
@@ -6456,7 +6436,7 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AK34" t="n">
         <v>0</v>
@@ -6502,7 +6482,7 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>Höveler (67%), Pavo (33%), Marstall (33%)</t>
+          <t>Pavo (67%), Marstall (67%), Höveler (67%)</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr"/>
@@ -6510,17 +6490,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -6586,22 +6566,22 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z35" t="n">
         <v>0.67</v>
       </c>
-      <c r="Y35" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
       <c r="AA35" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -6613,29 +6593,29 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AN35" t="n">
         <v>0.67</v>
       </c>
-      <c r="AH35" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>0</v>
-      </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
@@ -6643,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
         <v>0</v>
@@ -6658,17 +6638,17 @@
         <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AX35" t="n">
         <v>0</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Marstall (33%), Höveler (33%)</t>
+          <t>Eggersmann (67%), Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr"/>
@@ -6676,17 +6656,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -6709,7 +6689,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -6746,28 +6726,28 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -6779,37 +6759,37 @@
         <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AR36" t="n">
         <v>0</v>
@@ -6824,26 +6804,30 @@
         <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX36" t="n">
         <v>0</v>
       </c>
-      <c r="AY36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>St. Hippolyt (100%), Marstall (67%), Höveler (67%), Pavo (33%), Eggersmann (33%)</t>
+        </is>
+      </c>
       <c r="AZ36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -6908,7 +6892,7 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
@@ -6917,61 +6901,61 @@
         <v>0.33</v>
       </c>
       <c r="Y37" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
         <v>0.67</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
         <v>0.67</v>
       </c>
-      <c r="AA37" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ37" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
         <v>0</v>
@@ -6986,17 +6970,17 @@
         <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
         <v>0</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>Marstall (67%), Eggersmann (67%), St. Hippolyt (67%), Pavo (33%), Höveler (33%)</t>
+          <t>Höveler (67%), Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr"/>
@@ -7004,17 +6988,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -7074,10 +7058,10 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="X38" t="n">
         <v>0.33</v>
@@ -7086,10 +7070,10 @@
         <v>0.33</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
@@ -7104,7 +7088,7 @@
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AG38" t="n">
         <v>0.33</v>
@@ -7116,10 +7100,10 @@
         <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -7128,13 +7112,13 @@
         <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AQ38" t="n">
         <v>0</v>
@@ -7152,7 +7136,7 @@
         <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW38" t="n">
         <v>0.33</v>
@@ -7162,7 +7146,7 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), Eggersmann (33%), Höveler (33%), St. Hippolyt (33%)</t>
+          <t>Havens (67%), Höveler (67%), Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr"/>
@@ -7170,17 +7154,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -7240,16 +7224,16 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>0.33</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -7270,65 +7254,65 @@
         <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
         <v>0.67</v>
       </c>
-      <c r="AL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>0</v>
-      </c>
       <c r="AW39" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AX39" t="n">
         <v>0</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>Marstall (67%), St. Hippolyt (67%), Havens (33%), Pavo (33%), Höveler (33%)</t>
+          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr"/>
@@ -7336,17 +7320,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -7369,7 +7353,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -7406,16 +7390,16 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -7427,7 +7411,7 @@
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -7439,7 +7423,7 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
         <v>0</v>
@@ -7448,7 +7432,7 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
         <v>0</v>
@@ -7484,30 +7468,26 @@
         <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
         <v>0</v>
       </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -7516,7 +7496,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -7535,7 +7515,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -7581,7 +7561,7 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -7614,7 +7594,7 @@
         <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
         <v>0</v>
@@ -7658,31 +7638,27 @@
       <c r="AX41" t="n">
         <v>0</v>
       </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Marstall (33%)</t>
-        </is>
-      </c>
+      <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -7830,17 +7806,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -7992,17 +7968,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -8025,7 +8001,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -8068,7 +8044,7 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -8095,10 +8071,10 @@
         <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -8148,27 +8124,31 @@
       <c r="AX44" t="n">
         <v>0</v>
       </c>
-      <c r="AY44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Pavo (100%)</t>
+        </is>
+      </c>
       <c r="AZ44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -8227,10 +8207,10 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="Y45" t="n">
         <v>0.33</v>
@@ -8245,31 +8225,31 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
         <v>0</v>
       </c>
       <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
         <v>0.67</v>
       </c>
-      <c r="AH45" t="n">
-        <v>1</v>
-      </c>
       <c r="AI45" t="n">
         <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -8302,17 +8282,17 @@
         <v>0</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX45" t="n">
         <v>0</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>Pavo (100%), Havens (33%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (67%), St. Hippolyt (67%), Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr"/>
@@ -8320,21 +8300,21 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -8402,7 +8382,7 @@
         <v>0.67</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -8411,19 +8391,19 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
         <v>0.67</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0</v>
       </c>
       <c r="AH46" t="n">
         <v>1</v>
@@ -8432,7 +8412,7 @@
         <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK46" t="n">
         <v>0.67</v>
@@ -8441,10 +8421,10 @@
         <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -8471,14 +8451,14 @@
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AX46" t="n">
         <v>0</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>Pavo (100%), Marstall (67%), St. Hippolyt (67%)</t>
+          <t>Pavo (100%), St. Hippolyt (100%), Marstall (67%), Eggersmann (67%)</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr"/>
@@ -8486,12 +8466,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -8500,7 +8480,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -8562,62 +8542,62 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
         <v>0.67</v>
       </c>
-      <c r="Y47" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Z47" t="n">
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
         <v>0.67</v>
       </c>
-      <c r="AA47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ47" t="n">
         <v>0</v>
       </c>
@@ -8637,14 +8617,14 @@
         <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX47" t="n">
         <v>0</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>Pavo (67%), Eggersmann (67%), St. Hippolyt (67%), Marstall (33%)</t>
+          <t>Höveler (67%), Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr"/>
@@ -8652,12 +8632,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -8734,17 +8714,17 @@
         <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA48" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
         <v>1</v>
       </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AD48" t="n">
         <v>0</v>
       </c>
@@ -8776,41 +8756,41 @@
         <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW48" t="n">
         <v>1</v>
       </c>
-      <c r="AQ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>0</v>
-      </c>
       <c r="AX48" t="n">
         <v>0</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>Höveler (100%), St. Hippolyt (33%)</t>
+          <t>St. Hippolyt (100%), Höveler (67%), Eggersmann (33%)</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr"/>
@@ -8818,12 +8798,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -8900,58 +8880,58 @@
         <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AB49" t="n">
         <v>0</v>
       </c>
       <c r="AC49" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
         <v>0.67</v>
       </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR49" t="n">
         <v>0</v>
@@ -8966,17 +8946,17 @@
         <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AX49" t="n">
         <v>0</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>Höveler (100%), St. Hippolyt (67%), Eggersmann (33%)</t>
+          <t>Höveler (67%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr"/>
@@ -9229,10 +9209,10 @@
         <v>0.67</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -9253,7 +9233,7 @@
         <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AH51" t="n">
         <v>0.67</v>
@@ -9262,7 +9242,7 @@
         <v>0</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AK51" t="n">
         <v>0.33</v>
@@ -9271,10 +9251,10 @@
         <v>0</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN51" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
@@ -9308,7 +9288,7 @@
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Marstall (33%), Eggersmann (33%)</t>
+          <t>St. Hippolyt (100%), Pavo (67%), Marstall (67%), Eggersmann (67%)</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr"/>
@@ -9336,7 +9316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9406,17 +9386,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
+          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
+          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -9427,64 +9407,64 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
+          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
+          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.681</v>
+        <v>0.912</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -9508,21 +9488,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>0.681</v>
@@ -9542,31 +9522,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.443</v>
+        <v>0.681</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9576,31 +9556,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0.443</v>
+        <v>0.592</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H7" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9610,51 +9590,51 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0.443</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -9678,51 +9658,51 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>0.443</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -9733,10 +9713,10 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -9746,17 +9726,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -9780,12 +9760,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -9794,51 +9774,51 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>0.443</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>0.337</v>
+        <v>0.443</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
         <v>0.33</v>
       </c>
       <c r="H14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -9848,12 +9828,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -9862,25 +9842,127 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>0.337</v>
+        <v>0.443</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
         <v>0.33</v>
       </c>
       <c r="H15" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Pferde Vitamine und Mineralstoffe</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Gelenkunterstützung für Pferde</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Pferdefutter Ergänzungsmittel</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E15">
+  <conditionalFormatting sqref="E2:E18">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -9902,7 +9984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9972,17 +10054,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -10007,24 +10089,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>St. Hippolyt (67%), Pavo (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -10049,24 +10131,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Marstall (33%), Höveler (33%)</t>
+          <t>Marstall (100%), St. Hippolyt (100%), Pavo (67%), Eggersmann (67%), Höveler (67%)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -10091,24 +10173,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Pavo (67%), St. Hippolyt (67%), Marstall (33%), Höveler (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -10133,24 +10215,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Marstall (67%), Eggersmann (67%), Höveler (33%)</t>
+          <t>Marstall (100%), Höveler (100%), Pavo (50%), Nösenberger (50%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -10175,28 +10257,28 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Pavo (50%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -10217,24 +10299,24 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Marstall (100%), Höveler (100%), Pavo (50%), Nösenberger (50%), St. Hippolyt (50%)</t>
+          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -10259,24 +10341,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -10301,28 +10383,28 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Höveler (33%)</t>
+          <t>Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -10343,19 +10425,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -10385,24 +10467,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%)</t>
+          <t>Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -10427,7 +10509,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Marstall (33%)</t>
+          <t>Pavo (67%), Marstall (67%), Höveler (67%)</t>
         </is>
       </c>
     </row>
@@ -10469,24 +10551,24 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Eggersmann (67%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Eggersmann (67%), Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -10511,24 +10593,24 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Höveler (67%), Pavo (33%), Marstall (33%)</t>
+          <t>St. Hippolyt (100%), Marstall (67%), Höveler (67%), Pavo (33%), Eggersmann (33%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -10553,24 +10635,24 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Marstall (33%), Höveler (33%)</t>
+          <t>Höveler (67%), Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -10595,24 +10677,24 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Marstall (67%), Eggersmann (67%), St. Hippolyt (67%), Pavo (33%), Höveler (33%)</t>
+          <t>Havens (67%), Höveler (67%), Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -10637,24 +10719,24 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), Eggersmann (33%), Höveler (33%), St. Hippolyt (33%)</t>
+          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -10679,28 +10761,28 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Marstall (67%), St. Hippolyt (67%), Havens (33%), Pavo (33%), Höveler (33%)</t>
+          <t>Pavo (100%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -10721,24 +10803,24 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (67%), St. Hippolyt (67%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -10763,28 +10845,28 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Marstall (33%)</t>
+          <t>Pavo (100%), St. Hippolyt (100%), Marstall (67%), Eggersmann (67%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -10805,28 +10887,28 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Pavo (100%), Havens (33%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Höveler (67%), Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -10847,24 +10929,24 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Pavo (100%), Marstall (67%), St. Hippolyt (67%)</t>
+          <t>St. Hippolyt (100%), Höveler (67%), Eggersmann (33%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -10889,28 +10971,28 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Pavo (67%), Eggersmann (67%), St. Hippolyt (67%), Marstall (33%)</t>
+          <t>Höveler (67%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -10931,24 +11013,24 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Höveler (100%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -10973,96 +11055,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Höveler (100%), St. Hippolyt (67%), Eggersmann (33%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>3</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>own_only</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Pavo (33%), Höveler (33%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>own_only</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Marstall (33%), Eggersmann (33%)</t>
+          <t>St. Hippolyt (100%), Pavo (67%), Marstall (67%), Eggersmann (67%)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E27">
+  <conditionalFormatting sqref="E2:E25">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -11084,7 +11082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11154,17 +11152,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -11192,21 +11190,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -11230,21 +11228,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -11268,17 +11266,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -11306,17 +11304,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
+          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -11344,17 +11342,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -11382,21 +11380,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -11420,21 +11418,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -11458,17 +11456,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -11493,46 +11491,8 @@
       </c>
       <c r="J10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>full</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E11">
+  <conditionalFormatting sqref="E2:E10">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -11630,100 +11590,100 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
+          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
+          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.490000000000007</v>
+        <v>6.080000000000004</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0232</v>
+        <v>0.0181</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0232</v>
+        <v>0.0181</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0464</v>
+        <v>0.0181</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0116</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0232</v>
+        <v>0.0181</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8377</v>
+        <v>0.8734</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0348</v>
+        <v>0.0543</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
+          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
+          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.739999999999999</v>
+        <v>10.24000000000001</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0232</v>
+        <v>0.043</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.0322</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0232</v>
+        <v>0.043</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.0322</v>
       </c>
       <c r="J3" t="n">
-        <v>0.884</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0696</v>
+        <v>0.0215</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.540000000000001</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.0531</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -11732,31 +11692,31 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0551</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8898</v>
+        <v>0.8938</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0551</v>
+        <v>0.0531</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6.579999999999998</v>
+        <v>1.7</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -11771,13 +11731,13 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0258</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9742</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -11786,22 +11746,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3.23</v>
+        <v>5.409999999999998</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.0314</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -11810,13 +11770,13 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1579</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8421</v>
+        <v>0.9686</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -11825,22 +11785,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.059999999999999</v>
+        <v>6.719999999999999</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0281</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -11849,79 +11809,79 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0561</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8878</v>
+        <v>0.9747</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0281</v>
+        <v>0.0253</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8.250000000000009</v>
+        <v>4.89</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0133</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0267</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0133</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.2045</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.84</v>
+        <v>0.7607</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0267</v>
+        <v>0.0348</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.049999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0557</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.0255</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -11933,259 +11893,259 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9443</v>
+        <v>0.9236</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.0509</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7.150000000000006</v>
+        <v>8.69000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.0127</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0154</v>
+        <v>0.038</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0308</v>
+        <v>0.0127</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0462</v>
+        <v>0.0127</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0308</v>
+        <v>0.0759</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8462</v>
+        <v>0.8228</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0308</v>
+        <v>0.0253</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3.379999999999999</v>
+        <v>8.580000000000007</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.0256</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.0385</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.0256</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.0513</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.0641</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8994</v>
+        <v>0.7436</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1006</v>
+        <v>0.0513</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10.19</v>
+        <v>9.140000000000008</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0334</v>
+        <v>0.0241</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0167</v>
+        <v>0.0481</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0667</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0667</v>
+        <v>0.0241</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7831</v>
+        <v>0.8435</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0334</v>
+        <v>0.0481</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8.810000000000009</v>
+        <v>1.7</v>
       </c>
       <c r="D13" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0375</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0375</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0375</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8002</v>
+        <v>0.9</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0375</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.470000000000006</v>
+        <v>0.34</v>
       </c>
       <c r="D14" t="n">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.039</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0649</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7662</v>
+        <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0519</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4.739999999999999</v>
+        <v>5.889999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0359</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>0.0289</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0717</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.0289</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0717</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8207</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.0577</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.069999999999999</v>
+        <v>3.399999999999999</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -12200,76 +12160,76 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9329</v>
+        <v>0.85</v>
       </c>
       <c r="K16" t="n">
-        <v>0.06710000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3.879999999999999</v>
+        <v>9.36000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0438</v>
+        <v>0.0118</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.0353</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1753</v>
+        <v>0.0235</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6933</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0876</v>
+        <v>0.0588</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.940000000000007</v>
+        <v>6.899999999999999</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.0246</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -12281,52 +12241,52 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0369</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9016</v>
+        <v>0.8768</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0615</v>
+        <v>0.09859999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6.930000000000005</v>
+        <v>12.45</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0317</v>
+        <v>0.0265</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0159</v>
+        <v>0.0442</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.0618</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.0442</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8889</v>
+        <v>0.7526</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0635</v>
+        <v>0.0618</v>
       </c>
     </row>
     <row r="20">
@@ -12341,46 +12301,46 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9.480000000000006</v>
+        <v>8.370000000000006</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.0131</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0116</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0232</v>
+        <v>0.0131</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0116</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0348</v>
+        <v>0.0526</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9072</v>
+        <v>0.9211</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0116</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.53</v>
+        <v>8.800000000000008</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -12389,37 +12349,37 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0435</v>
+        <v>0.05</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0435</v>
+        <v>0.05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.913</v>
+        <v>0.725</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.0375</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6.490000000000001</v>
+        <v>4.729999999999999</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -12428,22 +12388,22 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0339</v>
+        <v>0.1163</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0847</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1017</v>
+        <v>0.093</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0508</v>
+        <v>0.093</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7119</v>
+        <v>0.6744</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0169</v>
+        <v>0.0233</v>
       </c>
     </row>
     <row r="23">
@@ -12458,7 +12418,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5.83</v>
+        <v>4.839999999999998</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -12467,22 +12427,22 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0566</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0377</v>
+        <v>0.0227</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0189</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0755</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8113</v>
+        <v>0.8409</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>0.0455</v>
       </c>
     </row>
     <row r="24">
@@ -12497,31 +12457,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8.910000000000002</v>
+        <v>7.149999999999999</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0123</v>
+        <v>0.0308</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0247</v>
+        <v>0.0462</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0123</v>
+        <v>0.0308</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0741</v>
+        <v>0.0308</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1358</v>
+        <v>0.1231</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5432</v>
+        <v>0.5231</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1975</v>
+        <v>0.2154</v>
       </c>
     </row>
     <row r="25">
@@ -12536,7 +12496,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8.370000000000008</v>
+        <v>8.370000000000006</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -12548,19 +12508,19 @@
         <v>0.0394</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0131</v>
+        <v>0.0263</v>
       </c>
       <c r="H25" t="n">
         <v>0.0394</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1183</v>
+        <v>0.1051</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7109</v>
+        <v>0.724</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0789</v>
+        <v>0.06569999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -12575,31 +12535,31 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10.24000000000001</v>
+        <v>9.900000000000013</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0215</v>
+        <v>0.0333</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0322</v>
+        <v>0.0222</v>
       </c>
       <c r="G26" t="n">
-        <v>0.043</v>
+        <v>0.0333</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0322</v>
+        <v>0.0111</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0322</v>
+        <v>0.0333</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7637</v>
+        <v>0.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0752</v>
+        <v>0.0667</v>
       </c>
     </row>
     <row r="27">
@@ -12614,13 +12574,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7.320000000000001</v>
+        <v>6.280000000000001</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0164</v>
+        <v>0.0382</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -12629,16 +12589,16 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0164</v>
+        <v>0.0191</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9508</v>
+        <v>0.9236</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0164</v>
+        <v>0.0191</v>
       </c>
     </row>
     <row r="28">
@@ -12653,7 +12613,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6.049999999999999</v>
+        <v>5.020000000000001</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -12662,100 +12622,100 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1273</v>
+        <v>0.1235</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0364</v>
+        <v>0.0239</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1091</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5818</v>
+        <v>0.5837</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0545</v>
+        <v>0.0717</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>12.99</v>
+        <v>8.620000000000003</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0169</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0423</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0508</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0254</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0593</v>
+        <v>0.0255</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7714</v>
+        <v>0.8596</v>
       </c>
       <c r="K29" t="n">
-        <v>0.0339</v>
+        <v>0.1148</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>11.46</v>
+        <v>11.67</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>0.0189</v>
       </c>
       <c r="E30" t="n">
-        <v>0.009599999999999999</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.048</v>
+        <v>0.0189</v>
       </c>
       <c r="G30" t="n">
-        <v>0.048</v>
+        <v>0.0471</v>
       </c>
       <c r="H30" t="n">
-        <v>0.048</v>
+        <v>0.0377</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0288</v>
+        <v>0.0471</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7792</v>
+        <v>0.8021</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0384</v>
+        <v>0.0283</v>
       </c>
     </row>
     <row r="31">
@@ -12770,31 +12730,31 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7.040000000000006</v>
+        <v>6.270000000000004</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0156</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0156</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0469</v>
+        <v>0.0526</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0469</v>
+        <v>0.0351</v>
       </c>
       <c r="J31" t="n">
-        <v>0.875</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="32">
@@ -12809,13 +12769,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2.21</v>
+        <v>5.899999999999999</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0769</v>
+        <v>0.0288</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -12824,13 +12784,13 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>0.0576</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0769</v>
+        <v>0.0288</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8462</v>
+        <v>0.8847</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -12839,16 +12799,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1.36</v>
+        <v>6.749999999999998</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -12857,10 +12817,10 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>0.0252</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.0252</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -12869,10 +12829,10 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0.9244</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>0.0252</v>
       </c>
     </row>
     <row r="34">
@@ -12887,7 +12847,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1.7</v>
+        <v>3.17</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -12917,22 +12877,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4.399999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0386</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -12947,64 +12907,64 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9227</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5.419999999999999</v>
+        <v>5.390000000000001</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>0.0204</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0314</v>
+        <v>0.1429</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0314</v>
+        <v>0.0408</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>0.1224</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>0.2041</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9373</v>
+        <v>0.4082</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>0.0612</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5.610000000000001</v>
+        <v>4.749999999999999</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -13013,37 +12973,37 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2157</v>
+        <v>0.1789</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0588</v>
+        <v>0.0358</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1569</v>
+        <v>0.0716</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1569</v>
+        <v>0.0358</v>
       </c>
       <c r="J37" t="n">
-        <v>0.3922</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>0.0196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8.529999999999999</v>
+        <v>8.040000000000004</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -13052,37 +13012,37 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1758</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0387</v>
+        <v>0.0137</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0586</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0199</v>
+        <v>0.041</v>
       </c>
       <c r="J38" t="n">
-        <v>0.7069</v>
+        <v>0.8209</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>0.1244</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>8.590000000000003</v>
+        <v>5.079999999999998</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -13094,73 +13054,73 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0128</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0256</v>
+        <v>0.0335</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0256</v>
+        <v>0.0335</v>
       </c>
       <c r="J39" t="n">
-        <v>0.8847</v>
+        <v>0.8327</v>
       </c>
       <c r="K39" t="n">
-        <v>0.0512</v>
+        <v>0.1004</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3.399999999999999</v>
+        <v>9.920000000000009</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>0.0111</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>0.0887</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.0222</v>
       </c>
       <c r="H40" t="n">
-        <v>0.05</v>
+        <v>0.0887</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>0.0887</v>
       </c>
       <c r="J40" t="n">
-        <v>0.85</v>
+        <v>0.6784</v>
       </c>
       <c r="K40" t="n">
-        <v>0.1</v>
+        <v>0.0222</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>5.709999999999999</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -13169,7 +13129,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>0.0595</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -13178,10 +13138,10 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>0.0893</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>0.8511</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -13190,16 +13150,16 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4.249999999999999</v>
+        <v>7.269999999999998</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -13208,19 +13168,19 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.08</v>
+        <v>0.0234</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>0.0234</v>
       </c>
       <c r="I42" t="n">
-        <v>0.12</v>
+        <v>0.0234</v>
       </c>
       <c r="J42" t="n">
-        <v>0.8</v>
+        <v>0.9298</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -13229,55 +13189,55 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>13.67</v>
+        <v>7.590000000000009</v>
       </c>
       <c r="D43" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.029</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0241</v>
+        <v>0.0145</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0885</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0885</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0.654</v>
+        <v>0.9275</v>
       </c>
       <c r="K43" t="n">
-        <v>0.0402</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3.869999999999999</v>
+        <v>4.399999999999999</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -13286,7 +13246,7 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0439</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -13298,25 +13258,25 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.7318</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>0.2682</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2.53</v>
+        <v>4.559999999999999</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -13325,7 +13285,7 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>0.0373</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -13334,34 +13294,34 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>0.0373</v>
       </c>
       <c r="J45" t="n">
-        <v>0.7352</v>
+        <v>0.9254</v>
       </c>
       <c r="K45" t="n">
-        <v>0.2648</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6.249999999999998</v>
+        <v>4.35</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>0.0391</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -13370,70 +13330,70 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.0391</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0.9728</v>
+        <v>0.7678</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0272</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8.299999999999997</v>
+        <v>5.56</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>0.0306</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0205</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.041</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0205</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>0.1223</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8157</v>
+        <v>0.786</v>
       </c>
       <c r="K47" t="n">
-        <v>0.1024</v>
+        <v>0.0612</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6.269999999999998</v>
+        <v>2.869999999999999</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -13445,34 +13405,34 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0542</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0271</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8915</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>0.0271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2.869999999999999</v>
+        <v>6.01</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -13484,7 +13444,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>0.0832</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -13493,10 +13453,10 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0.8885</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>0.0283</v>
       </c>
     </row>
     <row r="50">
@@ -13511,7 +13471,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7.079999999999998</v>
+        <v>3.889999999999999</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -13520,19 +13480,19 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0466</v>
+        <v>0.0848</v>
       </c>
       <c r="J50" t="n">
-        <v>0.8814</v>
+        <v>0.9152</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -13550,7 +13510,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5.729999999999999</v>
+        <v>4.17</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -13562,7 +13522,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0297</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -13571,10 +13531,10 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.9407</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0297</v>
+        <v>0.0408</v>
       </c>
     </row>
   </sheetData>

--- a/public/downloads/drift_radar.xlsx
+++ b/public/downloads/drift_radar.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-30 → 2026-05-02</t>
+          <t>2026-05-01 → 2026-05-03</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -561,7 +561,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5.8 %</t>
+          <t>6.1 %</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6.6 %</t>
+          <t>6.0 %</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7.3 %</t>
+          <t>8.7 %</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3.3 %</t>
+          <t>3.7 %</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2.2×</t>
+          <t>2.4×</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M2" t="n">
         <v>0.4385</v>
@@ -1282,7 +1282,7 @@
         <v>0.67</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -1326,21 +1326,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>0.912</v>
@@ -1371,49 +1371,49 @@
         <v>0.5615</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.4385</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5615</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4385</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -1422,13 +1422,13 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1437,13 +1437,13 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
@@ -1452,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
@@ -1470,13 +1470,13 @@
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr"/>
@@ -1484,33 +1484,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.681</v>
+        <v>0.912</v>
       </c>
       <c r="F4" t="n">
         <v>1.414</v>
       </c>
       <c r="G4" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.223</v>
+        <v>0.333</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -1529,37 +1529,37 @@
         <v>0.5615</v>
       </c>
       <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="X4" t="n">
         <v>0.67</v>
       </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.2077</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.9385</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.33</v>
-      </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>0.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>1</v>
@@ -1580,25 +1580,25 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -1619,16 +1619,16 @@
         <v>0</v>
       </c>
       <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
         <v>0.67</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
       </c>
       <c r="AW4" t="n">
         <v>1</v>
@@ -1642,21 +1642,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0.681</v>
@@ -1690,7 +1690,7 @@
         <v>0.67</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
         <v>0.2077</v>
@@ -1714,22 +1714,22 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1741,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -1750,10 +1750,10 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AT5" t="n">
         <v>0</v>
@@ -1789,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>0.67</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
         <v>0.2077</v>
@@ -1872,7 +1872,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
         <v>1</v>
@@ -1881,28 +1881,28 @@
         <v>1</v>
       </c>
       <c r="AA6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
         <v>0.67</v>
       </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1</v>
       </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AH6" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1926,28 +1926,28 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
         <v>0.67</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
@@ -2057,10 +2057,10 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -2102,10 +2102,10 @@
         <v>0</v>
       </c>
       <c r="AV7" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW7" t="n">
         <v>0.67</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.33</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
@@ -2116,49 +2116,49 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>0.443</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="F8" t="n">
         <v>1.414</v>
       </c>
       <c r="G8" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.11</v>
+        <v>0.167</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7923</v>
+        <v>0.5615</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -2173,37 +2173,37 @@
         <v>0.5615</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.0945</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.9055</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -2215,13 +2215,13 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
@@ -2242,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
         <v>0</v>
@@ -2260,7 +2260,7 @@
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
         <v>0</v>
@@ -2274,21 +2274,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
         <v>0.443</v>
@@ -2340,28 +2340,28 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7935</v>
+        <v>0.5615</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -2373,19 +2373,19 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2418,13 +2418,13 @@
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr"/>
@@ -2432,21 +2432,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0.443</v>
@@ -2465,16 +2465,16 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -2489,97 +2489,97 @@
         <v>0.5615</v>
       </c>
       <c r="S10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
         <v>1</v>
       </c>
-      <c r="U10" t="n">
-        <v>0.0615</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.7923</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
         <v>0.67</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
         <v>1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
@@ -2590,17 +2590,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2656,13 +2656,13 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5615</v>
+        <v>0.7935</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -2671,13 +2671,13 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -2689,13 +2689,13 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
         <v>0</v>
@@ -2734,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
@@ -2748,17 +2748,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -2781,29 +2781,29 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P12" t="n">
         <v>1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="Q12" t="n">
         <v>0.0615</v>
       </c>
-      <c r="N12" t="n">
+      <c r="R12" t="n">
         <v>0.7923</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.5615</v>
-      </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
@@ -2814,85 +2814,85 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
         <v>0.67</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z12" t="n">
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
         <v>0.67</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0.33</v>
       </c>
       <c r="AW12" t="n">
         <v>0.33</v>
@@ -3222,17 +3222,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -3258,7 +3258,7 @@
         <v>0.33</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
         <v>0.0615</v>
@@ -3294,10 +3294,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -3321,7 +3321,7 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -3333,7 +3333,7 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3366,10 +3366,10 @@
         <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
@@ -3380,21 +3380,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>0.443</v>
@@ -3413,16 +3413,16 @@
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7923</v>
+        <v>0.5615</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -3437,22 +3437,22 @@
         <v>0.5615</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.7923</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
@@ -3538,21 +3538,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0.443</v>
@@ -3583,37 +3583,37 @@
         <v>0.5615</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="S17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
         <v>1</v>
       </c>
-      <c r="U17" t="n">
-        <v>0.0615</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.7923</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -3637,10 +3637,10 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -3649,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3682,10 +3682,10 @@
         <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
@@ -3696,17 +3696,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -3729,29 +3729,29 @@
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="N18" t="n">
+        <v>0.7923</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
         <v>0.5615</v>
       </c>
-      <c r="O18" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.0615</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.7923</v>
-      </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
@@ -3768,22 +3768,22 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3795,10 +3795,10 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3822,7 +3822,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ18" t="n">
         <v>0</v>
@@ -3840,10 +3840,10 @@
         <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
@@ -3854,17 +3854,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -3924,7 +3924,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -3939,7 +3939,7 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -3957,13 +3957,13 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH19" t="n">
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
@@ -3984,7 +3984,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ19" t="n">
         <v>0</v>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Pavo (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr"/>
@@ -4020,12 +4020,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -4096,89 +4096,89 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
         <v>0.67</v>
       </c>
-      <c r="Y20" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z20" t="n">
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
         <v>0.67</v>
       </c>
-      <c r="AA20" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1</v>
-      </c>
       <c r="AX20" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>Marstall (100%), St. Hippolyt (100%), Pavo (67%), Eggersmann (67%), Höveler (67%)</t>
+          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr"/>
@@ -5232,13 +5232,13 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0.6576</v>
+        <v>0.5615</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="Y27" t="n">
         <v>1</v>
@@ -5250,10 +5250,10 @@
         <v>1</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -5265,16 +5265,16 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AK27" t="n">
         <v>0.33</v>
@@ -5295,7 +5295,7 @@
         <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AR27" t="n">
         <v>1</v>
@@ -5307,20 +5307,20 @@
         <v>0.33</v>
       </c>
       <c r="AU27" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AV27" t="n">
         <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AX27" t="n">
         <v>0</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>Marstall (100%), Höveler (100%), Pavo (50%), Nösenberger (50%), St. Hippolyt (33%)</t>
+          <t>Marstall (100%), Höveler (100%), Nösenberger (67%), St. Hippolyt (67%), Pavo (33%)</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr"/>
@@ -5328,17 +5328,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -5398,28 +5398,28 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0.6576</v>
+        <v>0.5615</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -5431,37 +5431,37 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH28" t="n">
         <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR28" t="n">
         <v>0</v>
@@ -5476,17 +5476,17 @@
         <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX28" t="n">
         <v>0</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>Pavo (50%)</t>
+          <t>Marstall (100%), Eggersmann (67%), St. Hippolyt (67%), Pavo (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr"/>
@@ -5494,17 +5494,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -5564,28 +5564,28 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0.5615</v>
+        <v>0.6576</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -5597,25 +5597,25 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
         <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN29" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
         <v>0</v>
@@ -5642,17 +5642,17 @@
         <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
         <v>0</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Höveler (33%)</t>
+          <t>Pavo (50%), Eggersmann (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr"/>
@@ -5660,17 +5660,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -5745,7 +5745,7 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -5790,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
         <v>0</v>
@@ -5816,27 +5816,23 @@
       <c r="AX30" t="n">
         <v>0</v>
       </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Höveler (33%)</t>
-        </is>
-      </c>
+      <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -5859,7 +5855,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -5902,10 +5898,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -5929,19 +5925,19 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5982,31 +5978,27 @@
       <c r="AX31" t="n">
         <v>0</v>
       </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>Pavo (33%), Marstall (33%)</t>
-        </is>
-      </c>
+      <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -6062,7 +6054,7 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -6104,13 +6096,13 @@
         <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
         <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AM32" t="n">
         <v>0</v>
@@ -6158,12 +6150,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6228,7 +6220,7 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -6237,13 +6229,13 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
@@ -6270,7 +6262,7 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
         <v>0</v>
@@ -6294,7 +6286,7 @@
         <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AS33" t="n">
         <v>0</v>
@@ -6316,7 +6308,7 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>Marstall (33%)</t>
+          <t>Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr"/>
@@ -6324,17 +6316,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -6394,95 +6386,95 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
       </c>
       <c r="X34" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
         <v>0.67</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
         <v>0.67</v>
       </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0</v>
-      </c>
       <c r="AW34" t="n">
         <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>Pavo (67%), Marstall (67%), Höveler (67%)</t>
+          <t>St. Hippolyt (67%), Pavo (33%)</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr"/>
@@ -6490,17 +6482,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -6569,52 +6561,52 @@
         <v>0.33</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
         <v>0.67</v>
       </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
       <c r="AK35" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -6648,7 +6640,7 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>Eggersmann (67%), Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (67%), Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr"/>
@@ -6656,17 +6648,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -6726,7 +6718,7 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -6735,19 +6727,19 @@
         <v>0.33</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -6762,7 +6754,7 @@
         <v>0.33</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -6771,25 +6763,25 @@
         <v>0.33</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
         <v>0</v>
@@ -6804,17 +6796,17 @@
         <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
         <v>0</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Marstall (67%), Höveler (67%), Pavo (33%), Eggersmann (33%)</t>
+          <t>Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr"/>
@@ -6822,17 +6814,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -6907,7 +6899,7 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
@@ -6952,7 +6944,7 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AQ37" t="n">
         <v>0</v>
@@ -6980,7 +6972,7 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>Höveler (67%), Pavo (33%), Marstall (33%)</t>
+          <t>Pavo (33%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr"/>
@@ -6988,12 +6980,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -7058,67 +7050,67 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
         <v>0.67</v>
       </c>
-      <c r="X38" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
       <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AN38" t="n">
         <v>0.67</v>
       </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>0</v>
-      </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
         <v>0</v>
@@ -7136,7 +7128,7 @@
         <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
         <v>0.33</v>
@@ -7146,7 +7138,7 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>Havens (67%), Höveler (67%), Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Eggersmann (67%), Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr"/>
@@ -7154,17 +7146,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -7224,7 +7216,7 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -7233,10 +7225,10 @@
         <v>0.33</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA39" t="n">
         <v>0.33</v>
@@ -7260,7 +7252,7 @@
         <v>0.33</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -7269,16 +7261,16 @@
         <v>0.33</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -7287,7 +7279,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR39" t="n">
         <v>0</v>
@@ -7302,17 +7294,17 @@
         <v>0</v>
       </c>
       <c r="AV39" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW39" t="n">
         <v>0.67</v>
       </c>
-      <c r="AW39" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AX39" t="n">
         <v>0</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Höveler (33%)</t>
+          <t>Marstall (67%), St. Hippolyt (67%), Pavo (33%), Eggersmann (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr"/>
@@ -7320,17 +7312,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -7353,7 +7345,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -7390,22 +7382,22 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
@@ -7423,7 +7415,7 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH40" t="n">
         <v>0</v>
@@ -7432,7 +7424,7 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK40" t="n">
         <v>0</v>
@@ -7450,7 +7442,7 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AQ40" t="n">
         <v>0</v>
@@ -7476,27 +7468,31 @@
       <c r="AX40" t="n">
         <v>0</v>
       </c>
-      <c r="AY40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Höveler (67%), Pavo (33%), Marstall (33%)</t>
+        </is>
+      </c>
       <c r="AZ40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -7515,7 +7511,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -7552,28 +7548,28 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB41" t="n">
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -7582,22 +7578,22 @@
         <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7612,7 +7608,7 @@
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ41" t="n">
         <v>0</v>
@@ -7630,31 +7626,35 @@
         <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX41" t="n">
         <v>0</v>
       </c>
-      <c r="AY41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Havens (100%), Marstall (67%), St. Hippolyt (67%), Pavo (33%), Höveler (33%)</t>
+        </is>
+      </c>
       <c r="AZ41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -7677,7 +7677,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -7720,22 +7720,22 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB42" t="n">
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -7747,7 +7747,7 @@
         <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH42" t="n">
         <v>0</v>
@@ -7756,7 +7756,7 @@
         <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK42" t="n">
         <v>0</v>
@@ -7774,7 +7774,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ42" t="n">
         <v>0</v>
@@ -7792,31 +7792,35 @@
         <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX42" t="n">
         <v>0</v>
       </c>
-      <c r="AY42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Höveler (33%)</t>
+        </is>
+      </c>
       <c r="AZ42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -7968,21 +7972,21 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -8001,7 +8005,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -8044,7 +8048,7 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -8071,10 +8075,10 @@
         <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -8124,31 +8128,27 @@
       <c r="AX44" t="n">
         <v>0</v>
       </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Pavo (100%)</t>
-        </is>
-      </c>
+      <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -8210,10 +8210,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -8240,7 +8240,7 @@
         <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -8249,7 +8249,7 @@
         <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -8285,32 +8285,28 @@
         <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX45" t="n">
         <v>0</v>
       </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>Pavo (67%), St. Hippolyt (67%), Marstall (33%)</t>
-        </is>
-      </c>
+      <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -8373,16 +8369,16 @@
         <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X46" t="n">
         <v>1</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -8391,19 +8387,19 @@
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AF46" t="n">
         <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AH46" t="n">
         <v>1</v>
@@ -8412,19 +8408,19 @@
         <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -8451,14 +8447,14 @@
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
         <v>0</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>Pavo (100%), St. Hippolyt (100%), Marstall (67%), Eggersmann (67%)</t>
+          <t>Pavo (100%), Havens (33%)</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr"/>
@@ -8466,21 +8462,21 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -8542,7 +8538,7 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y47" t="n">
         <v>0.33</v>
@@ -8551,14 +8547,14 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
         <v>0.67</v>
       </c>
-      <c r="AB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
       <c r="AD47" t="n">
         <v>0</v>
       </c>
@@ -8569,19 +8565,19 @@
         <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8596,35 +8592,35 @@
         <v>0</v>
       </c>
       <c r="AP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW47" t="n">
         <v>0.67</v>
       </c>
-      <c r="AQ47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>0</v>
-      </c>
       <c r="AX47" t="n">
         <v>0</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>Höveler (67%), Pavo (33%), Marstall (33%)</t>
+          <t>Pavo (67%), St. Hippolyt (67%), Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr"/>
@@ -8632,17 +8628,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -8708,16 +8704,16 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
@@ -8735,10 +8731,10 @@
         <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -8747,16 +8743,16 @@
         <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN48" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -8765,7 +8761,7 @@
         <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AR48" t="n">
         <v>0</v>
@@ -8790,7 +8786,7 @@
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Höveler (67%), Eggersmann (33%)</t>
+          <t>St. Hippolyt (100%), Pavo (67%), Marstall (67%), Eggersmann (67%)</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr"/>
@@ -8871,7 +8867,7 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X49" t="n">
         <v>0</v>
@@ -8895,7 +8891,7 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AF49" t="n">
         <v>0</v>
@@ -8956,7 +8952,7 @@
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>Höveler (67%), St. Hippolyt (33%)</t>
+          <t>Höveler (67%), Havens (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr"/>
@@ -9049,13 +9045,13 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -9094,7 +9090,7 @@
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ50" t="n">
         <v>0</v>
@@ -9112,7 +9108,7 @@
         <v>0</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW50" t="n">
         <v>0</v>
@@ -9122,7 +9118,7 @@
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>Pavo (33%), Höveler (33%)</t>
+          <t>Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr"/>
@@ -9212,16 +9208,16 @@
         <v>0.67</v>
       </c>
       <c r="Z51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
         <v>0.67</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
@@ -9236,7 +9232,7 @@
         <v>0.67</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
@@ -9245,7 +9241,7 @@
         <v>0.67</v>
       </c>
       <c r="AK51" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -9254,41 +9250,41 @@
         <v>0</v>
       </c>
       <c r="AN51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW51" t="n">
         <v>0.67</v>
       </c>
-      <c r="AO51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>1</v>
-      </c>
       <c r="AX51" t="n">
         <v>0</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Marstall (67%), Eggersmann (67%)</t>
+          <t>Eggersmann (100%), Pavo (67%), Marstall (67%), St. Hippolyt (67%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr"/>
@@ -9420,21 +9416,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>0.912</v>
@@ -9444,65 +9440,65 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.681</v>
+        <v>0.912</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0.681</v>
@@ -9590,55 +9586,55 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>0.443</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
         <v>0.443</v>
@@ -9658,51 +9654,51 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0.443</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -9726,17 +9722,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -9747,10 +9743,10 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -9828,17 +9824,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -9862,55 +9858,55 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>0.443</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0.443</v>
@@ -9920,27 +9916,27 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -9951,10 +9947,10 @@
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H18" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -9984,7 +9980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -10054,17 +10050,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -10089,19 +10085,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Pavo (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -10110,7 +10106,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -10131,7 +10127,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Marstall (100%), St. Hippolyt (100%), Pavo (67%), Eggersmann (67%), Höveler (67%)</t>
+          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
@@ -10215,24 +10211,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Marstall (100%), Höveler (100%), Pavo (50%), Nösenberger (50%), St. Hippolyt (33%)</t>
+          <t>Marstall (100%), Höveler (100%), Nösenberger (67%), St. Hippolyt (67%), Pavo (33%)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -10257,24 +10253,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Pavo (50%)</t>
+          <t>Marstall (100%), Eggersmann (67%), St. Hippolyt (67%), Pavo (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -10299,19 +10295,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Höveler (33%)</t>
+          <t>Pavo (50%), Eggersmann (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -10320,7 +10316,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -10341,7 +10337,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Höveler (33%)</t>
+          <t>Marstall (33%)</t>
         </is>
       </c>
     </row>
@@ -10383,24 +10379,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%)</t>
+          <t>Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -10425,24 +10421,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Marstall (33%)</t>
+          <t>St. Hippolyt (67%), Pavo (33%)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -10467,24 +10463,24 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Marstall (33%)</t>
+          <t>Marstall (67%), Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -10509,24 +10505,24 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Pavo (67%), Marstall (67%), Höveler (67%)</t>
+          <t>Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -10551,24 +10547,24 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Eggersmann (67%), Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -10593,19 +10589,19 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Marstall (67%), Höveler (67%), Pavo (33%), Eggersmann (33%)</t>
+          <t>Eggersmann (67%), Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -10635,24 +10631,24 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Höveler (67%), Pavo (33%), Marstall (33%)</t>
+          <t>Marstall (67%), St. Hippolyt (67%), Pavo (33%), Eggersmann (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -10677,24 +10673,24 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Havens (67%), Höveler (67%), Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Höveler (67%), Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -10719,19 +10715,19 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Höveler (33%)</t>
+          <t>Havens (100%), Marstall (67%), St. Hippolyt (67%), Pavo (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -10761,28 +10757,28 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Pavo (100%)</t>
+          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -10803,28 +10799,28 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Pavo (67%), St. Hippolyt (67%), Marstall (33%)</t>
+          <t>Pavo (100%), Havens (33%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10845,19 +10841,19 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Pavo (100%), St. Hippolyt (100%), Marstall (67%), Eggersmann (67%)</t>
+          <t>Pavo (67%), St. Hippolyt (67%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -10866,7 +10862,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -10887,19 +10883,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Höveler (67%), Pavo (33%), Marstall (33%)</t>
+          <t>St. Hippolyt (100%), Pavo (67%), Marstall (67%), Eggersmann (67%)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -10929,28 +10925,28 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Höveler (67%), Eggersmann (33%)</t>
+          <t>Höveler (67%), Havens (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10971,19 +10967,19 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Höveler (67%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -10992,7 +10988,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -11013,54 +11009,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Pavo (33%), Höveler (33%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>own_only</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Marstall (67%), Eggersmann (67%)</t>
+          <t>Eggersmann (100%), Pavo (67%), Marstall (67%), St. Hippolyt (67%), Höveler (33%)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E25">
+  <conditionalFormatting sqref="E2:E24">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -11082,7 +11036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11342,17 +11296,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -11380,21 +11334,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -11418,17 +11372,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -11456,43 +11410,81 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Magen-Darm-Gesundheit Pferd</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>2</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>full</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E10">
+  <conditionalFormatting sqref="E2:E11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -11599,136 +11591,136 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6.080000000000004</v>
+        <v>6.840000000000003</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0181</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0181</v>
+        <v>0.0161</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0181</v>
+        <v>0.0161</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0181</v>
+        <v>0.0322</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8734</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0543</v>
+        <v>0.0804</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10.24000000000001</v>
+        <v>2.72</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0322</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0322</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.8125</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0215</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3.199999999999999</v>
+        <v>10.46</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0531</v>
+        <v>0.0526</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.0315</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8938</v>
+        <v>0.8528</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0531</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.7</v>
+        <v>4.909999999999998</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.0346</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.0346</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -11737,10 +11729,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0.8269</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.1039</v>
       </c>
     </row>
     <row r="6">
@@ -11755,13 +11747,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.409999999999998</v>
+        <v>5.729999999999999</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0314</v>
+        <v>0.0297</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -11776,10 +11768,10 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9686</v>
+        <v>0.9407</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.0297</v>
       </c>
     </row>
     <row r="7">
@@ -11794,7 +11786,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.719999999999999</v>
+        <v>7.059999999999999</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -11815,205 +11807,205 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9747</v>
+        <v>0.9759</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0253</v>
+        <v>0.0241</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4.89</v>
+        <v>9.390000000000004</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.0128</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.0266</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.0128</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.0128</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2045</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.0639</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7607</v>
+        <v>0.8328</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0348</v>
+        <v>0.0383</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.5</v>
+        <v>6.930000000000008</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.0159</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0255</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.0159</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.0635</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9236</v>
+        <v>0.9048</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0509</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8.69000000000001</v>
+        <v>4.729999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0127</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0127</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0127</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0759</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8228</v>
+        <v>0.9641</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0253</v>
+        <v>0.0359</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8.580000000000007</v>
+        <v>6.489999999999998</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0256</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0385</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0256</v>
+        <v>0.0431</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0513</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0641</v>
+        <v>0.0216</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7436</v>
+        <v>0.8921</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0513</v>
+        <v>0.0431</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9.140000000000008</v>
+        <v>4.899999999999999</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.012</v>
+        <v>0.0347</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0241</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0481</v>
+        <v>0.0347</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0241</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8435</v>
+        <v>0.8612</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0481</v>
+        <v>0.0694</v>
       </c>
     </row>
     <row r="13">
@@ -12028,7 +12020,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -12049,10 +12041,10 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9</v>
+        <v>0.8882</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1</v>
+        <v>0.1118</v>
       </c>
     </row>
     <row r="14">
@@ -12097,28 +12089,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.889999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0289</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0289</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -12127,109 +12119,109 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8846000000000001</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0577</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3.399999999999999</v>
+        <v>8.580000000000009</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.0128</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.0385</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.0256</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1</v>
+        <v>0.0385</v>
       </c>
       <c r="I16" t="n">
-        <v>0.05</v>
+        <v>0.0385</v>
       </c>
       <c r="J16" t="n">
-        <v>0.85</v>
+        <v>0.8077</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.0385</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9.36000000000001</v>
+        <v>6.34</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0118</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.047</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0353</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.047</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0235</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.8155</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0588</v>
+        <v>0.1845</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.899999999999999</v>
+        <v>6.579999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.0258</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0246</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -12238,94 +12230,94 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.155</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8768</v>
+        <v>0.7933</v>
       </c>
       <c r="K18" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.0258</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12.45</v>
+        <v>9.979999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="E19" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.017</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0265</v>
+        <v>0.0511</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0442</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0618</v>
+        <v>0.0511</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0442</v>
+        <v>0.1363</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7526</v>
+        <v>0.6593</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0618</v>
+        <v>0.06809999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8.370000000000006</v>
+        <v>8.830000000000004</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0131</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0131</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0526</v>
+        <v>0.0374</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9211</v>
+        <v>0.8879</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.0747</v>
       </c>
     </row>
     <row r="21">
@@ -12340,7 +12332,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8.800000000000008</v>
+        <v>7.260000000000004</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -12349,22 +12341,22 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.05</v>
+        <v>0.0606</v>
       </c>
       <c r="G21" t="n">
-        <v>0.05</v>
+        <v>0.0455</v>
       </c>
       <c r="H21" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.0606</v>
       </c>
       <c r="I21" t="n">
-        <v>0.05</v>
+        <v>0.0606</v>
       </c>
       <c r="J21" t="n">
-        <v>0.725</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0375</v>
+        <v>0.0455</v>
       </c>
     </row>
     <row r="22">
@@ -12379,7 +12371,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4.729999999999999</v>
+        <v>8.040000000000003</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -12388,22 +12380,22 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1163</v>
+        <v>0.1095</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.0137</v>
       </c>
       <c r="H22" t="n">
-        <v>0.093</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>0.093</v>
+        <v>0.1368</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6744</v>
+        <v>0.6306</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0233</v>
+        <v>0.0274</v>
       </c>
     </row>
     <row r="23">
@@ -12430,13 +12422,13 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="H23" t="n">
         <v>0.0227</v>
       </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
       <c r="I23" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0455</v>
       </c>
       <c r="J23" t="n">
         <v>0.8409</v>
@@ -12457,31 +12449,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7.149999999999999</v>
+        <v>6.489999999999999</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0308</v>
+        <v>0.0339</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0462</v>
+        <v>0.0508</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0308</v>
+        <v>0.0508</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0308</v>
+        <v>0.0508</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1231</v>
+        <v>0.1017</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5231</v>
+        <v>0.5254</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2154</v>
+        <v>0.1864</v>
       </c>
     </row>
     <row r="25">
@@ -12496,7 +12488,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8.370000000000006</v>
+        <v>8.800000000000006</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -12505,22 +12497,22 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0394</v>
+        <v>0.0375</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0263</v>
+        <v>0.05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0394</v>
+        <v>0.0625</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1051</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>0.724</v>
+        <v>0.6625</v>
       </c>
       <c r="K25" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="26">
@@ -12535,31 +12527,31 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9.900000000000013</v>
+        <v>10.25000000000001</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0333</v>
+        <v>0.0215</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0222</v>
+        <v>0.0322</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0333</v>
+        <v>0.0429</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0111</v>
+        <v>0.0107</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0333</v>
+        <v>0.0322</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8</v>
+        <v>0.839</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0667</v>
+        <v>0.0215</v>
       </c>
     </row>
     <row r="27">
@@ -12574,13 +12566,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6.280000000000001</v>
+        <v>6.380000000000003</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0382</v>
+        <v>0.0345</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -12589,70 +12581,70 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0191</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9236</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0191</v>
+        <v>0.0517</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.020000000000001</v>
+        <v>7.590000000000006</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>0.0145</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1235</v>
+        <v>0.029</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0239</v>
+        <v>0.058</v>
       </c>
       <c r="H28" t="n">
-        <v>0.09959999999999999</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0145</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5837</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0717</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8.620000000000003</v>
+        <v>6.970000000000002</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -12661,154 +12653,154 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.1435</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.0172</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.1062</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0255</v>
+        <v>0.0703</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8596</v>
+        <v>0.5595</v>
       </c>
       <c r="K29" t="n">
-        <v>0.1148</v>
+        <v>0.1033</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>11.67</v>
+        <v>6.730000000000006</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0189</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0189</v>
+        <v>0.0163</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0471</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0377</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0471</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8021</v>
+        <v>0.951</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0283</v>
+        <v>0.0327</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6.270000000000004</v>
+        <v>14.86999999999998</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.0148</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.0296</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.0444</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0526</v>
+        <v>0.0296</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0351</v>
+        <v>0.037</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.8003</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0175</v>
+        <v>0.0444</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5.899999999999999</v>
+        <v>14.74999999999999</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0288</v>
+        <v>0.0075</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.0149</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.0298</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0576</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0288</v>
+        <v>0.0746</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8847</v>
+        <v>0.7166</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>0.0895</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6.749999999999998</v>
+        <v>5.390000000000001</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -12817,82 +12809,82 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0252</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0252</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>0.0612</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>0.0204</v>
       </c>
       <c r="J33" t="n">
-        <v>0.9244</v>
+        <v>0.898</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0252</v>
+        <v>0.0204</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3.17</v>
+        <v>7.700000000000002</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>0.0429</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>0.0429</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.0286</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0.6857</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>0.0571</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.36</v>
+        <v>6.719999999999999</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>0.0491</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -12901,13 +12893,13 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>0.0506</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>0.0491</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0.8512</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -12916,55 +12908,55 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5.390000000000001</v>
+        <v>3.18</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0.0204</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0408</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1224</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2041</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.4082</v>
+        <v>0.9465</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0612</v>
+        <v>0.0535</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4.749999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -12973,154 +12965,154 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1789</v>
+        <v>0.0495</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0358</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0716</v>
+        <v>0.033</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0358</v>
+        <v>0.0825</v>
       </c>
       <c r="J37" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.8018999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8.040000000000004</v>
+        <v>2.359999999999999</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0137</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0.041</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8209</v>
+        <v>0.8559</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1244</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>5.079999999999998</v>
+        <v>4.620000000000001</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>0.0238</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>0.1429</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.0238</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0335</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0335</v>
+        <v>0.2619</v>
       </c>
       <c r="J39" t="n">
-        <v>0.8327</v>
+        <v>0.4048</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1004</v>
+        <v>0.0476</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>9.920000000000009</v>
+        <v>2.529999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0111</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0887</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0222</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0887</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0887</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6784</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0.0222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5.709999999999999</v>
+        <v>6.270000000000002</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -13129,7 +13121,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.0595</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -13138,28 +13130,28 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0893</v>
+        <v>0.0526</v>
       </c>
       <c r="J41" t="n">
-        <v>0.8511</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>0.0526</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7.269999999999998</v>
+        <v>4.909999999999999</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -13168,76 +13160,76 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0234</v>
+        <v>0.0346</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>0.0692</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0234</v>
+        <v>0.0346</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0234</v>
+        <v>0.0346</v>
       </c>
       <c r="J42" t="n">
-        <v>0.9298</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>0.0692</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7.590000000000009</v>
+        <v>7.610000000000007</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>0.0145</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.029</v>
+        <v>0.0434</v>
       </c>
       <c r="G43" t="n">
         <v>0.0145</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>0.0578</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>0.0723</v>
       </c>
       <c r="J43" t="n">
-        <v>0.9275</v>
+        <v>0.7976</v>
       </c>
       <c r="K43" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4.399999999999999</v>
+        <v>4.85</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -13246,37 +13238,37 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>0.0351</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>0.0351</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7318</v>
+        <v>0.8247</v>
       </c>
       <c r="K44" t="n">
-        <v>0.2682</v>
+        <v>0.1052</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4.559999999999999</v>
+        <v>5.429999999999999</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -13285,19 +13277,19 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0373</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>0.0313</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0373</v>
+        <v>0.0313</v>
       </c>
       <c r="J45" t="n">
-        <v>0.9254</v>
+        <v>0.9374</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -13306,64 +13298,64 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4.35</v>
+        <v>6.969999999999999</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0391</v>
+        <v>0.0244</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>0.0244</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.0391</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>0.0244</v>
       </c>
       <c r="J46" t="n">
-        <v>0.7678</v>
+        <v>0.7805</v>
       </c>
       <c r="K46" t="n">
-        <v>0.154</v>
+        <v>0.1463</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5.56</v>
+        <v>3.229999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0306</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>0.0526</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -13372,34 +13364,34 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1223</v>
+        <v>0.0526</v>
       </c>
       <c r="J47" t="n">
-        <v>0.786</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>0.0612</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2.869999999999999</v>
+        <v>4.33</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>0.0762</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -13414,10 +13406,10 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0.8845</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>0.0393</v>
       </c>
     </row>
     <row r="49">
@@ -13432,7 +13424,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6.01</v>
+        <v>5.929999999999999</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -13444,7 +13436,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0832</v>
+        <v>0.0287</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -13453,10 +13445,10 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.8885</v>
+        <v>0.8853</v>
       </c>
       <c r="K49" t="n">
-        <v>0.0283</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -13471,7 +13463,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3.889999999999999</v>
+        <v>2.719999999999999</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -13489,10 +13481,10 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0848</v>
+        <v>0.0625</v>
       </c>
       <c r="J50" t="n">
-        <v>0.9152</v>
+        <v>0.9375</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -13510,7 +13502,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -13531,10 +13523,10 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0.9592000000000001</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0408</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/public/downloads/drift_radar.xlsx
+++ b/public/downloads/drift_radar.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-01 → 2026-05-03</t>
+          <t>2026-05-02 → 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>33 / 50  (66 %)</t>
+          <t>36 / 50  (72 %)</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -561,7 +561,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6.1 %</t>
+          <t>5.8 %</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8.7 %</t>
+          <t>7.3 %</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3.7 %</t>
+          <t>4.0 %</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2.4×</t>
+          <t>1.8×</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1326,21 +1326,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0.912</v>
@@ -1371,49 +1371,49 @@
         <v>0.5615</v>
       </c>
       <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="P3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
         <v>0.4385</v>
       </c>
-      <c r="R3" t="n">
+      <c r="V3" t="n">
         <v>1</v>
       </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -1425,10 +1425,10 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1440,10 +1440,10 @@
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
@@ -1452,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
@@ -1470,10 +1470,10 @@
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
@@ -1484,33 +1484,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.912</v>
+        <v>0.681</v>
       </c>
       <c r="F4" t="n">
         <v>1.414</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="H4" t="n">
-        <v>0.333</v>
+        <v>0.223</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -1529,91 +1529,91 @@
         <v>0.5615</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>0.2077</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5615</v>
+        <v>0.9385</v>
       </c>
       <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
         <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.4385</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.67</v>
       </c>
       <c r="Y4" t="n">
         <v>0.67</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1</v>
       </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
       <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK4" t="n">
         <v>0.67</v>
       </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
       <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AN4" t="n">
         <v>0.67</v>
       </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1628,10 +1628,10 @@
         <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
@@ -1642,21 +1642,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0.681</v>
@@ -1687,49 +1687,49 @@
         <v>0.5615</v>
       </c>
       <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="S5" t="n">
         <v>0.67</v>
       </c>
-      <c r="P5" t="n">
+      <c r="T5" t="n">
         <v>2</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="U5" t="n">
         <v>0.2077</v>
       </c>
-      <c r="R5" t="n">
+      <c r="V5" t="n">
         <v>0.9385</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1741,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
@@ -1750,10 +1750,10 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
         <v>0</v>
@@ -1789,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
@@ -1800,55 +1800,55 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.681</v>
+        <v>0.592</v>
       </c>
       <c r="F6" t="n">
-        <v>1.414</v>
+        <v>0.821</v>
       </c>
       <c r="G6" t="n">
         <v>0.67</v>
       </c>
       <c r="H6" t="n">
-        <v>0.223</v>
+        <v>0.333</v>
       </c>
       <c r="I6" t="b">
         <v>0</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="O6" t="n">
         <v>0.67</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
         <v>0.2077</v>
@@ -1872,16 +1872,16 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1899,55 +1899,55 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
         <v>0.67</v>
       </c>
-      <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
       <c r="AW6" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
@@ -1958,21 +1958,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>0.592</v>
@@ -2006,7 +2006,7 @@
         <v>0.67</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
         <v>0.2077</v>
@@ -2039,13 +2039,13 @@
         <v>0.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -2057,10 +2057,10 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -2075,16 +2075,16 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
         <v>0</v>
@@ -2102,10 +2102,10 @@
         <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
@@ -2116,12 +2116,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2130,80 +2130,80 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.592</v>
       </c>
       <c r="F8" t="n">
-        <v>1.414</v>
+        <v>0.821</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="H8" t="n">
-        <v>0.167</v>
+        <v>0.333</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>0.2077</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5615</v>
+        <v>0.9385</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0945</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9055</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="Y8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -2215,13 +2215,13 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
@@ -2230,19 +2230,19 @@
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ8" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
@@ -2274,12 +2274,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>0.443</v>
@@ -2319,49 +2319,49 @@
         <v>0.5615</v>
       </c>
       <c r="O9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="U9" t="n">
         <v>0.0615</v>
       </c>
-      <c r="R9" t="n">
+      <c r="V9" t="n">
         <v>0.7923</v>
       </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.5615</v>
-      </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Y9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -2373,19 +2373,19 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2403,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2418,13 +2418,13 @@
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr"/>
@@ -2432,21 +2432,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>0.443</v>
@@ -2510,16 +2510,16 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -2552,16 +2552,16 @@
         <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
         <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
@@ -2590,17 +2590,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2623,62 +2623,62 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="N11" t="n">
+        <v>0.7923</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.5615</v>
       </c>
-      <c r="O11" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0.0615</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.7923</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.7935</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2710,16 +2710,16 @@
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -2734,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
@@ -2748,17 +2748,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -2781,29 +2781,29 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="N12" t="n">
+        <v>0.7923</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>0.5615</v>
       </c>
-      <c r="O12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.0615</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.7923</v>
-      </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
@@ -2820,10 +2820,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2847,7 +2847,7 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
@@ -2859,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2892,10 +2892,10 @@
         <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
@@ -2906,17 +2906,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -2939,61 +2939,61 @@
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P13" t="n">
         <v>1</v>
       </c>
-      <c r="M13" t="n">
+      <c r="Q13" t="n">
         <v>0.0615</v>
       </c>
-      <c r="N13" t="n">
+      <c r="R13" t="n">
         <v>0.7923</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
         <v>0.5615</v>
       </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -3005,19 +3005,19 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -3032,10 +3032,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3050,13 +3050,13 @@
         <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr"/>
@@ -3064,17 +3064,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -3097,29 +3097,29 @@
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
         <v>0.0615</v>
       </c>
-      <c r="N14" t="n">
+      <c r="R14" t="n">
         <v>0.7923</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.5615</v>
-      </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
@@ -3136,10 +3136,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -3163,16 +3163,16 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -3208,10 +3208,10 @@
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
@@ -3222,17 +3222,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -3255,29 +3255,29 @@
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
         <v>0.0615</v>
       </c>
-      <c r="N15" t="n">
+      <c r="R15" t="n">
         <v>0.7923</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.5615</v>
-      </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
@@ -3294,22 +3294,22 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -3321,7 +3321,7 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -3330,10 +3330,10 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
         <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3351,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3366,10 +3366,10 @@
         <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
@@ -3380,38 +3380,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="b">
         <v>1</v>
       </c>
-      <c r="E16" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1.414</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
@@ -3437,16 +3441,16 @@
         <v>0.5615</v>
       </c>
       <c r="S16" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7923</v>
+        <v>0.5615</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -3538,38 +3542,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0.443</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.414</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="I17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>own_only</t>
+        </is>
+      </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
@@ -3583,16 +3591,16 @@
         <v>0.5615</v>
       </c>
       <c r="O17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7923</v>
+        <v>0.5615</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3610,10 +3618,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -3625,7 +3633,7 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -3637,10 +3645,10 @@
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -3649,7 +3657,7 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3682,63 +3690,71 @@
         <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Pavo (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>0.443</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.414</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="I18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>own_only</t>
+        </is>
+      </c>
       <c r="K18" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7923</v>
+        <v>0.5615</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -3765,13 +3781,13 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3783,13 +3799,13 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -3807,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3843,32 +3859,36 @@
         <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Havens (33%), Marstall (33%), Höveler (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -3887,7 +3907,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -3924,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -3939,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -3957,7 +3977,7 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
         <v>0</v>
@@ -3984,7 +4004,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
         <v>0</v>
@@ -4010,27 +4030,23 @@
       <c r="AX19" t="n">
         <v>0</v>
       </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Pavo (33%), Höveler (33%)</t>
-        </is>
-      </c>
+      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -4053,7 +4069,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -4096,22 +4112,22 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -4123,7 +4139,7 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
         <v>0</v>
@@ -4132,10 +4148,10 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -4150,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
         <v>0</v>
@@ -4171,32 +4187,28 @@
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
       </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Höveler (33%)</t>
-        </is>
-      </c>
+      <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -4256,13 +4268,13 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="X21" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -4280,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -4292,7 +4304,7 @@
         <v>0.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -4344,7 +4356,7 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Pavo (100%), Havens (67%)</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr"/>
@@ -4514,21 +4526,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4547,7 +4559,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -4590,22 +4602,22 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -4617,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
@@ -4626,28 +4638,28 @@
         <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AR23" t="n">
         <v>0</v>
@@ -4662,31 +4674,35 @@
         <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX23" t="n">
         <v>0</v>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Marstall (100%), St. Hippolyt (100%), Höveler (67%), Pavo (33%), Eggersmann (33%)</t>
+        </is>
+      </c>
       <c r="AZ23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -4709,7 +4725,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -4746,28 +4762,28 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -4779,28 +4795,28 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -4809,7 +4825,7 @@
         <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR24" t="n">
         <v>0</v>
@@ -4827,28 +4843,32 @@
         <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX24" t="n">
         <v>0</v>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Eggersmann (100%), Pavo (67%), Marstall (67%), St. Hippolyt (67%), Höveler (33%)</t>
+        </is>
+      </c>
       <c r="AZ24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -4871,7 +4891,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -4914,22 +4934,22 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -4944,7 +4964,7 @@
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -4953,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4962,16 +4982,16 @@
         <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AR25" t="n">
         <v>0</v>
@@ -4989,32 +5009,36 @@
         <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX25" t="n">
         <v>0</v>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Marstall (100%), Pavo (67%), Höveler (67%), St. Hippolyt (67%), Eggersmann (33%)</t>
+        </is>
+      </c>
       <c r="AZ25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
+          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -5033,7 +5057,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -5076,22 +5100,22 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -5103,28 +5127,28 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM26" t="n">
         <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5133,10 +5157,10 @@
         <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS26" t="n">
         <v>0</v>
@@ -5145,38 +5169,42 @@
         <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AV26" t="n">
         <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+        <v>0.33</v>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Marstall (100%), Höveler (100%), Pavo (67%), Nösenberger (67%), St. Hippolyt (67%)</t>
+        </is>
+      </c>
       <c r="AZ26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -5195,7 +5223,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -5232,28 +5260,28 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -5265,22 +5293,22 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
         <v>0</v>
@@ -5295,50 +5323,46 @@
         <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
         <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
         <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
         <v>0</v>
       </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Marstall (100%), Höveler (100%), Nösenberger (67%), St. Hippolyt (67%), Pavo (33%)</t>
-        </is>
-      </c>
+      <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -5398,7 +5422,7 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0.5615</v>
+        <v>0.6576</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -5407,19 +5431,19 @@
         <v>0.33</v>
       </c>
       <c r="Y28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -5440,28 +5464,28 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
         <v>0</v>
@@ -5476,17 +5500,17 @@
         <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
         <v>0</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>Marstall (100%), Eggersmann (67%), St. Hippolyt (67%), Pavo (33%), Höveler (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr"/>
@@ -5494,21 +5518,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -5564,19 +5588,19 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0.6576</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -5597,13 +5621,13 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH29" t="n">
         <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
         <v>0</v>
@@ -5615,7 +5639,7 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
         <v>0</v>
@@ -5652,7 +5676,7 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>Pavo (50%), Eggersmann (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (67%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr"/>
@@ -5660,17 +5684,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -5693,7 +5717,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -5730,7 +5754,7 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0.5615</v>
+        <v>0.6576</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -5742,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -5751,7 +5775,7 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -5781,7 +5805,7 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN30" t="n">
         <v>0</v>
@@ -5808,7 +5832,7 @@
         <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW30" t="n">
         <v>0</v>
@@ -5816,27 +5840,31 @@
       <c r="AX30" t="n">
         <v>0</v>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Eggersmann (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -5855,7 +5883,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -5892,13 +5920,13 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -5907,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -5925,7 +5953,7 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
@@ -5952,7 +5980,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ31" t="n">
         <v>0</v>
@@ -5978,27 +6006,31 @@
       <c r="AX31" t="n">
         <v>0</v>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Pavo (33%), Höveler (33%)</t>
+        </is>
+      </c>
       <c r="AZ31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -6063,13 +6095,13 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
@@ -6102,7 +6134,7 @@
         <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
         <v>0</v>
@@ -6120,7 +6152,7 @@
         <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AS32" t="n">
         <v>0</v>
@@ -6142,7 +6174,7 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>Marstall (33%)</t>
+          <t>Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr"/>
@@ -6150,17 +6182,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -6226,22 +6258,22 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -6253,7 +6285,7 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH33" t="n">
         <v>0</v>
@@ -6265,7 +6297,7 @@
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6286,7 +6318,7 @@
         <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
         <v>0</v>
@@ -6301,14 +6333,14 @@
         <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX33" t="n">
         <v>0</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>Höveler (33%)</t>
+          <t>Marstall (67%), St. Hippolyt (67%), Pavo (33%)</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr"/>
@@ -6316,17 +6348,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -6349,7 +6381,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -6386,13 +6418,13 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -6407,7 +6439,7 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -6419,13 +6451,13 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
         <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
         <v>0</v>
@@ -6464,19 +6496,15 @@
         <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
         <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>St. Hippolyt (67%), Pavo (33%)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -6558,23 +6586,23 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
         <v>0.67</v>
       </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AD35" t="n">
         <v>0</v>
       </c>
@@ -6588,59 +6616,59 @@
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
       </c>
       <c r="AJ35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
         <v>0.67</v>
       </c>
-      <c r="AK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AX35" t="n">
         <v>0</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>Marstall (67%), Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (67%), St. Hippolyt (67%), Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr"/>
@@ -6648,17 +6676,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -6724,22 +6752,22 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>0.33</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -6751,7 +6779,7 @@
         <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
         <v>0</v>
@@ -6769,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN36" t="n">
         <v>0</v>
@@ -6778,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR36" t="n">
         <v>0</v>
@@ -6796,17 +6824,17 @@
         <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX36" t="n">
         <v>0</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%)</t>
+          <t>Höveler (67%), Marstall (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr"/>
@@ -6814,21 +6842,21 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -6847,7 +6875,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -6884,22 +6912,22 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
@@ -6917,7 +6945,7 @@
         <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
         <v>0</v>
@@ -6926,7 +6954,7 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
         <v>0</v>
@@ -6944,7 +6972,7 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
         <v>0</v>
@@ -6970,27 +6998,23 @@
       <c r="AX37" t="n">
         <v>0</v>
       </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Pavo (33%), Marstall (33%), Höveler (33%)</t>
-        </is>
-      </c>
+      <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -7056,10 +7080,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z38" t="n">
         <v>0.67</v>
@@ -7071,7 +7095,7 @@
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -7083,10 +7107,10 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -7095,7 +7119,7 @@
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -7131,14 +7155,14 @@
         <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AX38" t="n">
         <v>0</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>Eggersmann (67%), Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (100%), Pavo (67%), Eggersmann (67%), St. Hippolyt (67%)</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr"/>
@@ -7146,21 +7170,21 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -7179,7 +7203,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -7216,28 +7240,28 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -7249,37 +7273,37 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
         <v>0</v>
@@ -7294,35 +7318,31 @@
         <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
         <v>0</v>
       </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Marstall (67%), St. Hippolyt (67%), Pavo (33%), Eggersmann (33%), Höveler (33%)</t>
-        </is>
-      </c>
+      <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -7345,7 +7365,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -7382,22 +7402,22 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
@@ -7415,7 +7435,7 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
         <v>0</v>
@@ -7424,7 +7444,7 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
         <v>0</v>
@@ -7442,7 +7462,7 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
         <v>0</v>
@@ -7468,27 +7488,23 @@
       <c r="AX40" t="n">
         <v>0</v>
       </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Höveler (67%), Pavo (33%), Marstall (33%)</t>
-        </is>
-      </c>
+      <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -7548,19 +7564,19 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0.33</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA41" t="n">
         <v>0.33</v>
@@ -7569,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -7578,22 +7594,22 @@
         <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0.33</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7602,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -7611,7 +7627,7 @@
         <v>0.33</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR41" t="n">
         <v>0</v>
@@ -7626,17 +7642,17 @@
         <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
         <v>0</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>Havens (100%), Marstall (67%), St. Hippolyt (67%), Pavo (33%), Höveler (33%)</t>
+          <t>Pavo (33%), Eggersmann (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr"/>
@@ -7644,12 +7660,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7658,7 +7674,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -7714,13 +7730,13 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>0.33</v>
@@ -7729,13 +7745,13 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -7747,7 +7763,7 @@
         <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
         <v>0</v>
@@ -7756,13 +7772,13 @@
         <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
         <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AM42" t="n">
         <v>0</v>
@@ -7774,7 +7790,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
         <v>0</v>
@@ -7792,17 +7808,17 @@
         <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
         <v>0</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Höveler (33%)</t>
+          <t>Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr"/>
@@ -7810,17 +7826,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -7843,7 +7859,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -7901,7 +7917,7 @@
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -7958,7 +7974,7 @@
         <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW43" t="n">
         <v>0</v>
@@ -7966,27 +7982,31 @@
       <c r="AX43" t="n">
         <v>0</v>
       </c>
-      <c r="AY43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -8005,7 +8025,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -8048,10 +8068,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -8075,7 +8095,7 @@
         <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH44" t="n">
         <v>0</v>
@@ -8084,7 +8104,7 @@
         <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK44" t="n">
         <v>0</v>
@@ -8128,18 +8148,22 @@
       <c r="AX44" t="n">
         <v>0</v>
       </c>
-      <c r="AY44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Pavo (33%), Marstall (33%)</t>
+        </is>
+      </c>
       <c r="AZ44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -8167,7 +8191,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -8210,10 +8234,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -8225,7 +8249,7 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -8237,7 +8261,7 @@
         <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH45" t="n">
         <v>0</v>
@@ -8246,10 +8270,10 @@
         <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -8285,28 +8309,32 @@
         <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX45" t="n">
         <v>0</v>
       </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -8366,52 +8394,52 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W46" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="X46" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
         <v>1</v>
       </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
       <c r="AG46" t="n">
         <v>0.33</v>
       </c>
       <c r="AH46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -8426,7 +8454,7 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ46" t="n">
         <v>0</v>
@@ -8435,7 +8463,7 @@
         <v>0</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AT46" t="n">
         <v>0</v>
@@ -8444,17 +8472,17 @@
         <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX46" t="n">
         <v>0</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>Pavo (100%), Havens (33%)</t>
+          <t>Havens (100%), Pavo (33%), Marstall (33%), Höveler (33%), Nösenberger (33%)</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr"/>
@@ -8462,21 +8490,21 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -8532,16 +8560,16 @@
         <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>0.6576</v>
       </c>
       <c r="W47" t="n">
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -8553,7 +8581,7 @@
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -8565,10 +8593,10 @@
         <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -8577,10 +8605,10 @@
         <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM47" t="n">
         <v>0</v>
@@ -8613,14 +8641,14 @@
         <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX47" t="n">
         <v>0</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>Pavo (67%), St. Hippolyt (67%), Marstall (33%)</t>
+          <t>Marstall (100%), Pavo (33%)</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr"/>
@@ -8628,17 +8656,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -8698,19 +8726,19 @@
         <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>0.6576</v>
       </c>
       <c r="W48" t="n">
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -8719,7 +8747,7 @@
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -8731,10 +8759,10 @@
         <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
@@ -8743,16 +8771,16 @@
         <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -8776,17 +8804,17 @@
         <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW48" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AX48" t="n">
         <v>0</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Marstall (67%), Eggersmann (67%)</t>
+          <t>St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr"/>
@@ -8794,17 +8822,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -8867,19 +8895,19 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
         <v>0</v>
@@ -8891,7 +8919,7 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
         <v>0</v>
@@ -8900,7 +8928,7 @@
         <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -8909,7 +8937,7 @@
         <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8918,13 +8946,13 @@
         <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AQ49" t="n">
         <v>0</v>
@@ -8942,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW49" t="n">
         <v>0.33</v>
@@ -8952,7 +8980,7 @@
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>Höveler (67%), Havens (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%), Marstall (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr"/>
@@ -8960,12 +8988,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -8974,7 +9002,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -8993,7 +9021,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -9036,7 +9064,7 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
         <v>0</v>
@@ -9051,7 +9079,7 @@
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -9063,7 +9091,7 @@
         <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
         <v>0</v>
@@ -9108,7 +9136,7 @@
         <v>0</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW50" t="n">
         <v>0</v>
@@ -9116,27 +9144,23 @@
       <c r="AX50" t="n">
         <v>0</v>
       </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>Pavo (33%), St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -9159,7 +9183,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -9196,28 +9220,28 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W51" t="n">
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
         <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
@@ -9229,19 +9253,19 @@
         <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -9250,7 +9274,7 @@
         <v>0</v>
       </c>
       <c r="AN51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO51" t="n">
         <v>0</v>
@@ -9259,7 +9283,7 @@
         <v>0</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR51" t="n">
         <v>0</v>
@@ -9274,19 +9298,15 @@
         <v>0</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW51" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX51" t="n">
         <v>0</v>
       </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Eggersmann (100%), Pavo (67%), Marstall (67%), St. Hippolyt (67%), Höveler (33%)</t>
-        </is>
-      </c>
+      <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr"/>
     </row>
   </sheetData>
@@ -9312,7 +9332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9416,21 +9436,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0.912</v>
@@ -9440,65 +9460,65 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
       </c>
       <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.912</v>
+        <v>0.681</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0.681</v>
@@ -9508,38 +9528,38 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>0.67</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
       </c>
       <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.681</v>
+        <v>0.592</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H6" t="n">
         <v>0.67</v>
@@ -9552,21 +9572,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>0.592</v>
@@ -9586,12 +9606,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -9600,32 +9620,32 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.592</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -9634,7 +9654,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>0.443</v>
@@ -9644,31 +9664,31 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>0.443</v>
@@ -9688,17 +9708,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -9709,10 +9729,10 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -9722,17 +9742,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -9743,10 +9763,10 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="H12" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -9756,17 +9776,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -9777,10 +9797,10 @@
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -9790,17 +9810,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -9811,10 +9831,10 @@
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -9824,17 +9844,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -9845,120 +9865,18 @@
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Gelenkunterstützung für Pferde</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Natürliche Pferdepflege</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E18">
+  <conditionalFormatting sqref="E2:E15">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -9980,7 +9898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -10050,21 +9968,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -10085,24 +10003,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Pavo (33%), Höveler (33%)</t>
+          <t>Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -10127,24 +10045,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Höveler (33%)</t>
+          <t>Havens (33%), Marstall (33%), Höveler (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -10169,28 +10087,28 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Pavo (100%), Havens (67%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -10211,24 +10129,24 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Marstall (100%), Höveler (100%), Nösenberger (67%), St. Hippolyt (67%), Pavo (33%)</t>
+          <t>Marstall (100%), St. Hippolyt (100%), Höveler (67%), Pavo (33%), Eggersmann (33%)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -10253,24 +10171,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Marstall (100%), Eggersmann (67%), St. Hippolyt (67%), Pavo (33%), Höveler (33%)</t>
+          <t>Eggersmann (100%), Pavo (67%), Marstall (67%), St. Hippolyt (67%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -10295,19 +10213,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Pavo (50%), Eggersmann (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (100%), Pavo (67%), Höveler (67%), St. Hippolyt (67%), Eggersmann (33%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -10337,24 +10255,24 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Marstall (33%)</t>
+          <t>Marstall (100%), Höveler (100%), Pavo (67%), Nösenberger (67%), St. Hippolyt (67%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -10379,28 +10297,28 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Höveler (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -10421,19 +10339,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>St. Hippolyt (67%), Pavo (33%)</t>
+          <t>Pavo (67%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -10463,28 +10381,28 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Marstall (67%), Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Eggersmann (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -10505,24 +10423,24 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%)</t>
+          <t>Pavo (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -10547,19 +10465,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), Höveler (33%)</t>
+          <t>Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -10589,24 +10507,24 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Eggersmann (67%), Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (67%), St. Hippolyt (67%), Pavo (33%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -10631,24 +10549,24 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Marstall (67%), St. Hippolyt (67%), Pavo (33%), Eggersmann (33%), Höveler (33%)</t>
+          <t>Pavo (67%), St. Hippolyt (67%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -10673,24 +10591,24 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Höveler (67%), Pavo (33%), Marstall (33%)</t>
+          <t>Höveler (67%), Marstall (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -10715,24 +10633,24 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Havens (100%), Marstall (67%), St. Hippolyt (67%), Pavo (33%), Höveler (33%)</t>
+          <t>Marstall (100%), Pavo (67%), Eggersmann (67%), St. Hippolyt (67%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -10757,19 +10675,19 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%), Höveler (33%)</t>
+          <t>Pavo (33%), Eggersmann (33%), Höveler (33%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -10778,7 +10696,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -10799,28 +10717,28 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Pavo (100%), Havens (33%)</t>
+          <t>Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10841,24 +10759,24 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Pavo (67%), St. Hippolyt (67%), Marstall (33%)</t>
+          <t>St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -10883,19 +10801,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>St. Hippolyt (100%), Pavo (67%), Marstall (67%), Eggersmann (67%)</t>
+          <t>Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -10925,28 +10843,28 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Höveler (67%), Havens (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10967,54 +10885,138 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Havens (100%), Pavo (33%), Marstall (33%), Höveler (33%), Nösenberger (33%)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>own_only</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Marstall (100%), Pavo (33%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Gelenkunterstützung für Pferde</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>2</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>own_only</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Eggersmann (100%), Pavo (67%), Marstall (67%), St. Hippolyt (67%), Höveler (33%)</t>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>St. Hippolyt (33%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Natürliche Pferdepflege</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>own_only</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Pavo (33%), Marstall (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E24">
+  <conditionalFormatting sqref="E2:E26">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -11036,7 +11038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11106,17 +11108,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -11144,21 +11146,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -11182,12 +11184,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -11220,17 +11222,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -11258,17 +11260,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -11296,17 +11298,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -11334,21 +11336,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -11372,21 +11374,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -11410,21 +11412,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -11448,17 +11450,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -11483,8 +11485,46 @@
       </c>
       <c r="J11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pferdefutter Ergänzungsmittel</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:E11">
+  <conditionalFormatting sqref="E2:E12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -11591,7 +11631,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6.840000000000003</v>
+        <v>7.390000000000003</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -11600,166 +11640,166 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0161</v>
+        <v>0.0298</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0161</v>
+        <v>0.0149</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0322</v>
+        <v>0.0447</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.8214</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0804</v>
+        <v>0.0893</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.72</v>
+        <v>11.12</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.0495</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.0297</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.0297</v>
       </c>
       <c r="H3" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.0396</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8125</v>
+        <v>0.8417</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0625</v>
+        <v>0.009900000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10.46</v>
+        <v>6.029999999999999</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0526</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0315</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8528</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0.021</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.909999999999998</v>
+        <v>9.140000000000011</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0346</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.0722</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0346</v>
+        <v>0.012</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.0602</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8269</v>
+        <v>0.7954</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1039</v>
+        <v>0.0481</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.729999999999999</v>
+        <v>5.559999999999999</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0297</v>
+        <v>0.0306</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.0306</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -11768,25 +11808,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9407</v>
+        <v>0.9388</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7.059999999999999</v>
+        <v>4.379999999999999</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -11795,115 +11835,115 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.0388</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.0776</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9759</v>
+        <v>0.8082</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0241</v>
+        <v>0.07530000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.390000000000004</v>
+        <v>5.409999999999998</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0128</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0266</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0128</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0128</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0639</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8328</v>
+        <v>0.9372</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0383</v>
+        <v>0.06279999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6.930000000000008</v>
+        <v>9.900000000000011</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>0.0222</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0159</v>
+        <v>0.0333</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.0222</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0159</v>
+        <v>0.0556</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0635</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9048</v>
+        <v>0.7222</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.0444</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4.729999999999999</v>
+        <v>4.889999999999999</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -11924,25 +11964,25 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9641</v>
+        <v>0.8609</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0359</v>
+        <v>0.1391</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6.489999999999998</v>
+        <v>4.069999999999999</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -11951,115 +11991,115 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0431</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0216</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8921</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0431</v>
+        <v>0.0418</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_2ba844fe-a638-44f2-bc07-e04b26bc411b</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Finde Nervenpellets für gestresste Pferde ohne Industriezucker.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4.899999999999999</v>
+        <v>2.21</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0347</v>
+        <v>0.0769</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0347</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.2308</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.1538</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8612</v>
+        <v>0.4615</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0694</v>
+        <v>0.0769</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.52</v>
+        <v>7.820000000000007</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.0281</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>0.0141</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.0141</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.0422</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8882</v>
+        <v>0.8875</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1118</v>
+        <v>0.0141</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.34</v>
+        <v>6.17</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -12080,25 +12120,25 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5</v>
+        <v>0.8104</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5</v>
+        <v>0.1896</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1.36</v>
+        <v>3.399999999999999</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -12110,7 +12150,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -12119,64 +12159,64 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.580000000000009</v>
+        <v>9.140000000000011</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0128</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0385</v>
+        <v>0.0241</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0256</v>
+        <v>0.0361</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0385</v>
+        <v>0.012</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0385</v>
+        <v>0.0602</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8077</v>
+        <v>0.8435</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0385</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6.34</v>
+        <v>4.529999999999999</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -12185,40 +12225,40 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.0375</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.0375</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.0728</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8155</v>
+        <v>0.777</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1845</v>
+        <v>0.0751</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.579999999999999</v>
+        <v>7.729999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0258</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12227,73 +12267,73 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="H18" t="n">
-        <v>0.155</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7933</v>
+        <v>0.8913</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0258</v>
+        <v>0.0867</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9.979999999999999</v>
+        <v>6.940000000000007</v>
       </c>
       <c r="D19" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0511</v>
+        <v>0.0159</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0511</v>
+        <v>0.0476</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1363</v>
+        <v>0.0476</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6593</v>
+        <v>0.8732</v>
       </c>
       <c r="K19" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0159</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8.830000000000004</v>
+        <v>15.20999999999998</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -12302,61 +12342,61 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.0506</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.0434</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.0434</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0374</v>
+        <v>0.0434</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8879</v>
+        <v>0.7758</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0747</v>
+        <v>0.0434</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7.260000000000004</v>
+        <v>5.909999999999999</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.0558</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0606</v>
+        <v>0.0288</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0455</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0606</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0606</v>
+        <v>0.0288</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7272999999999999</v>
+        <v>0.7428</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0455</v>
+        <v>0.1438</v>
       </c>
     </row>
     <row r="22">
@@ -12371,7 +12411,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8.040000000000003</v>
+        <v>9.260000000000005</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -12380,271 +12420,271 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1095</v>
+        <v>0.1188</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0137</v>
+        <v>0.0119</v>
       </c>
       <c r="H22" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0832</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1368</v>
+        <v>0.1425</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6306</v>
+        <v>0.6199</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0274</v>
+        <v>0.0238</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4.839999999999998</v>
+        <v>6.380000000000003</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.0172</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.0172</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0455</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0227</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0455</v>
+        <v>0.0172</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8409</v>
+        <v>0.8448</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0455</v>
+        <v>0.0345</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6.489999999999999</v>
+        <v>4.18</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0339</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0508</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0508</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0508</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1017</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5254</v>
+        <v>0.9187</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1864</v>
+        <v>0.0813</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8.800000000000006</v>
+        <v>8.25</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>0.0133</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0375</v>
+        <v>0.12</v>
       </c>
       <c r="G25" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0625</v>
+        <v>0.1333</v>
       </c>
       <c r="I25" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.1867</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6625</v>
+        <v>0.4267</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
+          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10.25000000000001</v>
+        <v>8.920000000000003</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0215</v>
+        <v>0.0247</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0322</v>
+        <v>0.0123</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0429</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0107</v>
+        <v>0.0123</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0322</v>
+        <v>0.0123</v>
       </c>
       <c r="J26" t="n">
-        <v>0.839</v>
+        <v>0.8027</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0215</v>
+        <v>0.1357</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6.380000000000003</v>
+        <v>9.219999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.0184</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0345</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.0184</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.1269</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>0.0184</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9137999999999999</v>
+        <v>0.7809</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0517</v>
+        <v>0.0369</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7.590000000000006</v>
+        <v>7.550000000000002</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0145</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.029</v>
+        <v>0.0159</v>
       </c>
       <c r="G28" t="n">
-        <v>0.058</v>
+        <v>0.0159</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0145</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.058</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6.970000000000002</v>
+        <v>3.23</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -12653,37 +12693,37 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1435</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0172</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1062</v>
+        <v>0.1053</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0703</v>
+        <v>0.2632</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5595</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.1033</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>6.730000000000006</v>
+        <v>5.620000000000002</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -12692,115 +12732,115 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0163</v>
+        <v>0.1121</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.0214</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.1103</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>0.0641</v>
       </c>
       <c r="J30" t="n">
-        <v>0.951</v>
+        <v>0.6281</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0327</v>
+        <v>0.0641</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>14.86999999999998</v>
+        <v>11.42</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0148</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>0.0149</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0296</v>
+        <v>0.0447</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0444</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0296</v>
+        <v>0.0876</v>
       </c>
       <c r="I31" t="n">
-        <v>0.037</v>
+        <v>0.1611</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8003</v>
+        <v>0.6182</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0444</v>
+        <v>0.0736</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>14.74999999999999</v>
+        <v>4.51</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0075</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0149</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0298</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0732</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0746</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.7166</v>
+        <v>0.9024</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0895</v>
+        <v>0.0244</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5.390000000000001</v>
+        <v>8.720000000000004</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -12815,55 +12855,55 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0612</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0204</v>
+        <v>0.0252</v>
       </c>
       <c r="J33" t="n">
-        <v>0.898</v>
+        <v>0.7729</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0204</v>
+        <v>0.2018</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7.700000000000002</v>
+        <v>4.929999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0429</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0429</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0286</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.07140000000000001</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0345</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>0.0345</v>
       </c>
       <c r="J34" t="n">
-        <v>0.6857</v>
+        <v>0.931</v>
       </c>
       <c r="K34" t="n">
-        <v>0.0571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -12878,46 +12918,46 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6.719999999999999</v>
+        <v>11.65</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.0491</v>
+        <v>0.0283</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.0584</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0506</v>
+        <v>0.0292</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0491</v>
+        <v>0.0584</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8512</v>
+        <v>0.7674</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>0.0584</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3.18</v>
+        <v>7.729999999999999</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -12926,37 +12966,37 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9465</v>
+        <v>0.7607</v>
       </c>
       <c r="K36" t="n">
-        <v>0.0535</v>
+        <v>0.1294</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>10.3</v>
+        <v>6.710000000000002</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -12965,43 +13005,43 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0495</v>
+        <v>0.0492</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.0492</v>
       </c>
       <c r="H37" t="n">
-        <v>0.033</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0825</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.7049</v>
       </c>
       <c r="K37" t="n">
-        <v>0.033</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.359999999999999</v>
+        <v>5.899999999999999</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0559</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -13016,64 +13056,64 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8559</v>
+        <v>0.9153</v>
       </c>
       <c r="K38" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0288</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4.620000000000001</v>
+        <v>5.059999999999999</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0238</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1429</v>
+        <v>0.0336</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0238</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.0336</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2619</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.4048</v>
+        <v>0.7352</v>
       </c>
       <c r="K39" t="n">
-        <v>0.0476</v>
+        <v>0.1976</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.529999999999999</v>
+        <v>7.590000000000002</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -13082,37 +13122,37 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.0435</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>0.0725</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>0.1014</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0.6522</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>0.0725</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6.270000000000002</v>
+        <v>2.359999999999999</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -13130,106 +13170,106 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0526</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0.8947000000000001</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>0.0526</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4.909999999999999</v>
+        <v>13.76</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0346</v>
+        <v>0.008</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0692</v>
+        <v>0.024</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0346</v>
+        <v>0.064</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0346</v>
+        <v>0.0799</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.6882</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0692</v>
+        <v>0.1279</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7.610000000000007</v>
+        <v>6.930000000000002</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0145</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0434</v>
+        <v>0.0635</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0145</v>
+        <v>0.0476</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0578</v>
+        <v>0.0794</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0723</v>
+        <v>0.0635</v>
       </c>
       <c r="J43" t="n">
-        <v>0.7976</v>
+        <v>0.7143</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>0.0317</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4.85</v>
+        <v>8.839999999999998</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -13238,37 +13278,37 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.0351</v>
+        <v>0.0577</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.0351</v>
+        <v>0.0385</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>0.8247</v>
+        <v>0.7692</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1052</v>
+        <v>0.0385</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5.429999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -13277,46 +13317,46 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>0.0531</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0313</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0313</v>
+        <v>0.0531</v>
       </c>
       <c r="J45" t="n">
-        <v>0.9374</v>
+        <v>0.8406</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>0.0531</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6.969999999999999</v>
+        <v>5.940000000000002</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0244</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0244</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -13325,118 +13365,118 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0244</v>
+        <v>0.037</v>
       </c>
       <c r="J46" t="n">
-        <v>0.7805</v>
+        <v>0.9074</v>
       </c>
       <c r="K46" t="n">
-        <v>0.1463</v>
+        <v>0.0556</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3.229999999999999</v>
+        <v>5.710000000000002</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>0.0438</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0526</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0526</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4.33</v>
+        <v>7.210000000000004</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0762</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>0.0333</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>0.0166</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8845</v>
+        <v>0.8807</v>
       </c>
       <c r="K48" t="n">
-        <v>0.0393</v>
+        <v>0.0693</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5.929999999999999</v>
+        <v>3.369999999999999</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>0.0979</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.0287</v>
+        <v>0.0504</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -13445,25 +13485,25 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0.8853</v>
+        <v>0.7507</v>
       </c>
       <c r="K49" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.1009</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2.719999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -13481,10 +13521,10 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0625</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0.9375</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -13493,40 +13533,40 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>9.680000000000003</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>0.0227</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>0.0227</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>0.0227</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>0.0682</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>0.1932</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>0.1477</v>
       </c>
     </row>
   </sheetData>

--- a/public/downloads/drift_radar.xlsx
+++ b/public/downloads/drift_radar.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-02 → 2026-05-04</t>
+          <t>2026-05-03 → 2026-05-05</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36 / 50  (72 %)</t>
+          <t>39 / 50  (78 %)</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -561,7 +561,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5.8 %</t>
+          <t>5.1 %</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6.0 %</t>
+          <t>4.6 %</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7.3 %</t>
+          <t>5.3 %</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4.0 %</t>
+          <t>5.3 %</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.8×</t>
+          <t>1.2×</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
+          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
+          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -1201,16 +1201,16 @@
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4385</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.5615</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1225,31 +1225,31 @@
         <v>0.5615</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>0.4385</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5615</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -1267,22 +1267,22 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
         <v>0.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -1294,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AW2" t="n">
         <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
@@ -1326,21 +1326,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
+          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Biete mir eine Auswahl an hochwertigen Magenpellets für sensible Pferde.</t>
+          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>0.912</v>
@@ -1386,10 +1386,10 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4385</v>
+        <v>0.3424</v>
       </c>
       <c r="V3" t="n">
         <v>1</v>
@@ -1398,22 +1398,22 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -1428,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
@@ -1452,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
@@ -1470,10 +1470,10 @@
         <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
@@ -1484,17 +1484,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
+          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
+          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1532,7 +1532,7 @@
         <v>0.67</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
         <v>0.2077</v>
@@ -1556,19 +1556,19 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AC4" t="n">
         <v>0.33</v>
@@ -1583,37 +1583,37 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AU4" t="n">
         <v>0</v>
@@ -1642,21 +1642,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pr_2b7a1b16-eabf-4447-a4ae-5fd09543b33f</t>
+          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Analysiere die Zusammensetzung von Gelenkpellets für Pferde im Hinblick auf Qualität und Verzicht auf Füllstoffe.</t>
+          <t>Zeige mir in der Schweiz erhältliche Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0.681</v>
@@ -1675,16 +1675,16 @@
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.2077</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5615</v>
+        <v>0.9385</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1699,100 +1699,100 @@
         <v>0.5615</v>
       </c>
       <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX5" t="n">
         <v>0.67</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.2077</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.9385</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -1911,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1947,7 +1947,7 @@
         <v>0.67</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
@@ -1958,21 +1958,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
+          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>0.592</v>
@@ -2003,29 +2003,29 @@
         <v>0.7923</v>
       </c>
       <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="S7" t="n">
         <v>0.67</v>
       </c>
-      <c r="P7" t="n">
+      <c r="T7" t="n">
         <v>2</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="U7" t="n">
         <v>0.2077</v>
       </c>
-      <c r="R7" t="n">
+      <c r="V7" t="n">
         <v>0.9385</v>
       </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
@@ -2075,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr"/>
@@ -2116,21 +2116,21 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pr_ce22dac0-782c-42ea-a6e4-2c595108b4d6</t>
+          <t>pr_47e52da7-8646-4683-846d-2af8c113a1fc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pferdefutter zur Gelenkunterstützung ohne künstliche Aromen kaufen.</t>
+          <t>Welche Gelenkpellets für Pferde sind in Deutschland am besten bewertet?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>0.592</v>
@@ -2197,13 +2197,13 @@
         <v>0.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -2215,10 +2215,10 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -2233,16 +2233,16 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
@@ -2263,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
@@ -2274,21 +2274,21 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pr_0ef83482-0bdc-4b69-b5e1-8d9fa4a354fd</t>
+          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichen Nervenpellets für gestresste Pferde.</t>
+          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
         <v>0.443</v>
@@ -2307,16 +2307,16 @@
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5615</v>
+        <v>0.7923</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -2331,22 +2331,22 @@
         <v>0.5615</v>
       </c>
       <c r="S9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7923</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -2379,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
@@ -2418,13 +2418,13 @@
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr"/>
@@ -2432,21 +2432,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>pr_4334d051-e2d1-4913-8548-8ab8ffd9ccba</t>
+          <t>pr_9ff7ac49-9b59-4fcc-976d-59646e809e01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Welche Gelenkpellets ohne Zuckerzusatz gibt es für Pferde?</t>
+          <t>Suche gesundes Zusatzfutter für Pferde in Deutschland.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0.443</v>
@@ -2465,29 +2465,29 @@
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0.0615</v>
       </c>
-      <c r="N10" t="n">
+      <c r="R10" t="n">
         <v>0.7923</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.5615</v>
-      </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
@@ -2504,22 +2504,22 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -2531,37 +2531,37 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
         <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
@@ -2590,21 +2590,21 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
+          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
+          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>0.443</v>
@@ -2623,86 +2623,86 @@
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.5615</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P11" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="Q11" t="n">
         <v>0.0615</v>
       </c>
-      <c r="N11" t="n">
+      <c r="R11" t="n">
         <v>0.7923</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
         <v>0.5615</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
         <v>0.67</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
         <v>0.67</v>
       </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1</v>
       </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
@@ -2710,37 +2710,37 @@
         <v>0</v>
       </c>
       <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW11" t="n">
         <v>0.67</v>
       </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AQ11" t="n">
+      <c r="AX11" t="n">
         <v>0.67</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr"/>
@@ -2748,17 +2748,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
+          <t>pr_dca2eb68-de3d-438c-99ad-fb1f5d30bd28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Gibt es Magenpellets ohne Zuckerzusatz für mein Pferd?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -2784,7 +2784,7 @@
         <v>0.33</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0.0615</v>
@@ -2823,19 +2823,19 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2856,7 +2856,7 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2868,16 +2868,16 @@
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
@@ -2906,38 +2906,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pr_b6f268b3-2a12-4b2d-a6c8-6604a6487b4d</t>
+          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wo finde ich in Deutschland gesundes Pferdefutter?</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>0.443</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.414</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="I13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
@@ -2951,16 +2955,16 @@
         <v>0.5615</v>
       </c>
       <c r="O13" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7923</v>
+        <v>0.5615</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2978,22 +2982,22 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -3011,13 +3015,13 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -3032,10 +3036,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3053,10 +3057,10 @@
         <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr"/>
@@ -3064,38 +3068,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
+          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
+          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.443</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1.414</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="I14" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>own_only</t>
+        </is>
+      </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
@@ -3109,16 +3117,16 @@
         <v>0.5615</v>
       </c>
       <c r="O14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7923</v>
+        <v>0.5615</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3139,7 +3147,7 @@
         <v>0.67</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -3151,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -3163,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
         <v>0.67</v>
@@ -3175,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3208,52 +3216,60 @@
         <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Pavo (67%), St. Hippolyt (67%), Marstall (33%)</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
+          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
+          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0.443</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.414</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="I15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>own_only</t>
+        </is>
+      </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
@@ -3267,16 +3283,16 @@
         <v>0.5615</v>
       </c>
       <c r="O15" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0615</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7923</v>
+        <v>0.5615</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3288,28 +3304,28 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="Y15" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -3321,28 +3337,28 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3351,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3366,31 +3382,35 @@
         <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Pavo (33%), Marstall (33%)</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pr_82801f08-92f8-41ec-aa0e-a5c0b5a8af5c</t>
+          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -3542,21 +3562,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pr_7a8a9195-6c6b-417b-9340-ce1db1d99933</t>
+          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets ohne Zuckerzusatz.</t>
+          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -3621,10 +3641,10 @@
         <v>0.33</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3654,10 +3674,10 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3666,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3700,7 +3720,7 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>Pavo (33%), St. Hippolyt (33%)</t>
+          <t>Eggersmann (67%), Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr"/>
@@ -3708,17 +3728,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
+          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
+          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -3741,7 +3761,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -3781,31 +3801,31 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -3823,7 +3843,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3838,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
         <v>0</v>
@@ -3859,32 +3879,28 @@
         <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Havens (33%), Marstall (33%), Höveler (33%), St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
+          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -3907,7 +3923,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -3944,16 +3960,16 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3977,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH19" t="n">
         <v>0</v>
@@ -3986,7 +4002,7 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -4030,27 +4046,31 @@
       <c r="AX19" t="n">
         <v>0</v>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Pavo (33%), Marstall (33%)</t>
+        </is>
+      </c>
       <c r="AZ19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
+          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
+          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -4198,17 +4218,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
+          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -4268,19 +4288,19 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W21" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -4289,22 +4309,22 @@
         <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -4319,10 +4339,10 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4346,7 +4366,7 @@
         <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW21" t="n">
         <v>0</v>
@@ -4356,7 +4376,7 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>Pavo (100%), Havens (67%)</t>
+          <t>Pavo (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr"/>
@@ -4364,21 +4384,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
+          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
+          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -4397,7 +4417,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -4434,16 +4454,16 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5615</v>
+        <v>0.6576</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -4467,7 +4487,7 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH22" t="n">
         <v>0</v>
@@ -4482,7 +4502,7 @@
         <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AM22" t="n">
         <v>0</v>
@@ -4520,23 +4540,27 @@
       <c r="AX22" t="n">
         <v>0</v>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Marstall (50%), Pavo (33%)</t>
+        </is>
+      </c>
       <c r="AZ22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
+          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
+          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -4596,28 +4620,28 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5615</v>
+        <v>0.6576</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -4629,7 +4653,7 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
@@ -4638,28 +4662,28 @@
         <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
         <v>0</v>
@@ -4674,17 +4698,17 @@
         <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AX23" t="n">
         <v>0</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>Marstall (100%), St. Hippolyt (100%), Höveler (67%), Pavo (33%), Eggersmann (33%)</t>
+          <t>St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr"/>
@@ -4692,17 +4716,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
+          <t>pr_d2a58aaf-8320-4b6c-a4ca-7f7b8e0ff45f</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
+          <t>Vergleiche die Wirksamkeit natürlicher Inhaltsstoffe in Gelenkzusatzfutter für Pferde.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Gelenkunterstützung für Pferde</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -4725,7 +4749,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -4762,28 +4786,28 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -4795,28 +4819,28 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -4825,7 +4849,7 @@
         <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
         <v>0</v>
@@ -4843,32 +4867,28 @@
         <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
         <v>0</v>
       </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Eggersmann (100%), Pavo (67%), Marstall (67%), St. Hippolyt (67%), Höveler (33%)</t>
-        </is>
-      </c>
+      <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
+          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
+          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -4931,49 +4951,49 @@
         <v>0.5615</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
         <v>1</v>
       </c>
-      <c r="Z25" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
       <c r="AG25" t="n">
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK25" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4982,22 +5002,22 @@
         <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
         <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AT25" t="n">
         <v>0</v>
@@ -5009,14 +5029,14 @@
         <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AX25" t="n">
         <v>0</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>Marstall (100%), Pavo (67%), Höveler (67%), St. Hippolyt (67%), Eggersmann (33%)</t>
+          <t>Havens (100%), Marstall (33%), Nösenberger (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr"/>
@@ -5024,12 +5044,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
+          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
+          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5038,7 +5058,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -5057,7 +5077,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -5100,22 +5120,22 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -5127,28 +5147,28 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
         <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5157,10 +5177,10 @@
         <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
         <v>0</v>
@@ -5169,38 +5189,34 @@
         <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
         <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Marstall (100%), Höveler (100%), Pavo (67%), Nösenberger (67%), St. Hippolyt (67%)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
+          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
+          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -5223,7 +5239,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -5266,22 +5282,22 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -5296,7 +5312,7 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -5305,16 +5321,16 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5323,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR27" t="n">
         <v>0</v>
@@ -5341,28 +5357,32 @@
         <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX27" t="n">
         <v>0</v>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Eggersmann (100%), Marstall (67%), Pavo (33%), Höveler (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
+          <t>pr_e3842bfb-9e30-414e-9765-88d2faadce04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
+          <t>Finde in Deutschland hergestelltes Magenfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -5422,28 +5442,28 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0.6576</v>
+        <v>0.5615</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -5455,7 +5475,7 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
         <v>0</v>
@@ -5464,16 +5484,16 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN28" t="n">
         <v>0</v>
@@ -5485,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AR28" t="n">
         <v>0</v>
@@ -5500,17 +5520,17 @@
         <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX28" t="n">
         <v>0</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>Pavo (33%)</t>
+          <t>Marstall (100%), Höveler (67%), St. Hippolyt (67%), Eggersmann (33%)</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr"/>
@@ -5518,21 +5538,21 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
+          <t>pr_892d418a-dd4f-4098-9dc5-c2d0c8be6d83</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Zeige mir gute Vitamine für mein Pferd.</t>
+          <t>Zeig mir Magenpellets für Pferde ohne künstliche Zusätze.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -5591,37 +5611,37 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="X29" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
         <v>0</v>
@@ -5633,7 +5653,7 @@
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5648,10 +5668,10 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR29" t="n">
         <v>0</v>
@@ -5666,7 +5686,7 @@
         <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
         <v>0</v>
@@ -5676,7 +5696,7 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>Pavo (67%), St. Hippolyt (33%)</t>
+          <t>Havens (33%), Marstall (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr"/>
@@ -5684,12 +5704,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>pr_5897c16c-f47e-460c-9e3a-ef50963d2d5f</t>
+          <t>pr_ad86aab8-1689-4374-b2eb-816d091ee9ad</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Zusatzfutter für Freizeitpferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5717,7 +5737,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -5754,7 +5774,7 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0.6576</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -5766,7 +5786,7 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -5775,7 +5795,7 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -5805,7 +5825,7 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
         <v>0</v>
@@ -5832,7 +5852,7 @@
         <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
         <v>0</v>
@@ -5840,31 +5860,27 @@
       <c r="AX30" t="n">
         <v>0</v>
       </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>Eggersmann (33%), St. Hippolyt (33%)</t>
-        </is>
-      </c>
+      <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
+          <t>pr_f4e212fe-a9a1-40dd-acc2-703f937ce744</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
+          <t>Empfiehl mir natürliches Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -5926,7 +5942,7 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -5935,13 +5951,13 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -5953,7 +5969,7 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
@@ -5980,7 +5996,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
         <v>0</v>
@@ -5998,7 +6014,7 @@
         <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW31" t="n">
         <v>0</v>
@@ -6008,7 +6024,7 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>Pavo (33%), Höveler (33%)</t>
+          <t>St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr"/>
@@ -6016,17 +6032,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
+          <t>pr_e6cee04f-e646-4a7f-94c0-48fc4c85c592</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
+          <t>Finde natürliche Pellets zur Unterstützung der Pferdegesundheit.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -6086,13 +6102,13 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0.5615</v>
+        <v>0.6576</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y32" t="n">
         <v>0</v>
@@ -6101,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -6119,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH32" t="n">
         <v>0</v>
@@ -6152,7 +6168,7 @@
         <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
         <v>0</v>
@@ -6164,7 +6180,7 @@
         <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW32" t="n">
         <v>0</v>
@@ -6174,7 +6190,7 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>Höveler (33%)</t>
+          <t>Pavo (33%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr"/>
@@ -6182,21 +6198,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
+          <t>pr_566b4b82-53bb-4435-ac57-2a02e3eb88aa</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
+          <t>Zeige mir gute Vitamine für mein Pferd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -6252,16 +6268,16 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -6273,7 +6289,7 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -6285,7 +6301,7 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AH33" t="n">
         <v>0</v>
@@ -6297,7 +6313,7 @@
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6330,17 +6346,17 @@
         <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
         <v>0</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>Marstall (67%), St. Hippolyt (67%), Pavo (33%)</t>
+          <t>Pavo (100%), St. Hippolyt (33%)</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr"/>
@@ -6348,17 +6364,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pr_ae44d933-64c5-4032-a0a0-74999632519b</t>
+          <t>pr_e2f64483-3123-48e4-aaee-b034f609647d</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Empfiehl mir natürliches Ergänzungsfutter für Pferde mit Magenproblemen.</t>
+          <t>Analysiere, welche Vorteile natürliche Nahrungsergänzungsmittel gegenüber synthetischen Produkten bieten.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -6418,7 +6434,7 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -6510,17 +6526,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
+          <t>pr_a513316a-939f-4130-a4e6-e5361bba66f4</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen unter 50 Euro.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -6589,13 +6605,13 @@
         <v>0.67</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -6613,28 +6629,28 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH35" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
         <v>0.67</v>
       </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0</v>
-      </c>
       <c r="AL35" t="n">
         <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -6643,7 +6659,7 @@
         <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR35" t="n">
         <v>0</v>
@@ -6668,7 +6684,7 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>Pavo (67%), St. Hippolyt (67%), Marstall (33%)</t>
+          <t>Eggersmann (100%), Pavo (67%), Marstall (67%), St. Hippolyt (67%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr"/>
@@ -6676,17 +6692,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
+          <t>pr_052a6419-3a6e-49c5-9995-e2812de6cb50</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
+          <t>Finde hochwertiges Pferdefutter mit natürlichen Inhaltsstoffen.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -6752,13 +6768,13 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AA36" t="n">
         <v>0.67</v>
@@ -6767,7 +6783,7 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -6779,10 +6795,10 @@
         <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -6791,26 +6807,26 @@
         <v>0.33</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ36" t="n">
         <v>0.67</v>
       </c>
-      <c r="AQ36" t="n">
-        <v>0.33</v>
-      </c>
       <c r="AR36" t="n">
         <v>0</v>
       </c>
@@ -6827,14 +6843,14 @@
         <v>0.33</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AX36" t="n">
         <v>0</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>Höveler (67%), Marstall (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
+          <t>Marstall (100%), St. Hippolyt (100%), Eggersmann (67%), Höveler (67%), Pavo (33%)</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr"/>
@@ -6842,21 +6858,21 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>pr_967a4253-01c0-4020-8087-e088910e9456</t>
+          <t>pr_919e94f2-5a66-46fd-b425-6ae88721d518</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Analysiere die Vorteile von natürlichem Zusatzfutter gegenüber synthetischen Produkten.</t>
+          <t>Zeige mir Ergänzungsfutter für Pferde mit Magenproblemen in den Niederlanden.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -6875,7 +6891,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -6912,13 +6928,13 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -6936,19 +6952,19 @@
         <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -6998,23 +7014,27 @@
       <c r="AX37" t="n">
         <v>0</v>
       </c>
-      <c r="AY37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Havens (100%), Pavo (100%)</t>
+        </is>
+      </c>
       <c r="AZ37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>pr_292a6b04-8dee-4ea2-969b-6a83c709753f</t>
+          <t>pr_cd85d59d-0c0b-4f1d-88f5-b8743632963a</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Suche gesundes Ergänzungsfutter für mein Pferd ohne Industriezucker.</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -7074,28 +7094,28 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -7107,10 +7127,10 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -7119,22 +7139,22 @@
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ38" t="n">
         <v>0</v>
@@ -7155,14 +7175,14 @@
         <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
         <v>0</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>Marstall (100%), Pavo (67%), Eggersmann (67%), St. Hippolyt (67%)</t>
+          <t>Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr"/>
@@ -7170,21 +7190,21 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
+          <t>pr_3b705cc9-5167-44e0-83c3-d105b97744ad</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Welche Pellets sind gut für die Gelenke?</t>
+          <t>Analysiere das Preis-Leistungs-Verhältnis von in Deutschland hergestelltem Pferdefutter.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzungsmittel</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -7203,7 +7223,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -7240,28 +7260,28 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -7273,28 +7293,28 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -7303,7 +7323,7 @@
         <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR39" t="n">
         <v>0</v>
@@ -7318,31 +7338,35 @@
         <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX39" t="n">
         <v>0</v>
       </c>
-      <c r="AY39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Marstall (100%), Pavo (67%), St. Hippolyt (67%), Eggersmann (33%), Höveler (33%)</t>
+        </is>
+      </c>
       <c r="AZ39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pr_1a61366f-4ec1-46f7-b5c8-949393e84550</t>
+          <t>pr_e107b87d-d16a-46cd-a7cd-97643c2eecea</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Analysiere die Wirksamkeit von natürlichen Inhaltsstoffen in Magenpellets für Pferde.</t>
+          <t>Gutes Zusatzfutter für Pferde in Österreich gesucht.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferdefutter Ergänzungsmittel</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -7365,7 +7389,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -7402,28 +7426,28 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -7435,7 +7459,7 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH40" t="n">
         <v>0</v>
@@ -7444,7 +7468,7 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK40" t="n">
         <v>0</v>
@@ -7453,7 +7477,7 @@
         <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN40" t="n">
         <v>0</v>
@@ -7462,10 +7486,10 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR40" t="n">
         <v>0</v>
@@ -7483,28 +7507,32 @@
         <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX40" t="n">
         <v>0</v>
       </c>
-      <c r="AY40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Pavo (33%), Marstall (33%), Eggersmann (33%), Höveler (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
+          <t>pr_96ac4e93-069a-498b-aab4-3c1d7e425dd4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
+          <t>Zeige mir in der Schweiz erhältliche Ergänzungsmittel für Hufe.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Natürliche Pferdepflege</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -7564,7 +7592,7 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -7573,19 +7601,19 @@
         <v>0.33</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -7609,7 +7637,7 @@
         <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7618,16 +7646,16 @@
         <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
         <v>0</v>
@@ -7645,14 +7673,14 @@
         <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AX41" t="n">
         <v>0</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>Pavo (33%), Eggersmann (33%), Höveler (33%)</t>
+          <t>St. Hippolyt (67%), Pavo (33%), Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr"/>
@@ -7660,12 +7688,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>pr_46512c1b-40cd-4b0b-ba0d-df3dc4fd74ad</t>
+          <t>pr_d445f7bc-4999-4f1b-9f83-21db9c52bbe8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Vergleiche die Wirksamkeit verschiedener Ergänzungsmittel für Hufe und Fell bei Freizeitpferden.</t>
+          <t>Welche Pellets für gestresste Pferde sind in Deutschland erhältlich?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7674,7 +7702,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -7730,16 +7758,16 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -7751,7 +7779,7 @@
         <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -7763,10 +7791,10 @@
         <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -7778,7 +7806,7 @@
         <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
         <v>0</v>
@@ -7808,17 +7836,17 @@
         <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX42" t="n">
         <v>0</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>Marstall (33%)</t>
+          <t>St. Hippolyt (100%), Pavo (67%)</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr"/>
@@ -7826,17 +7854,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
+          <t>pr_0b9644fb-0bec-4847-b388-b12ea14991da</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
+          <t>Vergleiche die Zusammensetzung von Magen-Darm-Ergänzungsfuttermitteln für sensible Sportpferde.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pferde Nahrungsergänzung</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -7908,16 +7936,16 @@
         <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -7953,7 +7981,7 @@
         <v>0</v>
       </c>
       <c r="AO43" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP43" t="n">
         <v>0</v>
@@ -7962,7 +7990,7 @@
         <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AS43" t="n">
         <v>0</v>
@@ -7974,7 +8002,7 @@
         <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW43" t="n">
         <v>0</v>
@@ -7984,7 +8012,7 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>St. Hippolyt (33%)</t>
+          <t>Eggersmann (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr"/>
@@ -7992,12 +8020,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>pr_9f26a21e-b794-4afa-965f-82573e3aafdd</t>
+          <t>pr_df6c13c4-5d9c-45f9-8971-cb9a61a20b5e</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nenne mir gutes Ergänzungsfutter für mein Pferd.</t>
+          <t>Wo finde ich in der Schweiz gesundes Pferdefutter ohne Zucker?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -8006,7 +8034,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -8062,28 +8090,28 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -8098,37 +8126,37 @@
         <v>0.33</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM44" t="n">
         <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS44" t="n">
         <v>0</v>
@@ -8137,20 +8165,20 @@
         <v>0</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%)</t>
+          <t>Marstall (100%), Höveler (100%), St. Hippolyt (100%), Pavo (67%), Nösenberger (67%)</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr"/>
@@ -8158,17 +8186,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
+          <t>pr_40c01f10-5541-49c6-90be-fec89294d3c5</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
+          <t>Welche Ergänzungsmittel für Hufe und Fell sind empfehlenswert?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Magen-Darm-Gesundheit Pferd</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -8234,7 +8262,7 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="Y45" t="n">
         <v>0.33</v>
@@ -8249,7 +8277,7 @@
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -8261,10 +8289,10 @@
         <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -8273,7 +8301,7 @@
         <v>0.33</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -8309,14 +8337,14 @@
         <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AX45" t="n">
         <v>0</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (67%), St. Hippolyt (67%), Marstall (33%)</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr"/>
@@ -8324,21 +8352,21 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>pr_6cb9c885-6bd8-4dad-91fa-1f9cacdf6c6f</t>
+          <t>pr_22b8e498-4894-4fe3-b560-df45dca80819</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Brauche Pferdefutter mit natürlichen Inhaltsstoffen für Österreich.</t>
+          <t>Welche Pellets sind gut für die Gelenke?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Nahrungsergänzungsmittel</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -8357,7 +8385,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>own_only</t>
+          <t>full</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -8394,28 +8422,28 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -8424,10 +8452,10 @@
         <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
         <v>0</v>
@@ -8436,10 +8464,10 @@
         <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -8454,7 +8482,7 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AQ46" t="n">
         <v>0</v>
@@ -8463,7 +8491,7 @@
         <v>0</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AT46" t="n">
         <v>0</v>
@@ -8472,39 +8500,35 @@
         <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
         <v>0</v>
       </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Havens (100%), Pavo (33%), Marstall (33%), Höveler (33%), Nösenberger (33%)</t>
-        </is>
-      </c>
+      <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>pr_0680bc23-ac9b-4fb2-8d46-7ae9bed12362</t>
+          <t>pr_76c76a27-2b6a-4e7c-9a05-7f270587a055</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für mein Pferd gesucht.</t>
+          <t>Zeige mir gute Ergänzungsfutter für mein Pferd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -8560,7 +8584,7 @@
         <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>0.6576</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
         <v>0</v>
@@ -8569,13 +8593,13 @@
         <v>0.33</v>
       </c>
       <c r="Y47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB47" t="n">
         <v>0</v>
@@ -8608,13 +8632,13 @@
         <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
         <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -8623,7 +8647,7 @@
         <v>0</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AR47" t="n">
         <v>0</v>
@@ -8648,7 +8672,7 @@
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>Marstall (100%), Pavo (33%)</t>
+          <t>Pavo (33%), Eggersmann (33%), Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr"/>
@@ -8656,17 +8680,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>pr_e3000671-0e60-4be0-bd6d-4571ddc261ce</t>
+          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Welche natürlichen Gelenkpellets für Pferde empfiehlst du?</t>
+          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Gelenkunterstützung für Pferde</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -8726,7 +8750,7 @@
         <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>0.6576</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
         <v>0</v>
@@ -8741,13 +8765,13 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -8786,7 +8810,7 @@
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AQ48" t="n">
         <v>0</v>
@@ -8804,17 +8828,17 @@
         <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX48" t="n">
         <v>0</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>St. Hippolyt (33%)</t>
+          <t>Höveler (33%)</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr"/>
@@ -8822,21 +8846,21 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>pr_0af825d7-da11-43fa-81d1-d03d8efe1b8f</t>
+          <t>pr_e229fc63-4622-49a9-99d3-65436ec2ee19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Suche natürliches Zusatzfutter für Pferde ohne Zucker.</t>
+          <t>Nenne mir empfehlenswerte Mineralstoffe für Pferde.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Natürliche Pferdepflege</t>
+          <t>Pferde Vitamine und Mineralstoffe</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -8901,10 +8925,10 @@
         <v>0.33</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -8913,7 +8937,7 @@
         <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -8925,10 +8949,10 @@
         <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -8937,7 +8961,7 @@
         <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -8946,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
@@ -8973,14 +8997,14 @@
         <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AX49" t="n">
         <v>0</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>Pavo (33%), Marstall (33%), Eggersmann (33%), St. Hippolyt (33%)</t>
+          <t>Pavo (33%)</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr"/>
@@ -8988,17 +9012,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>pr_e441ca7f-25e1-4dbf-b939-ff3d7195668b</t>
+          <t>pr_df883bf3-b98c-4bca-a389-2b4cab0aaca5</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Welche natürlichen Nahrungsergänzungsmittel für Pferde empfiehlst du?</t>
+          <t>Vergleiche die Inhaltsstoffe von natürlichem Ergänzungsfutter für Pferde.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pferde Vitamine und Mineralstoffe</t>
+          <t>Pferde Nahrungsergänzung</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -9021,7 +9045,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -9058,7 +9082,7 @@
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>0.5615</v>
       </c>
       <c r="W50" t="n">
         <v>0</v>
@@ -9079,7 +9103,7 @@
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -9136,7 +9160,7 @@
         <v>0</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW50" t="n">
         <v>0</v>
@@ -9144,23 +9168,27 @@
       <c r="AX50" t="n">
         <v>0</v>
       </c>
-      <c r="AY50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>pr_ebe654e5-8567-4eaa-b981-b302228a7121</t>
+          <t>pr_f410d9cf-503e-4fea-904b-f1fcc0ec70df</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Analysiere die Inhaltsstoffe von natürlichem Pferdefutter hinsichtlich ihrer biologischen Wertigkeit.</t>
+          <t>Gutes Zusatzfutter für Magen-Darm-Gesundheit beim Pferd gesucht.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pferdefutter Ergänzungsmittel</t>
+          <t>Magen-Darm-Gesundheit Pferd</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -9183,7 +9211,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>full</t>
+          <t>own_only</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -9220,16 +9248,16 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>0.5615</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -9241,7 +9269,7 @@
         <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
@@ -9253,7 +9281,7 @@
         <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AH51" t="n">
         <v>0</v>
@@ -9265,7 +9293,7 @@
         <v>0</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -9301,12 +9329,16 @@
         <v>0</v>
       </c>
       <c r="AW51" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX51" t="n">
         <v>0</v>
       </c>
-      <c r="AY51" t="inlineStr"/>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Pavo (33%), Marstall (33%), St. Hippolyt (33%)</t>
+        </is>
+      </c>
       <c r="AZ51" t="inlineStr"/>
     </row>
   </sheetData>
@@ -9332,7 +9364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9402,17 +9434,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pr_ec467175-1c22-4484-8f1d-d818f7b40a5e</t>
+          <t>pr_f430c245-6e0b-45f6-ae50-b96facca7aee</t>
         </is>
       </c>
       <c r="B2" t="